--- a/Översikt TOMELILLA.xlsx
+++ b/Översikt TOMELILLA.xlsx
@@ -601,7 +601,7 @@
         <v>44756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45120</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45260</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 14152-2023</t>
+          <t>A 2018-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45009</v>
+        <v>45308</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.5</v>
+        <v>17.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1125,10 +1125,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1140,153 +1140,153 @@
         <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Västlig hakmossa
+Röd glada</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2018-2024 artfynd.xlsx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2018-2024 karta.png", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2018-2024 georefererad karta.tif", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2018-2024 FSC-klagomål.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2018-2024 FSC-klagomål mail.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2018-2024 tillsynsbegäran.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2018-2024 tillsynsbegäran mail.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 2018-2024 prioriterade fågelarter.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 14152-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45009</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TOMELILLA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Kråka
 Röd glada</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 14152-2023 artfynd.xlsx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 14152-2023 karta.png", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 14152-2023 georefererad karta.tif", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 14152-2023 FSC-klagomål.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 14152-2023 FSC-klagomål mail.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 14152-2023 tillsynsbegäran.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 14152-2023 tillsynsbegäran mail.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 14152-2023 prioriterade fågelarter.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 2018-2024</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45308</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>TOMELILLA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Västlig hakmossa
-Röd glada</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2018-2024 artfynd.xlsx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2018-2024 karta.png", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2018-2024 georefererad karta.tif", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2018-2024 FSC-klagomål.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2018-2024 FSC-klagomål mail.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2018-2024 tillsynsbegäran.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2018-2024 tillsynsbegäran mail.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 2018-2024 prioriterade fågelarter.docx", "A 2018-2024")</f>
         <v/>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
         <v>45299</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>45429</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45744</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>44613</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>44721</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>45337</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 2193-2022</t>
+          <t>A 49813-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44578</v>
+        <v>45940</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1979,22 +1979,17 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2009,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2021,39 +2016,39 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Skogslysing</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2193-2022 artfynd.xlsx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 49813-2025 artfynd.xlsx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2193-2022 karta.png", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 49813-2025 karta.png", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2193-2022 georefererad karta.tif", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 49813-2025 georefererad karta.tif", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2193-2022 FSC-klagomål.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 49813-2025 FSC-klagomål.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2193-2022 FSC-klagomål mail.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 49813-2025 FSC-klagomål mail.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2193-2022 tillsynsbegäran.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 49813-2025 tillsynsbegäran.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2193-2022 tillsynsbegäran mail.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 49813-2025 tillsynsbegäran mail.docx", "A 49813-2025")</f>
         <v/>
       </c>
     </row>
@@ -2077,7 +2072,7 @@
         <v>45337</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2165,7 +2160,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 26958-2025</t>
+          <t>A 61314-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2179,10 +2174,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45811</v>
+        <v>46000</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2195,13 +2190,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2235,42 +2230,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26958-2025 artfynd.xlsx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26958-2025 karta.png", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26958-2025 georefererad karta.tif", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26958-2025 FSC-klagomål.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26958-2025 FSC-klagomål mail.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26958-2025 tillsynsbegäran.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26958-2025 tillsynsbegäran mail.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 49813-2025</t>
+          <t>A 26958-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2284,10 +2279,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45940</v>
+        <v>45811</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2300,13 +2295,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2340,42 +2335,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 49813-2025 artfynd.xlsx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26958-2025 artfynd.xlsx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 49813-2025 karta.png", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26958-2025 karta.png", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 49813-2025 georefererad karta.tif", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26958-2025 georefererad karta.tif", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 49813-2025 FSC-klagomål.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26958-2025 FSC-klagomål.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 49813-2025 FSC-klagomål mail.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26958-2025 FSC-klagomål mail.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 49813-2025 tillsynsbegäran.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26958-2025 tillsynsbegäran.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 49813-2025 tillsynsbegäran mail.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26958-2025 tillsynsbegäran mail.docx", "A 26958-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 61314-2025</t>
+          <t>A 2193-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2389,10 +2384,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46000</v>
+        <v>44578</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2404,18 +2399,23 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2441,46 +2441,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Skogslysing</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2193-2022 artfynd.xlsx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2193-2022 karta.png", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2193-2022 georefererad karta.tif", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2193-2022 FSC-klagomål.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2193-2022 FSC-klagomål mail.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2193-2022 tillsynsbegäran.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2193-2022 tillsynsbegäran mail.docx", "A 2193-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 6262-2024</t>
+          <t>A 32949-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45337</v>
+        <v>46244</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2546,46 +2546,50 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6262-2024 artfynd.xlsx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 32949-2026 artfynd.xlsx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6262-2024 karta.png", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 32949-2026 karta.png", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6262-2024 georefererad karta.tif", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 32949-2026 georefererad karta.tif", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6262-2024 FSC-klagomål.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 32949-2026 FSC-klagomål.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6262-2024 FSC-klagomål mail.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 32949-2026 FSC-klagomål mail.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6262-2024 tillsynsbegäran.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 32949-2026 tillsynsbegäran.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6262-2024 tillsynsbegäran mail.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 32949-2026 tillsynsbegäran mail.docx", "A 32949-2026")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 32949-2026 prioriterade fågelarter.docx", "A 32949-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 28862-2023</t>
+          <t>A 20397-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2599,10 +2603,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45104</v>
+        <v>46139</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2614,13 +2618,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2664,38 +2663,38 @@
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 20397-2026 artfynd.xlsx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 20397-2026 karta.png", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 28862-2023 georefererad karta.tif", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 20397-2026 georefererad karta.tif", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 28862-2023 FSC-klagomål.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 20397-2026 FSC-klagomål.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 28862-2023 FSC-klagomål mail.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 20397-2026 FSC-klagomål mail.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 28862-2023 tillsynsbegäran.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 20397-2026 tillsynsbegäran.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 28862-2023 tillsynsbegäran mail.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 20397-2026 tillsynsbegäran mail.docx", "A 20397-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 60820-2023</t>
+          <t>A 6262-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2709,10 +2708,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45260</v>
+        <v>45337</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2725,13 +2724,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2761,46 +2760,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 60820-2023 artfynd.xlsx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6262-2024 artfynd.xlsx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 60820-2023 karta.png", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6262-2024 karta.png", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 60820-2023 georefererad karta.tif", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6262-2024 georefererad karta.tif", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 60820-2023 FSC-klagomål.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6262-2024 FSC-klagomål.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 60820-2023 FSC-klagomål mail.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6262-2024 FSC-klagomål mail.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 60820-2023 tillsynsbegäran.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6262-2024 tillsynsbegäran.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 60820-2023 tillsynsbegäran mail.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6262-2024 tillsynsbegäran mail.docx", "A 6262-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 42387-2022</t>
+          <t>A 26823-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2814,10 +2813,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44830</v>
+        <v>46183</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2830,7 +2829,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>12.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2870,42 +2869,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 42387-2022 artfynd.xlsx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26823-2026 artfynd.xlsx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 42387-2022 karta.png", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26823-2026 karta.png", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 42387-2022 georefererad karta.tif", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26823-2026 georefererad karta.tif", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 42387-2022 FSC-klagomål.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26823-2026 FSC-klagomål.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 42387-2022 FSC-klagomål mail.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26823-2026 FSC-klagomål mail.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 42387-2022 tillsynsbegäran.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26823-2026 tillsynsbegäran.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 42387-2022 tillsynsbegäran mail.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26823-2026 tillsynsbegäran mail.docx", "A 26823-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 756-2024</t>
+          <t>A 60820-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2919,10 +2918,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45300</v>
+        <v>45260</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2934,22 +2933,17 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>13.1</v>
+        <v>4.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2964,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2980,42 +2974,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 756-2024 artfynd.xlsx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 60820-2023 artfynd.xlsx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 756-2024 karta.png", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 60820-2023 karta.png", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 756-2024 georefererad karta.tif", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 60820-2023 georefererad karta.tif", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 756-2024 FSC-klagomål.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 60820-2023 FSC-klagomål.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 756-2024 FSC-klagomål mail.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 60820-2023 FSC-klagomål mail.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 756-2024 tillsynsbegäran.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 60820-2023 tillsynsbegäran.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 756-2024 tillsynsbegäran mail.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 60820-2023 tillsynsbegäran mail.docx", "A 60820-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32949-2026</t>
+          <t>A 28862-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3029,10 +3023,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46244</v>
+        <v>45104</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3044,8 +3038,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3085,46 +3084,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 32949-2026 artfynd.xlsx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 32949-2026 karta.png", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 32949-2026 georefererad karta.tif", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 28862-2023 georefererad karta.tif", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 32949-2026 FSC-klagomål.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 28862-2023 FSC-klagomål.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 32949-2026 FSC-klagomål mail.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 28862-2023 FSC-klagomål mail.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 32949-2026 tillsynsbegäran.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 28862-2023 tillsynsbegäran.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 32949-2026 tillsynsbegäran mail.docx", "A 32949-2026")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 32949-2026 prioriterade fågelarter.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 28862-2023 tillsynsbegäran mail.docx", "A 28862-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 20397-2026</t>
+          <t>A 756-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3138,10 +3133,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46139</v>
+        <v>45300</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3153,18 +3148,23 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>4.2</v>
+        <v>13.1</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
@@ -3178,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3194,42 +3194,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 20397-2026 artfynd.xlsx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 756-2024 artfynd.xlsx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 20397-2026 karta.png", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 756-2024 karta.png", "A 756-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 20397-2026 georefererad karta.tif", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 756-2024 georefererad karta.tif", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 20397-2026 FSC-klagomål.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 756-2024 FSC-klagomål.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 20397-2026 FSC-klagomål mail.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 756-2024 FSC-klagomål mail.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 20397-2026 tillsynsbegäran.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 756-2024 tillsynsbegäran.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 20397-2026 tillsynsbegäran mail.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 756-2024 tillsynsbegäran mail.docx", "A 756-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 26823-2026</t>
+          <t>A 42387-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46183</v>
+        <v>44830</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>12.1</v>
+        <v>1.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3299,35 +3299,35 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26823-2026 artfynd.xlsx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 42387-2022 artfynd.xlsx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26823-2026 karta.png", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 42387-2022 karta.png", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26823-2026 georefererad karta.tif", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 42387-2022 georefererad karta.tif", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26823-2026 FSC-klagomål.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 42387-2022 FSC-klagomål.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26823-2026 FSC-klagomål mail.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 42387-2022 FSC-klagomål mail.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26823-2026 tillsynsbegäran.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 42387-2022 tillsynsbegäran.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26823-2026 tillsynsbegäran mail.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 42387-2022 tillsynsbegäran mail.docx", "A 42387-2022")</f>
         <v/>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
         <v>45419</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>44684</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44560</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44490</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44642</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44721</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 11802-2024</t>
+          <t>A 36180-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45375</v>
+        <v>45534</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3994,13 +3994,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>4.7</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4043,7 +4038,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 4023-2024</t>
+          <t>A 17760-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4057,10 +4052,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45323</v>
+        <v>45758</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4072,13 +4067,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>15.2</v>
+        <v>3.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4121,7 +4111,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 47231-2023</t>
+          <t>A 45729-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4135,10 +4125,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45202</v>
+        <v>45579</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4151,7 +4141,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>10.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4194,7 +4184,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 19454-2024</t>
+          <t>A 2548-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4208,10 +4198,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45429</v>
+        <v>45313</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4224,7 +4214,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4267,7 +4257,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 23813-2024</t>
+          <t>A 38787-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4281,10 +4271,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45455</v>
+        <v>45547</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4297,7 +4287,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4340,7 +4330,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 24248-2024</t>
+          <t>A 13159-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4354,10 +4344,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45457</v>
+        <v>45386</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4370,7 +4360,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4413,7 +4403,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2548-2024</t>
+          <t>A 2555-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4427,10 +4417,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45313</v>
+        <v>44579</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4443,7 +4433,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4486,7 +4476,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 44675-2024</t>
+          <t>A 743-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4496,14 +4486,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45574</v>
+        <v>45300</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4517,11 +4507,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4564,7 +4554,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 17316-2024</t>
+          <t>A 15075-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4574,14 +4564,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45414</v>
+        <v>45399</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4593,13 +4583,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4642,7 +4627,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60817-2023</t>
+          <t>A 11887-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4656,10 +4641,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45260</v>
+        <v>45376</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4671,8 +4656,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>4.3</v>
+        <v>6.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4715,7 +4705,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 7955-2024</t>
+          <t>A 11811-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4729,10 +4719,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45350</v>
+        <v>45727</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4745,7 +4735,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4788,7 +4778,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 16568-2024</t>
+          <t>A 10272-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4802,10 +4792,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45408</v>
+        <v>44986</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4817,8 +4807,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>7.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4861,7 +4856,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 12310-2023</t>
+          <t>A 15158-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4875,10 +4870,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44999</v>
+        <v>45744</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4890,13 +4885,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4939,7 +4929,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 42794-2024</t>
+          <t>A 15012-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4953,10 +4943,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45566</v>
+        <v>45399</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4969,7 +4959,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.9</v>
+        <v>6.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5012,7 +5002,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2190-2022</t>
+          <t>A 43306-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5026,10 +5016,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44578</v>
+        <v>45910</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5041,13 +5031,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5090,7 +5075,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 10272-2023</t>
+          <t>A 49815-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5104,10 +5089,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44986</v>
+        <v>45940</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5119,13 +5104,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>7.7</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5168,7 +5148,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 55676-2022</t>
+          <t>A 4969-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5182,10 +5162,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44888</v>
+        <v>46049</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5197,8 +5177,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5241,7 +5226,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 15158-2025</t>
+          <t>A 8190-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5255,10 +5240,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45744</v>
+        <v>45338</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5270,8 +5255,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5314,7 +5304,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30806-2023</t>
+          <t>A 8192-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5328,10 +5318,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45112</v>
+        <v>45338</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5345,11 +5335,11 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5392,7 +5382,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 43306-2025</t>
+          <t>A 47231-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5406,10 +5396,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45910</v>
+        <v>45202</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5465,7 +5455,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 35792-2025</t>
+          <t>A 28966-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5475,14 +5465,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45861</v>
+        <v>44749</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5494,13 +5484,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5543,7 +5528,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 35971-2025</t>
+          <t>A 578-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5557,10 +5542,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45863</v>
+        <v>45299</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5572,8 +5557,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5616,7 +5606,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 6316-2024</t>
+          <t>A 35792-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5630,10 +5620,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45338</v>
+        <v>45861</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5651,7 +5641,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>28.6</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5694,7 +5684,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8455-2024</t>
+          <t>A 35971-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5708,10 +5698,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45354</v>
+        <v>45863</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5723,13 +5713,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>5.1</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5772,7 +5757,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 13159-2024</t>
+          <t>A 48171-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5786,10 +5771,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45386</v>
+        <v>45933</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5802,7 +5787,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5845,7 +5830,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 48171-2025</t>
+          <t>A 6357-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5859,10 +5844,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45933</v>
+        <v>45338</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5874,8 +5859,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5918,7 +5908,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 61970-2025</t>
+          <t>A 39791-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5928,14 +5918,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46003</v>
+        <v>45891</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5948,7 +5938,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5991,7 +5981,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 39791-2025</t>
+          <t>A 23813-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6005,10 +5995,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45891</v>
+        <v>45455</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6021,7 +6011,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6064,7 +6054,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 7745-2025</t>
+          <t>A 19454-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6074,14 +6064,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45706</v>
+        <v>45429</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6094,7 +6084,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6137,7 +6127,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 15921-2025</t>
+          <t>A 59528-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6151,10 +6141,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45749</v>
+        <v>44907</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6166,8 +6156,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6210,7 +6205,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 6124-2026</t>
+          <t>A 61970-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6220,14 +6215,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46053</v>
+        <v>46003</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6240,7 +6235,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6283,7 +6278,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 16621-2026</t>
+          <t>A 30673-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6297,10 +6292,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46112</v>
+        <v>45112</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6314,11 +6309,11 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6361,7 +6356,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 15305-2025</t>
+          <t>A 6124-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6371,14 +6366,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45746</v>
+        <v>46053</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6391,7 +6386,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6434,7 +6429,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 28966-2022</t>
+          <t>A 16621-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6444,14 +6439,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44749</v>
+        <v>46112</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6463,8 +6458,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6507,7 +6507,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 49913-2025</t>
+          <t>A 1199-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6517,14 +6517,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45940</v>
+        <v>45302</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6536,8 +6536,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>16.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6580,7 +6585,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 578-2024</t>
+          <t>A 4018-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6594,10 +6599,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45299</v>
+        <v>45323</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6615,7 +6620,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>67.40000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6658,7 +6663,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 12988-2024</t>
+          <t>A 61841-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6672,10 +6677,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45385</v>
+        <v>46003</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6687,13 +6692,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>16.2</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6736,7 +6736,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 61841-2025</t>
+          <t>A 49913-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6746,14 +6746,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46003</v>
+        <v>45940</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6809,7 +6809,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 4677-2023</t>
+          <t>A 4482-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44952</v>
+        <v>46045</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6838,8 +6838,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>6.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6882,7 +6887,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 4018-2024</t>
+          <t>A 6259-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6896,10 +6901,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45323</v>
+        <v>45337</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6911,13 +6916,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6960,7 +6960,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 49815-2025</t>
+          <t>A 6316-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45940</v>
+        <v>45338</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6989,8 +6989,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>28.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7033,7 +7038,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 4969-2026</t>
+          <t>A 42794-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7047,10 +7052,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46049</v>
+        <v>45566</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7062,13 +7067,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7111,7 +7111,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 4482-2026</t>
+          <t>A 6852-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7125,10 +7125,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46045</v>
+        <v>46057</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7189,7 +7189,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 6852-2026</t>
+          <t>A 4188-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7203,10 +7203,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46057</v>
+        <v>45324</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.8</v>
+        <v>9.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7267,7 +7267,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 15012-2024</t>
+          <t>A 2190-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45399</v>
+        <v>44578</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7296,8 +7296,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>6.9</v>
+        <v>4.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7340,7 +7345,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 2555-2022</t>
+          <t>A 53977-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7354,10 +7359,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44579</v>
+        <v>44876</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7370,7 +7375,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7413,7 +7418,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 4651-2024</t>
+          <t>A 12903-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7427,10 +7432,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45328</v>
+        <v>45385</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7443,7 +7448,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7486,7 +7491,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 30040-2024</t>
+          <t>A 21291-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7496,14 +7501,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45488</v>
+        <v>46147</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7516,7 +7521,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7559,7 +7564,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 21291-2026</t>
+          <t>A 21293-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7576,7 +7581,7 @@
         <v>46147</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7589,7 +7594,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7632,7 +7637,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 21293-2026</t>
+          <t>A 17151-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7646,10 +7651,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46147</v>
+        <v>45412</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7661,8 +7666,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7705,7 +7715,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 6357-2024</t>
+          <t>A 30040-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7715,14 +7725,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45338</v>
+        <v>45488</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7734,13 +7744,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7783,7 +7788,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 30673-2023</t>
+          <t>A 15288-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7797,10 +7802,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45112</v>
+        <v>46105</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7812,13 +7817,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7861,7 +7861,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 15288-2026</t>
+          <t>A 39796-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46105</v>
+        <v>45891</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7934,7 +7934,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 39796-2025</t>
+          <t>A 16611-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7948,10 +7948,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45891</v>
+        <v>46112</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7963,8 +7963,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8007,7 +8012,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 31993-2023</t>
+          <t>A 24002-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8017,14 +8022,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45119</v>
+        <v>46167</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8037,7 +8042,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8080,7 +8085,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 11894-2024</t>
+          <t>A 15296-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8094,10 +8099,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45376</v>
+        <v>46105</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8109,13 +8114,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>4.4</v>
+        <v>0.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8158,7 +8158,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 16483-2024</t>
+          <t>A 23621-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8172,10 +8172,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45408</v>
+        <v>46162</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8231,7 +8231,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 16611-2026</t>
+          <t>A 32955-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46112</v>
+        <v>46244</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8260,13 +8260,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8309,7 +8304,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 38562-2023</t>
+          <t>A 32948-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8323,10 +8318,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45162</v>
+        <v>46244</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8339,7 +8334,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8382,7 +8377,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 51031-2023</t>
+          <t>A 24987-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8396,10 +8391,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45211</v>
+        <v>46174</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8412,7 +8407,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8455,7 +8450,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 24002-2026</t>
+          <t>A 16483-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8465,14 +8460,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46167</v>
+        <v>45408</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8485,7 +8480,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>6.4</v>
+        <v>0.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8528,7 +8523,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 59528-2022</t>
+          <t>A 12663-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8542,10 +8537,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44907</v>
+        <v>44641</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8563,7 +8558,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.8</v>
+        <v>12.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8606,7 +8601,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 16027-2022</t>
+          <t>A 31134-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8620,10 +8615,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44665</v>
+        <v>46216</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8641,7 +8636,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8684,7 +8679,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 15296-2026</t>
+          <t>A 30806-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8698,10 +8693,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46105</v>
+        <v>45112</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8713,8 +8708,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8757,7 +8757,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 6259-2024</t>
+          <t>A 10908-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8771,10 +8771,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45337</v>
+        <v>46079</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 1199-2024</t>
+          <t>A 17316-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8844,10 +8844,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45302</v>
+        <v>45414</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>16.1</v>
+        <v>4.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8908,7 +8908,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 26473-2024</t>
+          <t>A 35897-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8922,10 +8922,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45469</v>
+        <v>46266</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8981,7 +8981,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 17778-2024</t>
+          <t>A 31993-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8995,10 +8995,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45418</v>
+        <v>45119</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9010,13 +9010,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>2</v>
+        <v>6.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9059,7 +9054,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 8190-2024</t>
+          <t>A 16568-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9073,10 +9068,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45338</v>
+        <v>45408</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9088,13 +9083,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9137,7 +9127,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 8192-2024</t>
+          <t>A 4677-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9151,10 +9141,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45338</v>
+        <v>44952</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9166,13 +9156,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9215,7 +9200,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 32955-2026</t>
+          <t>A 25597-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9229,10 +9214,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46244</v>
+        <v>46177</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9245,7 +9230,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9288,7 +9273,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 23621-2026</t>
+          <t>A 25605-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9302,10 +9287,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46162</v>
+        <v>46177</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9318,7 +9303,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9361,7 +9346,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 17151-2024</t>
+          <t>A 11802-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9375,10 +9360,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45412</v>
+        <v>45375</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9396,7 +9381,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9439,7 +9424,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 32948-2026</t>
+          <t>A 11894-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9453,10 +9438,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46244</v>
+        <v>45376</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9468,8 +9453,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9512,7 +9502,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 12181-2023</t>
+          <t>A 24248-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9526,10 +9516,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44998</v>
+        <v>45457</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9542,7 +9532,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9585,7 +9575,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 23310-2022</t>
+          <t>A 5027-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9599,10 +9589,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44720</v>
+        <v>45329</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9620,7 +9610,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9663,7 +9653,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 5027-2024</t>
+          <t>A 12181-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9677,10 +9667,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45329</v>
+        <v>44998</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9692,13 +9682,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9741,7 +9726,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 743-2024</t>
+          <t>A 38562-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9755,10 +9740,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45300</v>
+        <v>45162</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9770,13 +9755,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>11.1</v>
+        <v>2.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9819,7 +9799,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 24987-2026</t>
+          <t>A 17778-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9833,10 +9813,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46174</v>
+        <v>45418</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9848,8 +9828,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9892,7 +9877,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 53977-2022</t>
+          <t>A 44675-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9902,14 +9887,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44876</v>
+        <v>45574</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9921,8 +9906,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>2.4</v>
+        <v>11.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9965,7 +9955,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 4188-2024</t>
+          <t>A 26473-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9979,10 +9969,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45324</v>
+        <v>45469</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9994,13 +9984,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>9.6</v>
+        <v>4.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10043,7 +10028,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 10908-2026</t>
+          <t>A 51031-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10057,10 +10042,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46079</v>
+        <v>45211</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10073,7 +10058,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10116,7 +10101,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 31134-2026</t>
+          <t>A 7745-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10126,14 +10111,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46216</v>
+        <v>45706</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10145,13 +10130,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10194,7 +10174,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 12663-2022</t>
+          <t>A 5565-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10208,10 +10188,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44641</v>
+        <v>45334</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10223,13 +10203,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>12.4</v>
+        <v>2.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10272,7 +10247,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 35897-2026</t>
+          <t>A 23310-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10286,10 +10261,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46266</v>
+        <v>44720</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10301,8 +10276,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10345,7 +10325,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 36180-2024</t>
+          <t>A 7955-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10359,10 +10339,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45534</v>
+        <v>45350</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10375,7 +10355,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10418,7 +10398,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 12903-2024</t>
+          <t>A 55676-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10432,10 +10412,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45385</v>
+        <v>44888</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10448,7 +10428,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>9.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10491,7 +10471,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 15075-2024</t>
+          <t>A 8455-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10501,14 +10481,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45399</v>
+        <v>45354</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10520,8 +10500,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>1.7</v>
+        <v>5.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10564,7 +10549,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 11887-2024</t>
+          <t>A 16027-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10578,10 +10563,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45376</v>
+        <v>44665</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10599,7 +10584,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>6.3</v>
+        <v>1.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10642,7 +10627,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 5565-2024</t>
+          <t>A 4651-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10656,10 +10641,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45334</v>
+        <v>45328</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10672,7 +10657,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10715,7 +10700,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 25597-2026</t>
+          <t>A 12988-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10729,10 +10714,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46177</v>
+        <v>45385</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10744,8 +10729,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>2.5</v>
+        <v>16.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10788,7 +10778,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 25605-2026</t>
+          <t>A 15305-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10798,14 +10788,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46177</v>
+        <v>45746</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10818,7 +10808,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10861,7 +10851,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 35742-2024</t>
+          <t>A 60817-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10875,10 +10865,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45532</v>
+        <v>45260</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10891,7 +10881,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10934,7 +10924,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 35715-2024</t>
+          <t>A 4023-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10948,10 +10938,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45532</v>
+        <v>45323</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10963,8 +10953,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>1.2</v>
+        <v>15.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11007,7 +11002,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 11806-2025</t>
+          <t>A 12310-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11021,10 +11016,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45727</v>
+        <v>44999</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11036,8 +11031,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11080,7 +11080,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 11810-2025</t>
+          <t>A 15921-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11094,10 +11094,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45727</v>
+        <v>45749</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11153,7 +11153,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 23185-2025</t>
+          <t>A 35742-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11163,14 +11163,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45791</v>
+        <v>45532</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11226,7 +11226,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 17760-2025</t>
+          <t>A 35715-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11240,10 +11240,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45758</v>
+        <v>45532</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11299,7 +11299,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 38787-2024</t>
+          <t>A 11806-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11313,10 +11313,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45547</v>
+        <v>45727</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11372,7 +11372,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 45729-2024</t>
+          <t>A 11810-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11386,10 +11386,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45579</v>
+        <v>45727</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>10.1</v>
+        <v>2.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11445,7 +11445,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 11811-2025</t>
+          <t>A 23185-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11455,14 +11455,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45727</v>
+        <v>45791</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>9.699999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11535,7 +11535,7 @@
         <v>45537</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>

--- a/Översikt TOMELILLA.xlsx
+++ b/Översikt TOMELILLA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE136"/>
+  <dimension ref="A1:AE137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45120</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45260</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2018-2024</t>
+          <t>A 14152-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45308</v>
+        <v>45009</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>17.2</v>
+        <v>3.5</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1125,10 +1125,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1140,153 +1140,153 @@
         <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Kråka
+Röd glada</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 14152-2023 artfynd.xlsx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 14152-2023 karta.png", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 14152-2023 georefererad karta.tif", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 14152-2023 FSC-klagomål.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 14152-2023 FSC-klagomål mail.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 14152-2023 tillsynsbegäran.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 14152-2023 tillsynsbegäran mail.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 14152-2023 prioriterade fågelarter.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 2018-2024</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45308</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TOMELILLA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Västlig hakmossa
 Röd glada</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2018-2024 artfynd.xlsx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2018-2024 karta.png", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2018-2024 georefererad karta.tif", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2018-2024 FSC-klagomål.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2018-2024 FSC-klagomål mail.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2018-2024 tillsynsbegäran.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2018-2024 tillsynsbegäran mail.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 2018-2024 prioriterade fågelarter.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 14152-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45009</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>TOMELILLA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Kråka
-Röd glada</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 14152-2023 artfynd.xlsx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 14152-2023 karta.png", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 14152-2023 georefererad karta.tif", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 14152-2023 FSC-klagomål.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 14152-2023 FSC-klagomål mail.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 14152-2023 tillsynsbegäran.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 14152-2023 tillsynsbegäran mail.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 14152-2023 prioriterade fågelarter.docx", "A 14152-2023")</f>
         <v/>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
         <v>45299</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>45429</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45744</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>44613</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>44721</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 6261-2024</t>
+          <t>A 60820-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45337</v>
+        <v>45260</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>12.6</v>
+        <v>4.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1911,46 +1911,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 60820-2023 artfynd.xlsx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 60820-2023 karta.png", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 60820-2023 georefererad karta.tif", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 60820-2023 FSC-klagomål.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 60820-2023 FSC-klagomål mail.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 60820-2023 tillsynsbegäran.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 60820-2023 tillsynsbegäran mail.docx", "A 60820-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 49813-2025</t>
+          <t>A 6261-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45940</v>
+        <v>45337</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1980,13 +1980,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.5</v>
+        <v>12.6</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -2016,46 +2016,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 49813-2025 artfynd.xlsx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 49813-2025 karta.png", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 49813-2025 georefererad karta.tif", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 49813-2025 FSC-klagomål.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 49813-2025 FSC-klagomål mail.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 49813-2025 tillsynsbegäran.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 49813-2025 tillsynsbegäran mail.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 6261-2024</t>
+          <t>A 42387-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45337</v>
+        <v>44830</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2085,17 +2085,17 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>12.6</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2121,46 +2121,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 42387-2022 artfynd.xlsx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 42387-2022 karta.png", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 42387-2022 georefererad karta.tif", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 42387-2022 FSC-klagomål.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 42387-2022 FSC-klagomål mail.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 42387-2022 tillsynsbegäran.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 42387-2022 tillsynsbegäran mail.docx", "A 42387-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 61314-2025</t>
+          <t>A 756-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46000</v>
+        <v>45300</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2189,18 +2189,23 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>13.1</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
@@ -2214,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2230,42 +2235,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 756-2024 artfynd.xlsx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 756-2024 karta.png", "A 756-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 756-2024 georefererad karta.tif", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 756-2024 FSC-klagomål.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 756-2024 FSC-klagomål mail.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 756-2024 tillsynsbegäran.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 756-2024 tillsynsbegäran mail.docx", "A 756-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 26958-2025</t>
+          <t>A 2193-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2279,10 +2284,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45811</v>
+        <v>44578</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2294,18 +2299,23 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
@@ -2319,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2331,46 +2341,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Skogslysing</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26958-2025 artfynd.xlsx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2193-2022 artfynd.xlsx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26958-2025 karta.png", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2193-2022 karta.png", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26958-2025 georefererad karta.tif", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2193-2022 georefererad karta.tif", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26958-2025 FSC-klagomål.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2193-2022 FSC-klagomål.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26958-2025 FSC-klagomål mail.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2193-2022 FSC-klagomål mail.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26958-2025 tillsynsbegäran.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2193-2022 tillsynsbegäran.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26958-2025 tillsynsbegäran mail.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2193-2022 tillsynsbegäran mail.docx", "A 2193-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 2193-2022</t>
+          <t>A 49813-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2384,10 +2394,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44578</v>
+        <v>45940</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2399,22 +2409,17 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2429,7 +2434,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2441,46 +2446,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Skogslysing</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2193-2022 artfynd.xlsx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 49813-2025 artfynd.xlsx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2193-2022 karta.png", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 49813-2025 karta.png", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2193-2022 georefererad karta.tif", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 49813-2025 georefererad karta.tif", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2193-2022 FSC-klagomål.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 49813-2025 FSC-klagomål.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2193-2022 FSC-klagomål mail.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 49813-2025 FSC-klagomål mail.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2193-2022 tillsynsbegäran.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 49813-2025 tillsynsbegäran.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2193-2022 tillsynsbegäran mail.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 49813-2025 tillsynsbegäran mail.docx", "A 49813-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 32949-2026</t>
+          <t>A 61314-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2494,10 +2499,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46244</v>
+        <v>46000</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2510,7 +2515,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2550,46 +2555,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 32949-2026 artfynd.xlsx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 32949-2026 karta.png", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 32949-2026 georefererad karta.tif", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 32949-2026 FSC-klagomål.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 32949-2026 FSC-klagomål mail.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 32949-2026 tillsynsbegäran.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 32949-2026 tillsynsbegäran mail.docx", "A 32949-2026")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 32949-2026 prioriterade fågelarter.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 20397-2026</t>
+          <t>A 32949-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2603,10 +2604,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46139</v>
+        <v>46244</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2619,7 +2620,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2659,35 +2660,39 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 20397-2026 artfynd.xlsx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 32949-2026 artfynd.xlsx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 20397-2026 karta.png", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 32949-2026 karta.png", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 20397-2026 georefererad karta.tif", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 32949-2026 georefererad karta.tif", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 20397-2026 FSC-klagomål.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 32949-2026 FSC-klagomål.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 20397-2026 FSC-klagomål mail.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 32949-2026 FSC-klagomål mail.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 20397-2026 tillsynsbegäran.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 32949-2026 tillsynsbegäran.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 20397-2026 tillsynsbegäran mail.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 32949-2026 tillsynsbegäran mail.docx", "A 32949-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 32949-2026 prioriterade fågelarter.docx", "A 32949-2026")</f>
         <v/>
       </c>
     </row>
@@ -2711,7 +2716,7 @@
         <v>45337</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2799,7 +2804,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 26823-2026</t>
+          <t>A 28862-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2813,10 +2818,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46183</v>
+        <v>45104</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2828,17 +2833,22 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>12.1</v>
+        <v>6.6</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2853,7 +2863,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2869,42 +2879,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26823-2026 artfynd.xlsx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26823-2026 karta.png", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26823-2026 georefererad karta.tif", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 28862-2023 georefererad karta.tif", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26823-2026 FSC-klagomål.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 28862-2023 FSC-klagomål.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26823-2026 FSC-klagomål mail.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 28862-2023 FSC-klagomål mail.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26823-2026 tillsynsbegäran.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 28862-2023 tillsynsbegäran.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26823-2026 tillsynsbegäran mail.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 28862-2023 tillsynsbegäran mail.docx", "A 28862-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 60820-2023</t>
+          <t>A 20397-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2918,10 +2928,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45260</v>
+        <v>46139</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2934,13 +2944,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2974,42 +2984,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 60820-2023 artfynd.xlsx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 20397-2026 artfynd.xlsx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 60820-2023 karta.png", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 20397-2026 karta.png", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 60820-2023 georefererad karta.tif", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 20397-2026 georefererad karta.tif", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 60820-2023 FSC-klagomål.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 20397-2026 FSC-klagomål.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 60820-2023 FSC-klagomål mail.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 20397-2026 FSC-klagomål mail.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 60820-2023 tillsynsbegäran.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 20397-2026 tillsynsbegäran.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 60820-2023 tillsynsbegäran mail.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 20397-2026 tillsynsbegäran mail.docx", "A 20397-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 28862-2023</t>
+          <t>A 26823-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3023,10 +3033,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45104</v>
+        <v>46183</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3038,23 +3048,18 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>6.6</v>
+        <v>12.1</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3068,7 +3073,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3084,42 +3089,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26823-2026 artfynd.xlsx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26823-2026 karta.png", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 28862-2023 georefererad karta.tif", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26823-2026 georefererad karta.tif", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 28862-2023 FSC-klagomål.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26823-2026 FSC-klagomål.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 28862-2023 FSC-klagomål mail.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26823-2026 FSC-klagomål mail.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 28862-2023 tillsynsbegäran.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26823-2026 tillsynsbegäran.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 28862-2023 tillsynsbegäran mail.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26823-2026 tillsynsbegäran mail.docx", "A 26823-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 756-2024</t>
+          <t>A 17907-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3133,10 +3138,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45300</v>
+        <v>45419</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3148,13 +3153,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>13.1</v>
+        <v>3.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3163,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3178,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3190,46 +3190,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Gulplister</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 756-2024 artfynd.xlsx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 17907-2024 artfynd.xlsx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 756-2024 karta.png", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 17907-2024 karta.png", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 756-2024 georefererad karta.tif", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 17907-2024 georefererad karta.tif", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 756-2024 FSC-klagomål.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 17907-2024 FSC-klagomål.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 756-2024 FSC-klagomål mail.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 17907-2024 FSC-klagomål mail.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 756-2024 tillsynsbegäran.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 17907-2024 tillsynsbegäran.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 756-2024 tillsynsbegäran mail.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 17907-2024 tillsynsbegäran mail.docx", "A 17907-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 42387-2022</t>
+          <t>A 6261-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44830</v>
+        <v>45337</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3259,16 +3259,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.1</v>
+        <v>12.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3295,46 +3295,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 42387-2022 artfynd.xlsx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 42387-2022 karta.png", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 42387-2022 georefererad karta.tif", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 42387-2022 FSC-klagomål.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 42387-2022 FSC-klagomål mail.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 42387-2022 tillsynsbegäran.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 42387-2022 tillsynsbegäran mail.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 17907-2024</t>
+          <t>A 26958-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45419</v>
+        <v>45811</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3364,13 +3364,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3400,39 +3400,39 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Gulplister</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 17907-2024 artfynd.xlsx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26958-2025 artfynd.xlsx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 17907-2024 karta.png", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26958-2025 karta.png", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 17907-2024 georefererad karta.tif", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26958-2025 georefererad karta.tif", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 17907-2024 FSC-klagomål.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26958-2025 FSC-klagomål.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 17907-2024 FSC-klagomål mail.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26958-2025 FSC-klagomål mail.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 17907-2024 tillsynsbegäran.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26958-2025 tillsynsbegäran.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 17907-2024 tillsynsbegäran mail.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26958-2025 tillsynsbegäran mail.docx", "A 26958-2025")</f>
         <v/>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
         <v>44684</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44560</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44490</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44642</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 23461-2022</t>
+          <t>A 47231-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44721</v>
+        <v>45202</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3916,13 +3916,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3965,7 +3960,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 36180-2024</t>
+          <t>A 4023-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3979,10 +3974,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45534</v>
+        <v>45323</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3994,8 +3989,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>15.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4038,7 +4038,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 17760-2025</t>
+          <t>A 11802-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45758</v>
+        <v>45375</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4067,8 +4067,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4111,7 +4116,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 45729-2024</t>
+          <t>A 23461-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4125,10 +4130,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45579</v>
+        <v>44721</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4140,8 +4145,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>10.1</v>
+        <v>3.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4184,7 +4194,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 2548-2024</t>
+          <t>A 38562-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4198,10 +4208,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45313</v>
+        <v>45162</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4214,7 +4224,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4257,7 +4267,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 38787-2024</t>
+          <t>A 51031-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4271,10 +4281,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45547</v>
+        <v>45211</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4287,7 +4297,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4330,7 +4340,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 13159-2024</t>
+          <t>A 59528-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4344,10 +4354,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45386</v>
+        <v>44907</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4359,8 +4369,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4403,7 +4418,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2555-2022</t>
+          <t>A 19454-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4417,10 +4432,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44579</v>
+        <v>45429</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4433,7 +4448,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4476,7 +4491,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 743-2024</t>
+          <t>A 16027-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4490,10 +4505,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45300</v>
+        <v>44665</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4511,7 +4526,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>11.1</v>
+        <v>1.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4554,7 +4569,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 15075-2024</t>
+          <t>A 23813-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4564,14 +4579,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45399</v>
+        <v>45455</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4584,7 +4599,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4627,7 +4642,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 11887-2024</t>
+          <t>A 24248-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4641,10 +4656,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45376</v>
+        <v>45457</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4656,13 +4671,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>6.3</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4705,7 +4715,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 11811-2025</t>
+          <t>A 6259-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4719,10 +4729,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45727</v>
+        <v>45337</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4735,7 +4745,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>9.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4778,7 +4788,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10272-2023</t>
+          <t>A 2548-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4792,10 +4802,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44986</v>
+        <v>45313</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4807,13 +4817,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>7.7</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4856,7 +4861,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 15158-2025</t>
+          <t>A 1199-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4870,10 +4875,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45744</v>
+        <v>45302</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4885,8 +4890,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>1.8</v>
+        <v>16.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4929,7 +4939,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 15012-2024</t>
+          <t>A 44675-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4939,14 +4949,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45399</v>
+        <v>45574</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4958,8 +4968,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>6.9</v>
+        <v>11.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5002,7 +5017,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 43306-2025</t>
+          <t>A 61970-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5012,14 +5027,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45910</v>
+        <v>46003</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5032,7 +5047,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5075,7 +5090,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 49815-2025</t>
+          <t>A 17316-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5089,10 +5104,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45940</v>
+        <v>45414</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5104,8 +5119,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5148,7 +5168,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 4969-2026</t>
+          <t>A 15158-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5162,10 +5182,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46049</v>
+        <v>45744</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5177,13 +5197,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5226,7 +5241,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 8190-2024</t>
+          <t>A 43306-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5240,10 +5255,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45338</v>
+        <v>45910</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5255,13 +5270,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5304,7 +5314,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8192-2024</t>
+          <t>A 6124-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5318,10 +5328,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45338</v>
+        <v>46053</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5333,13 +5343,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5382,7 +5387,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 47231-2023</t>
+          <t>A 16568-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5396,10 +5401,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45202</v>
+        <v>45408</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5412,7 +5417,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5455,7 +5460,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 28966-2022</t>
+          <t>A 12310-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5465,14 +5470,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44749</v>
+        <v>44999</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5484,8 +5489,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5528,7 +5538,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 578-2024</t>
+          <t>A 60817-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5542,10 +5552,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45299</v>
+        <v>45260</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5557,13 +5567,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>67.40000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5606,7 +5611,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 35792-2025</t>
+          <t>A 26473-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5620,10 +5625,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45861</v>
+        <v>45469</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5635,13 +5640,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5684,7 +5684,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35971-2025</t>
+          <t>A 7955-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5698,10 +5698,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45863</v>
+        <v>45350</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5757,7 +5757,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 48171-2025</t>
+          <t>A 17778-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45933</v>
+        <v>45418</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5786,8 +5786,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5830,7 +5835,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 6357-2024</t>
+          <t>A 16621-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5844,10 +5849,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45338</v>
+        <v>46112</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5861,11 +5866,11 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5908,7 +5913,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 39791-2025</t>
+          <t>A 42794-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5922,10 +5927,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45891</v>
+        <v>45566</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5938,7 +5943,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5981,7 +5986,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 23813-2024</t>
+          <t>A 48171-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5995,10 +6000,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45455</v>
+        <v>45933</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6011,7 +6016,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6054,7 +6059,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 19454-2024</t>
+          <t>A 8190-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6068,10 +6073,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45429</v>
+        <v>45338</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6083,8 +6088,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6127,7 +6137,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 59528-2022</t>
+          <t>A 8192-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6141,10 +6151,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44907</v>
+        <v>45338</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6158,11 +6168,11 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6205,7 +6215,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 61970-2025</t>
+          <t>A 2190-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6215,14 +6225,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46003</v>
+        <v>44578</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6234,8 +6244,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6278,7 +6293,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 30673-2023</t>
+          <t>A 39791-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6292,10 +6307,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45112</v>
+        <v>45891</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6307,13 +6322,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6356,7 +6366,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 6124-2026</t>
+          <t>A 10272-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6370,10 +6380,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46053</v>
+        <v>44986</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6385,8 +6395,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>7.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6429,7 +6444,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 16621-2026</t>
+          <t>A 61841-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6443,10 +6458,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46112</v>
+        <v>46003</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6458,13 +6473,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6507,7 +6517,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 1199-2024</t>
+          <t>A 55676-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6521,10 +6531,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45302</v>
+        <v>44888</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6536,13 +6546,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>16.1</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6585,7 +6590,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 4018-2024</t>
+          <t>A 30806-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6599,10 +6604,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45323</v>
+        <v>45112</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6620,7 +6625,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6663,7 +6668,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 61841-2025</t>
+          <t>A 6316-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6677,10 +6682,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46003</v>
+        <v>45338</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6692,8 +6697,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>28.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6736,7 +6746,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 49913-2025</t>
+          <t>A 17151-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6746,14 +6756,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45940</v>
+        <v>45412</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6765,8 +6775,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6826,7 +6841,7 @@
         <v>46045</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6887,7 +6902,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 6259-2024</t>
+          <t>A 8455-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6901,10 +6916,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45337</v>
+        <v>45354</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6916,8 +6931,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6960,7 +6980,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 6316-2024</t>
+          <t>A 6852-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6974,10 +6994,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45338</v>
+        <v>46057</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6995,7 +7015,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>28.6</v>
+        <v>4.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7038,7 +7058,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 42794-2024</t>
+          <t>A 12181-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7052,10 +7072,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45566</v>
+        <v>44998</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7068,7 +7088,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7111,7 +7131,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 6852-2026</t>
+          <t>A 13159-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7125,10 +7145,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46057</v>
+        <v>45386</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7140,13 +7160,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7189,7 +7204,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 4188-2024</t>
+          <t>A 49913-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7199,14 +7214,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45324</v>
+        <v>45940</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7218,13 +7233,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>9.6</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7267,7 +7277,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 2190-2022</t>
+          <t>A 23310-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7281,10 +7291,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44578</v>
+        <v>44720</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7298,11 +7308,11 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7345,7 +7355,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 53977-2022</t>
+          <t>A 21291-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7359,10 +7369,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44876</v>
+        <v>46147</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7375,7 +7385,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7418,7 +7428,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 12903-2024</t>
+          <t>A 21293-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7432,10 +7442,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45385</v>
+        <v>46147</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7448,7 +7458,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>9.199999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7491,7 +7501,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 21291-2026</t>
+          <t>A 7745-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7501,14 +7511,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46147</v>
+        <v>45706</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7521,7 +7531,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7564,7 +7574,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 21293-2026</t>
+          <t>A 15921-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7578,10 +7588,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46147</v>
+        <v>45749</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7594,7 +7604,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7637,7 +7647,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 17151-2024</t>
+          <t>A 15288-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7651,10 +7661,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45412</v>
+        <v>46105</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7666,13 +7676,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7715,7 +7720,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 30040-2024</t>
+          <t>A 39796-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7725,14 +7730,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45488</v>
+        <v>45891</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7745,7 +7750,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7788,7 +7793,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 15288-2026</t>
+          <t>A 15305-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7798,14 +7803,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46105</v>
+        <v>45746</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7818,7 +7823,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7861,7 +7866,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 39796-2025</t>
+          <t>A 5027-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7875,10 +7880,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45891</v>
+        <v>45329</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7890,8 +7895,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7934,7 +7944,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 16611-2026</t>
+          <t>A 28966-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7944,14 +7954,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46112</v>
+        <v>44749</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7963,13 +7973,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8012,7 +8017,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 24002-2026</t>
+          <t>A 743-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8022,14 +8027,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46167</v>
+        <v>45300</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8041,8 +8046,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>6.4</v>
+        <v>11.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8085,7 +8095,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 15296-2026</t>
+          <t>A 578-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8099,10 +8109,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46105</v>
+        <v>45299</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8114,8 +8124,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>0.3</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8158,7 +8173,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 23621-2026</t>
+          <t>A 16611-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8172,10 +8187,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46162</v>
+        <v>46112</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8187,8 +8202,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8231,7 +8251,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 32955-2026</t>
+          <t>A 24002-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8241,14 +8261,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46244</v>
+        <v>46167</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8261,7 +8281,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8304,7 +8324,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 32948-2026</t>
+          <t>A 12988-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8318,10 +8338,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46244</v>
+        <v>45385</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8333,8 +8353,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>1.9</v>
+        <v>16.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8377,7 +8402,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 24987-2026</t>
+          <t>A 49815-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8391,10 +8416,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46174</v>
+        <v>45940</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8407,7 +8432,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8450,7 +8475,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 16483-2024</t>
+          <t>A 53977-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8464,10 +8489,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45408</v>
+        <v>44876</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8480,7 +8505,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8523,7 +8548,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 12663-2022</t>
+          <t>A 4969-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8537,10 +8562,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44641</v>
+        <v>46049</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8558,7 +8583,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>12.4</v>
+        <v>2.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8601,7 +8626,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 31134-2026</t>
+          <t>A 15296-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8615,10 +8640,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46216</v>
+        <v>46105</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8630,13 +8655,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>4.5</v>
+        <v>0.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8679,7 +8699,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 30806-2023</t>
+          <t>A 4677-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8693,10 +8713,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45112</v>
+        <v>44952</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8708,13 +8728,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8757,7 +8772,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 10908-2026</t>
+          <t>A 4018-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8771,10 +8786,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46079</v>
+        <v>45323</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8786,8 +8801,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8830,7 +8850,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 17316-2024</t>
+          <t>A 4188-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8844,10 +8864,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45414</v>
+        <v>45324</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8865,7 +8885,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.3</v>
+        <v>9.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8908,7 +8928,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 35897-2026</t>
+          <t>A 32955-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8922,10 +8942,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46266</v>
+        <v>46244</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8938,7 +8958,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8981,7 +9001,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 31993-2023</t>
+          <t>A 23621-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8995,10 +9015,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45119</v>
+        <v>46162</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9011,7 +9031,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9054,7 +9074,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 16568-2024</t>
+          <t>A 32948-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9068,10 +9088,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45408</v>
+        <v>46244</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9084,7 +9104,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9127,7 +9147,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 4677-2023</t>
+          <t>A 15012-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9141,10 +9161,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44952</v>
+        <v>45399</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9157,7 +9177,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>6.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9200,7 +9220,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 25597-2026</t>
+          <t>A 2555-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9214,10 +9234,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46177</v>
+        <v>44579</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9230,7 +9250,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9273,7 +9293,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 25605-2026</t>
+          <t>A 4651-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9287,10 +9307,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46177</v>
+        <v>45328</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9303,7 +9323,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9346,7 +9366,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 11802-2024</t>
+          <t>A 30040-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9356,14 +9376,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45375</v>
+        <v>45488</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9375,13 +9395,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9424,7 +9439,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 11894-2024</t>
+          <t>A 12663-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9438,10 +9453,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45376</v>
+        <v>44641</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9459,7 +9474,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>4.4</v>
+        <v>12.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9502,7 +9517,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 24248-2024</t>
+          <t>A 24987-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9516,10 +9531,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45457</v>
+        <v>46174</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9532,7 +9547,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9575,7 +9590,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 5027-2024</t>
+          <t>A 6357-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9589,10 +9604,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45329</v>
+        <v>45338</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9606,11 +9621,11 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9653,7 +9668,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 12181-2023</t>
+          <t>A 30673-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9667,10 +9682,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44998</v>
+        <v>45112</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9682,8 +9697,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9726,7 +9746,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 38562-2023</t>
+          <t>A 36180-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9740,10 +9760,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45162</v>
+        <v>45534</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9756,7 +9776,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9799,7 +9819,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 17778-2024</t>
+          <t>A 31993-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9813,10 +9833,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45418</v>
+        <v>45119</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9828,13 +9848,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>6.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9877,7 +9892,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 44675-2024</t>
+          <t>A 11894-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9887,14 +9902,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45574</v>
+        <v>45376</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9908,11 +9923,11 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>11.2</v>
+        <v>4.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9955,7 +9970,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 26473-2024</t>
+          <t>A 16483-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9969,10 +9984,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45469</v>
+        <v>45408</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9985,7 +10000,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10028,7 +10043,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 51031-2023</t>
+          <t>A 10908-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10042,10 +10057,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45211</v>
+        <v>46079</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10058,7 +10073,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10101,7 +10116,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 7745-2025</t>
+          <t>A 31134-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10111,14 +10126,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45706</v>
+        <v>46216</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10130,8 +10145,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>0.4</v>
+        <v>4.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10174,7 +10194,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 5565-2024</t>
+          <t>A 12903-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10188,10 +10208,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45334</v>
+        <v>45385</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10204,7 +10224,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10247,7 +10267,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 23310-2022</t>
+          <t>A 15075-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10257,14 +10277,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44720</v>
+        <v>45399</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10276,13 +10296,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>5.3</v>
+        <v>1.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10325,7 +10340,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 7955-2024</t>
+          <t>A 11887-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10339,10 +10354,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45350</v>
+        <v>45376</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10354,8 +10369,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>2.2</v>
+        <v>6.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10398,7 +10418,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 55676-2022</t>
+          <t>A 35897-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10412,10 +10432,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44888</v>
+        <v>46266</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10428,7 +10448,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10471,7 +10491,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 8455-2024</t>
+          <t>A 5565-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10485,10 +10505,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45354</v>
+        <v>45334</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10500,13 +10520,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>5.1</v>
+        <v>2.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10549,7 +10564,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 16027-2022</t>
+          <t>A 25597-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10563,10 +10578,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44665</v>
+        <v>46177</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10578,13 +10593,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10627,7 +10637,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 4651-2024</t>
+          <t>A 25605-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10641,10 +10651,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45328</v>
+        <v>46177</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10657,7 +10667,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10700,7 +10710,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 12988-2024</t>
+          <t>A 35742-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10714,10 +10724,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45385</v>
+        <v>45532</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10729,13 +10739,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>16.2</v>
+        <v>1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10778,7 +10783,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 15305-2025</t>
+          <t>A 38074-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10788,14 +10793,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45746</v>
+        <v>46280</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10808,7 +10813,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10851,7 +10856,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 60817-2023</t>
+          <t>A 35715-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10865,10 +10870,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45260</v>
+        <v>45532</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10881,7 +10886,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10924,7 +10929,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 4023-2024</t>
+          <t>A 11806-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10938,10 +10943,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45323</v>
+        <v>45727</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10953,13 +10958,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>15.2</v>
+        <v>3.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11002,7 +11002,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 12310-2023</t>
+          <t>A 11810-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11016,10 +11016,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44999</v>
+        <v>45727</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11031,13 +11031,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11080,7 +11075,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 15921-2025</t>
+          <t>A 23185-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11090,14 +11085,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45749</v>
+        <v>45791</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11110,7 +11105,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11153,7 +11148,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 35742-2024</t>
+          <t>A 17760-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11167,10 +11162,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45532</v>
+        <v>45758</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11183,7 +11178,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11226,7 +11221,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 35715-2024</t>
+          <t>A 38787-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11240,10 +11235,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45532</v>
+        <v>45547</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11256,7 +11251,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11299,7 +11294,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 11806-2025</t>
+          <t>A 45729-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11313,10 +11308,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45727</v>
+        <v>45579</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11329,7 +11324,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.1</v>
+        <v>10.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11372,7 +11367,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 11810-2025</t>
+          <t>A 11811-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11389,7 +11384,7 @@
         <v>45727</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11402,7 +11397,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11445,7 +11440,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 23185-2025</t>
+          <t>A 35792-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11455,14 +11450,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45791</v>
+        <v>45861</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11474,8 +11469,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11515,83 +11515,156 @@
       </c>
       <c r="V135" s="2" t="inlineStr"/>
     </row>
-    <row r="136">
+    <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
+          <t>A 35971-2025</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D136" s="1" t="n">
+        <v>45863</v>
+      </c>
+      <c r="E136" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>TOMELILLA</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0</v>
+      </c>
+      <c r="V136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
           <t>S 3422-2024</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D136" s="1" t="n">
+      <c r="D137" s="1" t="n">
         <v>45537</v>
       </c>
-      <c r="E136" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>TOMELILLA</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
+      <c r="E137" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>TOMELILLA</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I136" t="n">
+      <c r="I137" t="n">
         <v>0.1</v>
       </c>
-      <c r="J136" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" t="n">
-        <v>0</v>
-      </c>
-      <c r="M136" t="n">
-        <v>0</v>
-      </c>
-      <c r="N136" t="n">
-        <v>0</v>
-      </c>
-      <c r="O136" t="n">
-        <v>0</v>
-      </c>
-      <c r="P136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
-      <c r="R136" t="n">
-        <v>0</v>
-      </c>
-      <c r="S136" t="n">
-        <v>0</v>
-      </c>
-      <c r="T136" t="n">
-        <v>0</v>
-      </c>
-      <c r="U136" t="n">
-        <v>0</v>
-      </c>
-      <c r="V136" s="2" t="inlineStr"/>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TOMELILLA.xlsx
+++ b/Översikt TOMELILLA.xlsx
@@ -601,7 +601,7 @@
         <v>44756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45120</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45260</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 14152-2023</t>
+          <t>A 2018-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45009</v>
+        <v>45308</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.5</v>
+        <v>17.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1125,10 +1125,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1140,153 +1140,153 @@
         <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Västlig hakmossa
+Röd glada</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2018-2024 artfynd.xlsx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2018-2024 karta.png", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2018-2024 georefererad karta.tif", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2018-2024 FSC-klagomål.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2018-2024 FSC-klagomål mail.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2018-2024 tillsynsbegäran.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2018-2024 tillsynsbegäran mail.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 2018-2024 prioriterade fågelarter.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 14152-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45009</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TOMELILLA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Kråka
 Röd glada</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 14152-2023 artfynd.xlsx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 14152-2023 karta.png", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 14152-2023 georefererad karta.tif", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 14152-2023 FSC-klagomål.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 14152-2023 FSC-klagomål mail.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 14152-2023 tillsynsbegäran.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 14152-2023 tillsynsbegäran mail.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 14152-2023 prioriterade fågelarter.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 2018-2024</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45308</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>TOMELILLA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Västlig hakmossa
-Röd glada</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2018-2024 artfynd.xlsx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2018-2024 karta.png", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2018-2024 georefererad karta.tif", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2018-2024 FSC-klagomål.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2018-2024 FSC-klagomål mail.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2018-2024 tillsynsbegäran.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2018-2024 tillsynsbegäran mail.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 2018-2024 prioriterade fågelarter.docx", "A 2018-2024")</f>
         <v/>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
         <v>45299</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>45429</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45744</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>44613</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>44721</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 60820-2023</t>
+          <t>A 6261-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45260</v>
+        <v>45337</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.6</v>
+        <v>12.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1911,39 +1911,39 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 60820-2023 artfynd.xlsx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 60820-2023 karta.png", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 60820-2023 georefererad karta.tif", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 60820-2023 FSC-klagomål.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 60820-2023 FSC-klagomål mail.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 60820-2023 tillsynsbegäran.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 60820-2023 tillsynsbegäran mail.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
         <v>45337</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 42387-2022</t>
+          <t>A 26958-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44830</v>
+        <v>45811</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2085,16 +2085,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2125,42 +2125,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 42387-2022 artfynd.xlsx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26958-2025 artfynd.xlsx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 42387-2022 karta.png", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26958-2025 karta.png", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 42387-2022 georefererad karta.tif", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26958-2025 georefererad karta.tif", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 42387-2022 FSC-klagomål.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26958-2025 FSC-klagomål.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 42387-2022 FSC-klagomål mail.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26958-2025 FSC-klagomål mail.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 42387-2022 tillsynsbegäran.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26958-2025 tillsynsbegäran.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 42387-2022 tillsynsbegäran mail.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26958-2025 tillsynsbegäran mail.docx", "A 26958-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 756-2024</t>
+          <t>A 49813-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45300</v>
+        <v>45940</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2189,22 +2189,17 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>13.1</v>
+        <v>4.5</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2219,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2235,42 +2230,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 756-2024 artfynd.xlsx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 49813-2025 artfynd.xlsx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 756-2024 karta.png", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 49813-2025 karta.png", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 756-2024 georefererad karta.tif", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 49813-2025 georefererad karta.tif", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 756-2024 FSC-klagomål.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 49813-2025 FSC-klagomål.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 756-2024 FSC-klagomål mail.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 49813-2025 FSC-klagomål mail.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 756-2024 tillsynsbegäran.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 49813-2025 tillsynsbegäran.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 756-2024 tillsynsbegäran mail.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 49813-2025 tillsynsbegäran mail.docx", "A 49813-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 2193-2022</t>
+          <t>A 61314-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2284,10 +2279,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44578</v>
+        <v>46000</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2299,22 +2294,17 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2329,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2341,46 +2331,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Skogslysing</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2193-2022 artfynd.xlsx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2193-2022 karta.png", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2193-2022 georefererad karta.tif", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2193-2022 FSC-klagomål.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2193-2022 FSC-klagomål mail.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2193-2022 tillsynsbegäran.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2193-2022 tillsynsbegäran mail.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 49813-2025</t>
+          <t>A 2193-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2394,10 +2384,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45940</v>
+        <v>44578</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2409,18 +2399,23 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -2434,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2446,46 +2441,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Skogslysing</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 49813-2025 artfynd.xlsx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2193-2022 artfynd.xlsx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 49813-2025 karta.png", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2193-2022 karta.png", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 49813-2025 georefererad karta.tif", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2193-2022 georefererad karta.tif", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 49813-2025 FSC-klagomål.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2193-2022 FSC-klagomål.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 49813-2025 FSC-klagomål mail.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2193-2022 FSC-klagomål mail.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 49813-2025 tillsynsbegäran.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2193-2022 tillsynsbegäran.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 49813-2025 tillsynsbegäran mail.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2193-2022 tillsynsbegäran mail.docx", "A 2193-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 61314-2025</t>
+          <t>A 6262-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2499,10 +2494,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46000</v>
+        <v>45337</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2510,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2551,46 +2546,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6262-2024 artfynd.xlsx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6262-2024 karta.png", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6262-2024 georefererad karta.tif", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6262-2024 FSC-klagomål.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6262-2024 FSC-klagomål mail.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6262-2024 tillsynsbegäran.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6262-2024 tillsynsbegäran mail.docx", "A 6262-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 32949-2026</t>
+          <t>A 60820-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2604,10 +2599,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46244</v>
+        <v>45260</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2620,13 +2615,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2660,46 +2655,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 32949-2026 artfynd.xlsx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 60820-2023 artfynd.xlsx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 32949-2026 karta.png", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 60820-2023 karta.png", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 32949-2026 georefererad karta.tif", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 60820-2023 georefererad karta.tif", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 32949-2026 FSC-klagomål.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 60820-2023 FSC-klagomål.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 32949-2026 FSC-klagomål mail.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 60820-2023 FSC-klagomål mail.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 32949-2026 tillsynsbegäran.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 60820-2023 tillsynsbegäran.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 32949-2026 tillsynsbegäran mail.docx", "A 32949-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 32949-2026 prioriterade fågelarter.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 60820-2023 tillsynsbegäran mail.docx", "A 60820-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 6262-2024</t>
+          <t>A 28862-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2713,10 +2704,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45337</v>
+        <v>45104</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2728,8 +2719,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2765,46 +2761,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6262-2024 artfynd.xlsx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6262-2024 karta.png", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6262-2024 georefererad karta.tif", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 28862-2023 georefererad karta.tif", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6262-2024 FSC-klagomål.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 28862-2023 FSC-klagomål.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6262-2024 FSC-klagomål mail.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 28862-2023 FSC-klagomål mail.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6262-2024 tillsynsbegäran.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 28862-2023 tillsynsbegäran.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6262-2024 tillsynsbegäran mail.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 28862-2023 tillsynsbegäran mail.docx", "A 28862-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 28862-2023</t>
+          <t>A 32949-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2818,10 +2814,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45104</v>
+        <v>46244</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,13 +2829,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2879,42 +2870,46 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 32949-2026 artfynd.xlsx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 32949-2026 karta.png", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 28862-2023 georefererad karta.tif", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 32949-2026 georefererad karta.tif", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 28862-2023 FSC-klagomål.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 32949-2026 FSC-klagomål.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 28862-2023 FSC-klagomål mail.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 32949-2026 FSC-klagomål mail.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 28862-2023 tillsynsbegäran.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 32949-2026 tillsynsbegäran.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 28862-2023 tillsynsbegäran mail.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 32949-2026 tillsynsbegäran mail.docx", "A 32949-2026")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 32949-2026 prioriterade fågelarter.docx", "A 32949-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 20397-2026</t>
+          <t>A 756-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2928,10 +2923,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46139</v>
+        <v>45300</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2943,18 +2938,23 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>4.2</v>
+        <v>13.1</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
@@ -2968,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2984,42 +2984,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 20397-2026 artfynd.xlsx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 756-2024 artfynd.xlsx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 20397-2026 karta.png", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 756-2024 karta.png", "A 756-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 20397-2026 georefererad karta.tif", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 756-2024 georefererad karta.tif", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 20397-2026 FSC-klagomål.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 756-2024 FSC-klagomål.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 20397-2026 FSC-klagomål mail.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 756-2024 FSC-klagomål mail.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 20397-2026 tillsynsbegäran.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 756-2024 tillsynsbegäran.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 20397-2026 tillsynsbegäran mail.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 756-2024 tillsynsbegäran mail.docx", "A 756-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 26823-2026</t>
+          <t>A 42387-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46183</v>
+        <v>44830</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>12.1</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3089,42 +3089,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26823-2026 artfynd.xlsx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 42387-2022 artfynd.xlsx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26823-2026 karta.png", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 42387-2022 karta.png", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26823-2026 georefererad karta.tif", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 42387-2022 georefererad karta.tif", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26823-2026 FSC-klagomål.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 42387-2022 FSC-klagomål.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26823-2026 FSC-klagomål mail.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 42387-2022 FSC-klagomål mail.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26823-2026 tillsynsbegäran.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 42387-2022 tillsynsbegäran.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26823-2026 tillsynsbegäran mail.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 42387-2022 tillsynsbegäran mail.docx", "A 42387-2022")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 17907-2024</t>
+          <t>A 20397-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3138,10 +3138,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45419</v>
+        <v>46139</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3190,46 +3190,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Gulplister</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 17907-2024 artfynd.xlsx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 20397-2026 artfynd.xlsx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 17907-2024 karta.png", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 20397-2026 karta.png", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 17907-2024 georefererad karta.tif", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 20397-2026 georefererad karta.tif", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 17907-2024 FSC-klagomål.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 20397-2026 FSC-klagomål.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 17907-2024 FSC-klagomål mail.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 20397-2026 FSC-klagomål mail.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 17907-2024 tillsynsbegäran.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 20397-2026 tillsynsbegäran.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 17907-2024 tillsynsbegäran mail.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 20397-2026 tillsynsbegäran mail.docx", "A 20397-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 6261-2024</t>
+          <t>A 26823-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45337</v>
+        <v>46183</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3259,17 +3259,17 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>12.6</v>
+        <v>12.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3295,46 +3295,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26823-2026 artfynd.xlsx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26823-2026 karta.png", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26823-2026 georefererad karta.tif", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26823-2026 FSC-klagomål.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26823-2026 FSC-klagomål mail.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26823-2026 tillsynsbegäran.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26823-2026 tillsynsbegäran mail.docx", "A 26823-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 26958-2025</t>
+          <t>A 17907-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45811</v>
+        <v>45419</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3364,13 +3364,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3400,39 +3400,39 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Gulplister</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26958-2025 artfynd.xlsx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 17907-2024 artfynd.xlsx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26958-2025 karta.png", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 17907-2024 karta.png", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26958-2025 georefererad karta.tif", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 17907-2024 georefererad karta.tif", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26958-2025 FSC-klagomål.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 17907-2024 FSC-klagomål.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26958-2025 FSC-klagomål mail.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 17907-2024 FSC-klagomål mail.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26958-2025 tillsynsbegäran.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 17907-2024 tillsynsbegäran.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26958-2025 tillsynsbegäran mail.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 17907-2024 tillsynsbegäran mail.docx", "A 17907-2024")</f>
         <v/>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
         <v>44684</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44560</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44490</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44642</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 47231-2023</t>
+          <t>A 23461-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45202</v>
+        <v>44721</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3916,8 +3916,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3960,7 +3965,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 4023-2024</t>
+          <t>A 36180-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3974,10 +3979,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45323</v>
+        <v>45534</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3989,13 +3994,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>15.2</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4038,7 +4038,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 11802-2024</t>
+          <t>A 2548-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45375</v>
+        <v>45313</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4067,13 +4067,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4116,7 +4111,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 23461-2022</t>
+          <t>A 13159-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4130,10 +4125,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44721</v>
+        <v>45386</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4145,13 +4140,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4194,7 +4184,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 38562-2023</t>
+          <t>A 2555-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4208,10 +4198,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45162</v>
+        <v>44579</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4224,7 +4214,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4267,7 +4257,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 51031-2023</t>
+          <t>A 45729-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4281,10 +4271,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45211</v>
+        <v>45579</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4297,7 +4287,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>10.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4340,7 +4330,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 59528-2022</t>
+          <t>A 15075-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4350,14 +4340,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44907</v>
+        <v>45399</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4369,13 +4359,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4418,7 +4403,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 19454-2024</t>
+          <t>A 38787-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4432,10 +4417,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45429</v>
+        <v>45547</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4448,7 +4433,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4491,7 +4476,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 16027-2022</t>
+          <t>A 743-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4505,10 +4490,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44665</v>
+        <v>45300</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4526,7 +4511,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.9</v>
+        <v>11.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4569,7 +4554,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 23813-2024</t>
+          <t>A 11887-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4583,10 +4568,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45455</v>
+        <v>45376</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4598,8 +4583,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>6.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4642,7 +4632,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 24248-2024</t>
+          <t>A 10272-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4656,10 +4646,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45457</v>
+        <v>44986</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4671,8 +4661,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>7.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4715,7 +4710,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 6259-2024</t>
+          <t>A 15012-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4729,10 +4724,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45337</v>
+        <v>45399</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4745,7 +4740,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5</v>
+        <v>6.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4788,7 +4783,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 2548-2024</t>
+          <t>A 11811-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4802,10 +4797,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45313</v>
+        <v>45727</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4818,7 +4813,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4861,7 +4856,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 1199-2024</t>
+          <t>A 8190-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4875,10 +4870,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45302</v>
+        <v>45338</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4892,11 +4887,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>16.1</v>
+        <v>3.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4939,7 +4934,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 44675-2024</t>
+          <t>A 8192-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4949,14 +4944,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45574</v>
+        <v>45338</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4970,11 +4965,11 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>11.2</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5017,7 +5012,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 61970-2025</t>
+          <t>A 47231-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5027,14 +5022,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46003</v>
+        <v>45202</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5047,7 +5042,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5090,7 +5085,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 17316-2024</t>
+          <t>A 15158-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5104,10 +5099,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45414</v>
+        <v>45744</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5119,13 +5114,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5168,7 +5158,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 15158-2025</t>
+          <t>A 28966-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5178,14 +5168,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45744</v>
+        <v>44749</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5198,7 +5188,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5258,7 +5248,7 @@
         <v>45910</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5314,7 +5304,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 6124-2026</t>
+          <t>A 578-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5328,10 +5318,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46053</v>
+        <v>45299</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5343,8 +5333,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5387,7 +5382,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 16568-2024</t>
+          <t>A 6357-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5401,10 +5396,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45408</v>
+        <v>45338</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5414,6 +5409,11 @@
       <c r="G54" t="inlineStr">
         <is>
           <t>TOMELILLA</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -5460,7 +5460,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 12310-2023</t>
+          <t>A 23813-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5474,10 +5474,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44999</v>
+        <v>45455</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5489,13 +5489,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5538,7 +5533,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 60817-2023</t>
+          <t>A 35792-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5552,10 +5547,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45260</v>
+        <v>45861</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5567,8 +5562,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5611,7 +5611,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 26473-2024</t>
+          <t>A 35971-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45469</v>
+        <v>45863</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5684,7 +5684,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 7955-2024</t>
+          <t>A 48171-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5698,10 +5698,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45350</v>
+        <v>45933</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5757,7 +5757,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 17778-2024</t>
+          <t>A 19454-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45418</v>
+        <v>45429</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5786,13 +5786,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5835,7 +5830,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 16621-2026</t>
+          <t>A 39791-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5849,10 +5844,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46112</v>
+        <v>45891</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5864,13 +5859,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5913,7 +5903,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 42794-2024</t>
+          <t>A 59528-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5927,10 +5917,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45566</v>
+        <v>44907</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5942,8 +5932,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5986,7 +5981,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 48171-2025</t>
+          <t>A 30673-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6000,10 +5995,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45933</v>
+        <v>45112</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6015,8 +6010,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6059,7 +6059,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 8190-2024</t>
+          <t>A 49815-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6073,10 +6073,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45338</v>
+        <v>45940</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6088,13 +6088,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6137,7 +6132,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 8192-2024</t>
+          <t>A 4969-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6151,10 +6146,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45338</v>
+        <v>46049</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6168,11 +6163,11 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6215,7 +6210,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 2190-2022</t>
+          <t>A 1199-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6229,10 +6224,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44578</v>
+        <v>45302</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6246,11 +6241,11 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.9</v>
+        <v>16.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6293,7 +6288,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 39791-2025</t>
+          <t>A 4018-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6307,10 +6302,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45891</v>
+        <v>45323</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6322,8 +6317,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6366,7 +6366,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 10272-2023</t>
+          <t>A 6259-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6380,10 +6380,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44986</v>
+        <v>45337</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6395,13 +6395,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>7.7</v>
+        <v>5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6444,7 +6439,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 61841-2025</t>
+          <t>A 49913-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6454,14 +6449,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46003</v>
+        <v>45940</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6474,7 +6469,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6517,7 +6512,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 55676-2022</t>
+          <t>A 6316-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6531,10 +6526,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44888</v>
+        <v>45338</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6546,8 +6541,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>28.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6590,7 +6590,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 30806-2023</t>
+          <t>A 42794-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6604,10 +6604,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45112</v>
+        <v>45566</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6619,13 +6619,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6668,7 +6663,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 6316-2024</t>
+          <t>A 61970-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6678,14 +6673,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45338</v>
+        <v>46003</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6697,13 +6692,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>28.6</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6746,7 +6736,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 17151-2024</t>
+          <t>A 4188-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6760,10 +6750,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45412</v>
+        <v>45324</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6781,7 +6771,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.6</v>
+        <v>9.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6824,7 +6814,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 4482-2026</t>
+          <t>A 2190-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6838,10 +6828,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46045</v>
+        <v>44578</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6855,11 +6845,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6902,7 +6892,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8455-2024</t>
+          <t>A 53977-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6916,10 +6906,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45354</v>
+        <v>44876</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6931,13 +6921,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6980,7 +6965,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 6852-2026</t>
+          <t>A 12903-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6994,10 +6979,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46057</v>
+        <v>45385</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7009,13 +6994,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>4.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7058,7 +7038,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 12181-2023</t>
+          <t>A 17151-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7072,10 +7052,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44998</v>
+        <v>45412</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7087,8 +7067,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7131,7 +7116,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13159-2024</t>
+          <t>A 6124-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7145,10 +7130,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45386</v>
+        <v>46053</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7161,7 +7146,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7204,7 +7189,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 49913-2025</t>
+          <t>A 30040-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7218,10 +7203,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45940</v>
+        <v>45488</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7234,7 +7219,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7277,7 +7262,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 23310-2022</t>
+          <t>A 16621-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7291,10 +7276,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44720</v>
+        <v>46112</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7308,11 +7293,11 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.3</v>
+        <v>0.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7355,7 +7340,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 21291-2026</t>
+          <t>A 16483-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7369,10 +7354,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46147</v>
+        <v>45408</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7385,7 +7370,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7428,7 +7413,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 21293-2026</t>
+          <t>A 12663-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7442,10 +7427,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46147</v>
+        <v>44641</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7457,8 +7442,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>2.6</v>
+        <v>12.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7501,7 +7491,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 7745-2025</t>
+          <t>A 30806-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7511,14 +7501,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45706</v>
+        <v>45112</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7530,8 +7520,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7574,7 +7569,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 15921-2025</t>
+          <t>A 61841-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7588,10 +7583,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45749</v>
+        <v>46003</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7604,7 +7599,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7647,7 +7642,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 15288-2026</t>
+          <t>A 17316-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7661,10 +7656,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46105</v>
+        <v>45414</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7676,8 +7671,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7720,7 +7720,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 39796-2025</t>
+          <t>A 4482-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7734,10 +7734,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45891</v>
+        <v>46045</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7749,8 +7749,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7793,7 +7798,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 15305-2025</t>
+          <t>A 6852-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7803,14 +7808,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45746</v>
+        <v>46057</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7822,8 +7827,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7866,7 +7876,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 5027-2024</t>
+          <t>A 31993-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7880,10 +7890,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45329</v>
+        <v>45119</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7895,13 +7905,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7944,7 +7949,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 28966-2022</t>
+          <t>A 16568-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7954,14 +7959,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44749</v>
+        <v>45408</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7974,7 +7979,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8017,7 +8022,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 743-2024</t>
+          <t>A 4677-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8031,10 +8036,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45300</v>
+        <v>44952</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8046,13 +8051,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>11.1</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8095,7 +8095,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 578-2024</t>
+          <t>A 21291-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45299</v>
+        <v>46147</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8124,13 +8124,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>67.40000000000001</v>
+        <v>3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8173,7 +8168,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 16611-2026</t>
+          <t>A 21293-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8187,10 +8182,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46112</v>
+        <v>46147</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8202,13 +8197,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8251,7 +8241,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 24002-2026</t>
+          <t>A 11802-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8261,14 +8251,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46167</v>
+        <v>45375</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8280,8 +8270,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8324,7 +8319,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 12988-2024</t>
+          <t>A 11894-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8338,10 +8333,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45385</v>
+        <v>45376</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8359,7 +8354,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>16.2</v>
+        <v>4.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8402,7 +8397,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 49815-2025</t>
+          <t>A 24248-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8416,10 +8411,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45940</v>
+        <v>45457</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8432,7 +8427,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8475,7 +8470,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 53977-2022</t>
+          <t>A 15288-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8489,10 +8484,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44876</v>
+        <v>46105</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8505,7 +8500,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8548,7 +8543,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 4969-2026</t>
+          <t>A 5027-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8562,10 +8557,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46049</v>
+        <v>45329</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8583,7 +8578,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8626,7 +8621,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 15296-2026</t>
+          <t>A 39796-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8640,10 +8635,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46105</v>
+        <v>45891</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8656,7 +8651,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.3</v>
+        <v>3.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8699,7 +8694,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 4677-2023</t>
+          <t>A 16611-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8713,10 +8708,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44952</v>
+        <v>46112</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8728,8 +8723,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8772,7 +8772,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 4018-2024</t>
+          <t>A 12181-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45323</v>
+        <v>44998</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8801,13 +8801,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8850,7 +8845,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 4188-2024</t>
+          <t>A 38562-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8864,10 +8859,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45324</v>
+        <v>45162</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8879,13 +8874,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>9.6</v>
+        <v>2.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8928,7 +8918,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 32955-2026</t>
+          <t>A 17778-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8942,10 +8932,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46244</v>
+        <v>45418</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8957,8 +8947,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9001,7 +8996,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 23621-2026</t>
+          <t>A 24002-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9011,14 +9006,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9031,7 +9026,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9074,7 +9069,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 32948-2026</t>
+          <t>A 44675-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9084,14 +9079,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46244</v>
+        <v>45574</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9103,8 +9098,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.9</v>
+        <v>11.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 15012-2024</t>
+          <t>A 15296-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9161,10 +9161,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45399</v>
+        <v>46105</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>6.9</v>
+        <v>0.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9220,7 +9220,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 2555-2022</t>
+          <t>A 26473-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9234,10 +9234,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44579</v>
+        <v>45469</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9293,7 +9293,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 4651-2024</t>
+          <t>A 51031-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9307,10 +9307,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45328</v>
+        <v>45211</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9366,7 +9366,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 30040-2024</t>
+          <t>A 7745-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9380,10 +9380,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45488</v>
+        <v>45706</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.3</v>
+        <v>0.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9439,7 +9439,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 12663-2022</t>
+          <t>A 5565-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9453,10 +9453,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44641</v>
+        <v>45334</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9468,13 +9468,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>12.4</v>
+        <v>2.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9517,7 +9512,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 24987-2026</t>
+          <t>A 23310-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9531,10 +9526,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46174</v>
+        <v>44720</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9546,8 +9541,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>0.8</v>
+        <v>5.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9590,7 +9590,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 6357-2024</t>
+          <t>A 23621-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9604,10 +9604,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45338</v>
+        <v>46162</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9619,13 +9619,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9668,7 +9663,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 30673-2023</t>
+          <t>A 32955-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9682,10 +9677,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45112</v>
+        <v>46244</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9697,13 +9692,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9746,7 +9736,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 36180-2024</t>
+          <t>A 32948-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9760,10 +9750,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45534</v>
+        <v>46244</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9776,7 +9766,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9819,7 +9809,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 31993-2023</t>
+          <t>A 7955-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9833,10 +9823,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45119</v>
+        <v>45350</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9849,7 +9839,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>6.8</v>
+        <v>2.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9892,7 +9882,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 11894-2024</t>
+          <t>A 24987-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9906,10 +9896,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45376</v>
+        <v>46174</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9921,13 +9911,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9970,7 +9955,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 16483-2024</t>
+          <t>A 55676-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9984,10 +9969,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45408</v>
+        <v>44888</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10000,7 +9985,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10043,7 +10028,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 10908-2026</t>
+          <t>A 31134-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10057,10 +10042,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46079</v>
+        <v>46216</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10072,8 +10057,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10116,7 +10106,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 31134-2026</t>
+          <t>A 8455-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10130,10 +10120,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46216</v>
+        <v>45354</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10151,7 +10141,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10194,7 +10184,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 12903-2024</t>
+          <t>A 10908-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10208,10 +10198,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45385</v>
+        <v>46079</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10224,7 +10214,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>9.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10267,7 +10257,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 15075-2024</t>
+          <t>A 16027-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10277,14 +10267,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45399</v>
+        <v>44665</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10296,8 +10286,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10340,7 +10335,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 11887-2024</t>
+          <t>A 35897-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10354,10 +10349,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45376</v>
+        <v>46266</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10369,13 +10364,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>6.3</v>
+        <v>3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10418,7 +10408,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 35897-2026</t>
+          <t>A 4651-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10432,10 +10422,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46266</v>
+        <v>45328</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10448,7 +10438,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10491,7 +10481,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 5565-2024</t>
+          <t>A 12988-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10505,10 +10495,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45334</v>
+        <v>45385</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10520,8 +10510,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>2.9</v>
+        <v>16.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10564,7 +10559,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 25597-2026</t>
+          <t>A 15305-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10574,14 +10569,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46177</v>
+        <v>45746</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10594,7 +10589,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10637,7 +10632,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 25605-2026</t>
+          <t>A 60817-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10651,10 +10646,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46177</v>
+        <v>45260</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10667,7 +10662,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10710,7 +10705,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 35742-2024</t>
+          <t>A 4023-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10724,10 +10719,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45532</v>
+        <v>45323</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10739,8 +10734,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>15.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10783,7 +10783,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 38074-2026</t>
+          <t>A 12310-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10797,10 +10797,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46280</v>
+        <v>44999</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10812,8 +10812,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10856,7 +10861,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 35715-2024</t>
+          <t>A 25597-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10870,10 +10875,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45532</v>
+        <v>46177</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10886,7 +10891,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10929,7 +10934,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 11806-2025</t>
+          <t>A 25605-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10943,10 +10948,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45727</v>
+        <v>46177</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10959,7 +10964,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11002,7 +11007,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 11810-2025</t>
+          <t>A 15921-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11016,10 +11021,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45727</v>
+        <v>45749</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11032,7 +11037,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11075,7 +11080,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 23185-2025</t>
+          <t>A 35742-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11085,14 +11090,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45791</v>
+        <v>45532</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11105,7 +11110,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11148,7 +11153,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 17760-2025</t>
+          <t>A 35715-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11162,10 +11167,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45758</v>
+        <v>45532</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11178,7 +11183,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11221,7 +11226,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 38787-2024</t>
+          <t>A 38074-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11235,10 +11240,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45547</v>
+        <v>46280</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11251,7 +11256,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11294,7 +11299,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 45729-2024</t>
+          <t>A 11806-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11308,10 +11313,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45579</v>
+        <v>45727</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11324,7 +11329,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>10.1</v>
+        <v>3.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11367,7 +11372,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 11811-2025</t>
+          <t>A 11810-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11384,7 +11389,7 @@
         <v>45727</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11397,7 +11402,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>9.699999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11440,7 +11445,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 35792-2025</t>
+          <t>A 23185-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11450,14 +11455,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45861</v>
+        <v>45791</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11469,13 +11474,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11518,7 +11518,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 35971-2025</t>
+          <t>A 17760-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11532,10 +11532,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45863</v>
+        <v>45758</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11608,7 +11608,7 @@
         <v>45537</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>

--- a/Översikt TOMELILLA.xlsx
+++ b/Översikt TOMELILLA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE137"/>
+  <dimension ref="A1:AE138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45120</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45260</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2018-2024</t>
+          <t>A 14152-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45308</v>
+        <v>45009</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>17.2</v>
+        <v>3.5</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1125,10 +1125,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1140,153 +1140,153 @@
         <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Kråka
+Röd glada</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 14152-2023 artfynd.xlsx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 14152-2023 karta.png", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 14152-2023 georefererad karta.tif", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 14152-2023 FSC-klagomål.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 14152-2023 FSC-klagomål mail.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 14152-2023 tillsynsbegäran.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 14152-2023 tillsynsbegäran mail.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 14152-2023 prioriterade fågelarter.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 2018-2024</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45308</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TOMELILLA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Västlig hakmossa
 Röd glada</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2018-2024 artfynd.xlsx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2018-2024 karta.png", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2018-2024 georefererad karta.tif", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2018-2024 FSC-klagomål.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2018-2024 FSC-klagomål mail.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2018-2024 tillsynsbegäran.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2018-2024 tillsynsbegäran mail.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 2018-2024 prioriterade fågelarter.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 14152-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45009</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>TOMELILLA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Kråka
-Röd glada</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 14152-2023 artfynd.xlsx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 14152-2023 karta.png", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 14152-2023 georefererad karta.tif", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 14152-2023 FSC-klagomål.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 14152-2023 FSC-klagomål mail.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 14152-2023 tillsynsbegäran.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 14152-2023 tillsynsbegäran mail.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 14152-2023 prioriterade fågelarter.docx", "A 14152-2023")</f>
         <v/>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
         <v>45299</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>45429</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45744</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>44613</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>44721</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>45337</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 6261-2024</t>
+          <t>A 2193-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45337</v>
+        <v>44578</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1979,18 +1979,23 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>12.6</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -2004,7 +2009,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2020,42 +2025,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Skogslysing</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2193-2022 artfynd.xlsx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2193-2022 karta.png", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2193-2022 georefererad karta.tif", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2193-2022 FSC-klagomål.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2193-2022 FSC-klagomål mail.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2193-2022 tillsynsbegäran.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2193-2022 tillsynsbegäran mail.docx", "A 2193-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 26958-2025</t>
+          <t>A 6261-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2069,10 +2074,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45811</v>
+        <v>45337</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2085,7 +2090,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.9</v>
+        <v>12.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2121,46 +2126,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26958-2025 artfynd.xlsx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26958-2025 karta.png", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26958-2025 georefererad karta.tif", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26958-2025 FSC-klagomål.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26958-2025 FSC-klagomål mail.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26958-2025 tillsynsbegäran.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26958-2025 tillsynsbegäran mail.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 49813-2025</t>
+          <t>A 26958-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2174,10 +2179,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45940</v>
+        <v>45811</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2190,13 +2195,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2230,42 +2235,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 49813-2025 artfynd.xlsx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26958-2025 artfynd.xlsx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 49813-2025 karta.png", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26958-2025 karta.png", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 49813-2025 georefererad karta.tif", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26958-2025 georefererad karta.tif", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 49813-2025 FSC-klagomål.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26958-2025 FSC-klagomål.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 49813-2025 FSC-klagomål mail.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26958-2025 FSC-klagomål mail.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 49813-2025 tillsynsbegäran.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26958-2025 tillsynsbegäran.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 49813-2025 tillsynsbegäran mail.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26958-2025 tillsynsbegäran mail.docx", "A 26958-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 61314-2025</t>
+          <t>A 6262-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2279,10 +2284,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46000</v>
+        <v>45337</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2295,7 +2300,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2331,46 +2336,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6262-2024 artfynd.xlsx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6262-2024 karta.png", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6262-2024 georefererad karta.tif", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6262-2024 FSC-klagomål.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6262-2024 FSC-klagomål mail.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6262-2024 tillsynsbegäran.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6262-2024 tillsynsbegäran mail.docx", "A 6262-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 2193-2022</t>
+          <t>A 28862-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2384,10 +2389,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44578</v>
+        <v>45104</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2401,20 +2406,20 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>6.6</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2429,7 +2434,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2441,46 +2446,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Skogslysing</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2193-2022 artfynd.xlsx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2193-2022 karta.png", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2193-2022 georefererad karta.tif", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 28862-2023 georefererad karta.tif", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2193-2022 FSC-klagomål.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 28862-2023 FSC-klagomål.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2193-2022 FSC-klagomål mail.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 28862-2023 FSC-klagomål mail.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2193-2022 tillsynsbegäran.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 28862-2023 tillsynsbegäran.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2193-2022 tillsynsbegäran mail.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 28862-2023 tillsynsbegäran mail.docx", "A 28862-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 6262-2024</t>
+          <t>A 32949-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2494,10 +2499,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45337</v>
+        <v>46244</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2510,7 +2515,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2546,39 +2551,43 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6262-2024 artfynd.xlsx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 32949-2026 artfynd.xlsx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6262-2024 karta.png", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 32949-2026 karta.png", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6262-2024 georefererad karta.tif", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 32949-2026 georefererad karta.tif", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6262-2024 FSC-klagomål.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 32949-2026 FSC-klagomål.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6262-2024 FSC-klagomål mail.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 32949-2026 FSC-klagomål mail.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6262-2024 tillsynsbegäran.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 32949-2026 tillsynsbegäran.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6262-2024 tillsynsbegäran mail.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 32949-2026 tillsynsbegäran mail.docx", "A 32949-2026")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 32949-2026 prioriterade fågelarter.docx", "A 32949-2026")</f>
         <v/>
       </c>
     </row>
@@ -2602,7 +2611,7 @@
         <v>45260</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2690,7 +2699,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 28862-2023</t>
+          <t>A 20397-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2704,10 +2713,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45104</v>
+        <v>46139</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2719,13 +2728,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2769,38 +2773,38 @@
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 20397-2026 artfynd.xlsx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 20397-2026 karta.png", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 28862-2023 georefererad karta.tif", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 20397-2026 georefererad karta.tif", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 28862-2023 FSC-klagomål.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 20397-2026 FSC-klagomål.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 28862-2023 FSC-klagomål mail.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 20397-2026 FSC-klagomål mail.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 28862-2023 tillsynsbegäran.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 20397-2026 tillsynsbegäran.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 28862-2023 tillsynsbegäran mail.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 20397-2026 tillsynsbegäran mail.docx", "A 20397-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32949-2026</t>
+          <t>A 42387-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2814,10 +2818,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46244</v>
+        <v>44830</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2830,17 +2834,17 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
@@ -2854,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2870,39 +2874,35 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 32949-2026 artfynd.xlsx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 42387-2022 artfynd.xlsx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 32949-2026 karta.png", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 42387-2022 karta.png", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 32949-2026 georefererad karta.tif", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 42387-2022 georefererad karta.tif", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 32949-2026 FSC-klagomål.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 42387-2022 FSC-klagomål.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 32949-2026 FSC-klagomål mail.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 42387-2022 FSC-klagomål mail.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 32949-2026 tillsynsbegäran.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 42387-2022 tillsynsbegäran.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 32949-2026 tillsynsbegäran mail.docx", "A 32949-2026")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 32949-2026 prioriterade fågelarter.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 42387-2022 tillsynsbegäran mail.docx", "A 42387-2022")</f>
         <v/>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
         <v>45300</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 42387-2022</t>
+          <t>A 26823-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44830</v>
+        <v>46183</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>12.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3089,42 +3089,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 42387-2022 artfynd.xlsx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26823-2026 artfynd.xlsx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 42387-2022 karta.png", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26823-2026 karta.png", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 42387-2022 georefererad karta.tif", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26823-2026 georefererad karta.tif", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 42387-2022 FSC-klagomål.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26823-2026 FSC-klagomål.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 42387-2022 FSC-klagomål mail.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26823-2026 FSC-klagomål mail.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 42387-2022 tillsynsbegäran.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26823-2026 tillsynsbegäran.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 42387-2022 tillsynsbegäran mail.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26823-2026 tillsynsbegäran mail.docx", "A 26823-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 20397-2026</t>
+          <t>A 49813-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3138,10 +3138,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46139</v>
+        <v>45940</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3198,38 +3198,38 @@
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 20397-2026 artfynd.xlsx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 49813-2025 artfynd.xlsx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 20397-2026 karta.png", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 49813-2025 karta.png", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 20397-2026 georefererad karta.tif", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 49813-2025 georefererad karta.tif", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 20397-2026 FSC-klagomål.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 49813-2025 FSC-klagomål.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 20397-2026 FSC-klagomål mail.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 49813-2025 FSC-klagomål mail.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 20397-2026 tillsynsbegäran.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 49813-2025 tillsynsbegäran.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 20397-2026 tillsynsbegäran mail.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 49813-2025 tillsynsbegäran mail.docx", "A 49813-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 26823-2026</t>
+          <t>A 61314-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46183</v>
+        <v>46000</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3259,16 +3259,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>12.1</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3299,35 +3299,35 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26823-2026 artfynd.xlsx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26823-2026 karta.png", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26823-2026 georefererad karta.tif", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26823-2026 FSC-klagomål.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26823-2026 FSC-klagomål mail.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26823-2026 tillsynsbegäran.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26823-2026 tillsynsbegäran mail.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
         <v>45419</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>44684</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44560</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44490</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44642</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44721</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 36180-2024</t>
+          <t>A 4023-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45534</v>
+        <v>45323</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3994,8 +3994,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>15.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4038,7 +4043,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 2548-2024</t>
+          <t>A 47231-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4052,10 +4057,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45313</v>
+        <v>45202</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4068,7 +4073,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4111,7 +4116,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 13159-2024</t>
+          <t>A 11802-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4125,10 +4130,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45386</v>
+        <v>45375</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4140,8 +4145,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4184,7 +4194,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 2555-2022</t>
+          <t>A 19454-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4198,10 +4208,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44579</v>
+        <v>45429</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4214,7 +4224,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4257,7 +4267,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 45729-2024</t>
+          <t>A 23813-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4271,10 +4281,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45579</v>
+        <v>45455</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4287,7 +4297,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>10.1</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4330,7 +4340,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 15075-2024</t>
+          <t>A 24248-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4340,14 +4350,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45399</v>
+        <v>45457</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4360,7 +4370,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4403,7 +4413,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38787-2024</t>
+          <t>A 2548-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4417,10 +4427,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45547</v>
+        <v>45313</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4433,7 +4443,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4476,7 +4486,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 743-2024</t>
+          <t>A 44675-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4486,14 +4496,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45300</v>
+        <v>45574</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4507,11 +4517,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4554,7 +4564,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 11887-2024</t>
+          <t>A 17316-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4568,10 +4578,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45376</v>
+        <v>45414</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4589,7 +4599,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.3</v>
+        <v>4.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4632,7 +4642,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10272-2023</t>
+          <t>A 60817-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4646,10 +4656,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44986</v>
+        <v>45260</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4661,13 +4671,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>7.7</v>
+        <v>4.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4710,7 +4715,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 15012-2024</t>
+          <t>A 7955-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4724,10 +4729,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45399</v>
+        <v>45350</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4740,7 +4745,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>6.9</v>
+        <v>2.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4783,7 +4788,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11811-2025</t>
+          <t>A 42794-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4797,10 +4802,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45727</v>
+        <v>45566</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4813,7 +4818,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>9.699999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4856,7 +4861,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 8190-2024</t>
+          <t>A 16568-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4870,10 +4875,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45338</v>
+        <v>45408</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4885,13 +4890,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 8192-2024</t>
+          <t>A 12310-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4948,10 +4948,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45338</v>
+        <v>44999</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4965,11 +4965,11 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 47231-2023</t>
+          <t>A 2190-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45202</v>
+        <v>44578</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5041,8 +5041,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>4.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5085,7 +5090,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 15158-2025</t>
+          <t>A 10272-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5099,10 +5104,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45744</v>
+        <v>44986</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5114,8 +5119,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>1.8</v>
+        <v>7.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5158,7 +5168,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 28966-2022</t>
+          <t>A 55676-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5168,14 +5178,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44749</v>
+        <v>44888</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5188,7 +5198,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5231,7 +5241,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 43306-2025</t>
+          <t>A 61970-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5241,14 +5251,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45910</v>
+        <v>46003</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5261,7 +5271,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5304,7 +5314,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 578-2024</t>
+          <t>A 30806-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5318,10 +5328,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45299</v>
+        <v>45112</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5339,7 +5349,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>67.40000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5382,7 +5392,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 6357-2024</t>
+          <t>A 6316-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5399,7 +5409,7 @@
         <v>45338</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5413,11 +5423,11 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.6</v>
+        <v>28.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5460,7 +5470,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 23813-2024</t>
+          <t>A 35792-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5474,10 +5484,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45455</v>
+        <v>45861</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5489,8 +5499,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5533,7 +5548,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 35792-2025</t>
+          <t>A 35971-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5547,10 +5562,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45861</v>
+        <v>45863</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5562,13 +5577,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5611,7 +5621,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 35971-2025</t>
+          <t>A 6124-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5625,10 +5635,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45863</v>
+        <v>46053</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5641,7 +5651,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5684,7 +5694,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 48171-2025</t>
+          <t>A 16621-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5698,10 +5708,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45933</v>
+        <v>46112</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5713,8 +5723,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5757,7 +5772,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 19454-2024</t>
+          <t>A 8455-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5771,10 +5786,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45429</v>
+        <v>45354</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5786,8 +5801,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>2.1</v>
+        <v>5.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5830,7 +5850,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 39791-2025</t>
+          <t>A 13159-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5844,10 +5864,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45891</v>
+        <v>45386</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5860,7 +5880,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5903,7 +5923,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 59528-2022</t>
+          <t>A 15158-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5917,10 +5937,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44907</v>
+        <v>45744</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5932,13 +5952,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5981,7 +5996,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 30673-2023</t>
+          <t>A 43306-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5995,10 +6010,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45112</v>
+        <v>45910</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6010,13 +6025,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6059,7 +6069,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 49815-2025</t>
+          <t>A 61841-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6073,10 +6083,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45940</v>
+        <v>46003</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6089,7 +6099,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6132,7 +6142,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 4969-2026</t>
+          <t>A 7745-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6142,14 +6152,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46049</v>
+        <v>45706</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6161,13 +6171,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6210,7 +6215,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1199-2024</t>
+          <t>A 15921-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6224,10 +6229,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45302</v>
+        <v>45749</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6239,13 +6244,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>16.1</v>
+        <v>2.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6288,7 +6288,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 4018-2024</t>
+          <t>A 15305-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6298,14 +6298,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45323</v>
+        <v>45746</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6317,13 +6317,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6366,7 +6361,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 6259-2024</t>
+          <t>A 4482-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6380,10 +6375,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45337</v>
+        <v>46045</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6395,8 +6390,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6439,7 +6439,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 49913-2025</t>
+          <t>A 6852-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6449,14 +6449,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45940</v>
+        <v>46057</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6468,8 +6468,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6512,7 +6517,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 6316-2024</t>
+          <t>A 28966-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6522,14 +6527,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45338</v>
+        <v>44749</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6541,13 +6546,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>28.6</v>
+        <v>3.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6590,7 +6590,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 42794-2024</t>
+          <t>A 578-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6604,10 +6604,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45566</v>
+        <v>45299</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6619,8 +6619,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6663,7 +6668,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 61970-2025</t>
+          <t>A 12988-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6673,14 +6678,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46003</v>
+        <v>45385</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6692,8 +6697,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>16.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6736,7 +6746,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 4188-2024</t>
+          <t>A 21291-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6750,10 +6760,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45324</v>
+        <v>46147</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6765,13 +6775,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>9.6</v>
+        <v>3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6814,7 +6819,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 2190-2022</t>
+          <t>A 21293-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6828,10 +6833,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44578</v>
+        <v>46147</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6843,13 +6848,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6892,7 +6892,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 53977-2022</t>
+          <t>A 48171-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6906,10 +6906,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44876</v>
+        <v>45933</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6965,7 +6965,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 12903-2024</t>
+          <t>A 15288-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6979,10 +6979,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45385</v>
+        <v>46105</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>9.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7038,7 +7038,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 17151-2024</t>
+          <t>A 39796-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7052,10 +7052,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45412</v>
+        <v>45891</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7067,13 +7067,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7116,7 +7111,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 6124-2026</t>
+          <t>A 4677-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7130,10 +7125,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46053</v>
+        <v>44952</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7146,7 +7141,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7189,7 +7184,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 30040-2024</t>
+          <t>A 4018-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7199,14 +7194,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45488</v>
+        <v>45323</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7218,8 +7213,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7262,7 +7262,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 16621-2026</t>
+          <t>A 16611-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7279,7 +7279,7 @@
         <v>46112</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7340,7 +7340,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 16483-2024</t>
+          <t>A 39791-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7354,10 +7354,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45408</v>
+        <v>45891</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7413,7 +7413,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 12663-2022</t>
+          <t>A 15012-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7427,10 +7427,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44641</v>
+        <v>45399</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7442,13 +7442,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>12.4</v>
+        <v>6.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7491,7 +7486,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 30806-2023</t>
+          <t>A 24002-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7501,14 +7496,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45112</v>
+        <v>46167</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7520,13 +7515,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>6.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7569,7 +7559,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 61841-2025</t>
+          <t>A 2555-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7583,10 +7573,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46003</v>
+        <v>44579</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7599,7 +7589,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7642,7 +7632,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 17316-2024</t>
+          <t>A 4651-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7656,10 +7646,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45414</v>
+        <v>45328</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7671,13 +7661,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7720,7 +7705,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 4482-2026</t>
+          <t>A 15296-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7734,10 +7719,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46045</v>
+        <v>46105</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7749,13 +7734,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>6.5</v>
+        <v>0.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7798,7 +7778,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 6852-2026</t>
+          <t>A 30040-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7808,14 +7788,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46057</v>
+        <v>45488</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7827,13 +7807,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7876,7 +7851,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 31993-2023</t>
+          <t>A 6357-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7890,10 +7865,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45119</v>
+        <v>45338</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7905,8 +7880,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>6.8</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7949,7 +7929,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 16568-2024</t>
+          <t>A 30673-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7963,10 +7943,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45408</v>
+        <v>45112</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7978,8 +7958,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8022,7 +8007,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 4677-2023</t>
+          <t>A 32955-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8036,10 +8021,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44952</v>
+        <v>46244</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8052,7 +8037,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8095,7 +8080,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 21291-2026</t>
+          <t>A 31993-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8109,10 +8094,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46147</v>
+        <v>45119</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8125,7 +8110,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8168,7 +8153,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 21293-2026</t>
+          <t>A 23621-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8182,10 +8167,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46147</v>
+        <v>46162</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8198,7 +8183,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8241,7 +8226,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 11802-2024</t>
+          <t>A 11894-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8255,10 +8240,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45375</v>
+        <v>45376</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8276,7 +8261,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8319,7 +8304,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 11894-2024</t>
+          <t>A 32948-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8333,10 +8318,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45376</v>
+        <v>46244</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8348,13 +8333,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8397,7 +8377,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 24248-2024</t>
+          <t>A 16483-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8411,10 +8391,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45457</v>
+        <v>45408</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8427,7 +8407,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8470,7 +8450,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 15288-2026</t>
+          <t>A 24987-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8484,10 +8464,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46105</v>
+        <v>46174</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8500,7 +8480,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8543,7 +8523,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 5027-2024</t>
+          <t>A 38562-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8557,10 +8537,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45329</v>
+        <v>45162</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8572,13 +8552,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8621,7 +8596,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 39796-2025</t>
+          <t>A 51031-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8635,10 +8610,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45891</v>
+        <v>45211</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8651,7 +8626,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8694,7 +8669,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 16611-2026</t>
+          <t>A 59528-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8708,10 +8683,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46112</v>
+        <v>44907</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8725,11 +8700,11 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8772,7 +8747,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 12181-2023</t>
+          <t>A 16027-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8786,10 +8761,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44998</v>
+        <v>44665</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8801,8 +8776,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8845,7 +8825,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 38562-2023</t>
+          <t>A 49913-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8855,14 +8835,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45162</v>
+        <v>45940</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8875,7 +8855,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8918,7 +8898,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 17778-2024</t>
+          <t>A 6259-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8932,10 +8912,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45418</v>
+        <v>45337</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8947,13 +8927,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8996,7 +8971,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 24002-2026</t>
+          <t>A 10908-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9006,14 +8981,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46167</v>
+        <v>46079</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9026,7 +9001,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>6.4</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9069,7 +9044,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 44675-2024</t>
+          <t>A 31134-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9079,14 +9054,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45574</v>
+        <v>46216</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9100,11 +9075,11 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>11.2</v>
+        <v>4.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9147,7 +9122,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 15296-2026</t>
+          <t>A 1199-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9161,10 +9136,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46105</v>
+        <v>45302</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9176,8 +9151,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>0.3</v>
+        <v>16.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9220,7 +9200,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 26473-2024</t>
+          <t>A 35897-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9234,10 +9214,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45469</v>
+        <v>46266</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9250,7 +9230,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9293,7 +9273,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 51031-2023</t>
+          <t>A 26473-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9307,10 +9287,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45211</v>
+        <v>45469</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9323,7 +9303,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9366,7 +9346,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 7745-2025</t>
+          <t>A 17778-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9376,14 +9356,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45706</v>
+        <v>45418</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9395,8 +9375,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9439,7 +9424,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 5565-2024</t>
+          <t>A 8190-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9453,10 +9438,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45334</v>
+        <v>45338</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9468,8 +9453,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9512,7 +9502,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 23310-2022</t>
+          <t>A 8192-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9526,10 +9516,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44720</v>
+        <v>45338</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9543,11 +9533,11 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9590,7 +9580,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 23621-2026</t>
+          <t>A 25597-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9604,10 +9594,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46162</v>
+        <v>46177</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9620,7 +9610,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9663,7 +9653,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 32955-2026</t>
+          <t>A 25605-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9677,10 +9667,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46244</v>
+        <v>46177</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9693,7 +9683,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>6</v>
+        <v>1.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9736,7 +9726,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 32948-2026</t>
+          <t>A 17151-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9750,10 +9740,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46244</v>
+        <v>45412</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9765,8 +9755,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9809,7 +9804,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 7955-2024</t>
+          <t>A 12181-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9823,10 +9818,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45350</v>
+        <v>44998</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9839,7 +9834,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9882,7 +9877,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 24987-2026</t>
+          <t>A 37743-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9896,10 +9891,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46174</v>
+        <v>46279</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9912,7 +9907,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9955,7 +9950,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 55676-2022</t>
+          <t>A 23310-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9969,10 +9964,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44888</v>
+        <v>44720</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9984,8 +9979,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10028,7 +10028,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 31134-2026</t>
+          <t>A 38074-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10042,10 +10042,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46216</v>
+        <v>46280</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10057,13 +10057,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10106,7 +10101,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 8455-2024</t>
+          <t>A 5027-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10120,10 +10115,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45354</v>
+        <v>45329</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10141,7 +10136,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10184,7 +10179,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 10908-2026</t>
+          <t>A 743-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10198,10 +10193,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46079</v>
+        <v>45300</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10213,8 +10208,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>11.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10257,7 +10257,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 16027-2022</t>
+          <t>A 53977-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10271,10 +10271,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44665</v>
+        <v>44876</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10286,13 +10286,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10335,7 +10330,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 35897-2026</t>
+          <t>A 49815-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10349,10 +10344,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46266</v>
+        <v>45940</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10365,7 +10360,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10408,7 +10403,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 4651-2024</t>
+          <t>A 4969-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10422,10 +10417,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45328</v>
+        <v>46049</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10437,8 +10432,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10481,7 +10481,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 12988-2024</t>
+          <t>A 4188-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10495,10 +10495,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45385</v>
+        <v>45324</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>16.2</v>
+        <v>9.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10559,7 +10559,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 15305-2025</t>
+          <t>A 12663-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10569,14 +10569,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45746</v>
+        <v>44641</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10588,8 +10588,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>0.6</v>
+        <v>12.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10632,7 +10637,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 60817-2023</t>
+          <t>A 36180-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10646,10 +10651,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45260</v>
+        <v>45534</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10662,7 +10667,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>4.3</v>
+        <v>1.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10705,7 +10710,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 4023-2024</t>
+          <t>A 12903-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10719,10 +10724,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45323</v>
+        <v>45385</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10734,13 +10739,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>15.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10783,7 +10783,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 12310-2023</t>
+          <t>A 15075-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10793,14 +10793,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44999</v>
+        <v>45399</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10812,13 +10812,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10861,7 +10856,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 25597-2026</t>
+          <t>A 11887-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10875,10 +10870,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46177</v>
+        <v>45376</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10890,8 +10885,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>2.5</v>
+        <v>6.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10934,7 +10934,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 25605-2026</t>
+          <t>A 5565-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10948,10 +10948,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46177</v>
+        <v>45334</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11007,7 +11007,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 15921-2025</t>
+          <t>A 35742-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11021,10 +11021,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45749</v>
+        <v>45532</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11080,7 +11080,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 35742-2024</t>
+          <t>A 35715-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11097,7 +11097,7 @@
         <v>45532</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11153,7 +11153,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 35715-2024</t>
+          <t>A 11806-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11167,10 +11167,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45532</v>
+        <v>45727</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11226,7 +11226,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 38074-2026</t>
+          <t>A 11810-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11240,10 +11240,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46280</v>
+        <v>45727</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11299,7 +11299,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 11806-2025</t>
+          <t>A 23185-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11309,14 +11309,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45727</v>
+        <v>45791</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11372,7 +11372,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 11810-2025</t>
+          <t>A 17760-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11386,10 +11386,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45727</v>
+        <v>45758</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11445,7 +11445,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 23185-2025</t>
+          <t>A 38787-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11455,14 +11455,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45791</v>
+        <v>45547</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11518,7 +11518,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 17760-2025</t>
+          <t>A 45729-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11532,10 +11532,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45758</v>
+        <v>45579</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>3.7</v>
+        <v>10.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11588,83 +11588,156 @@
       </c>
       <c r="V136" s="2" t="inlineStr"/>
     </row>
-    <row r="137">
+    <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
+          <t>A 11811-2025</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D137" s="1" t="n">
+        <v>45727</v>
+      </c>
+      <c r="E137" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>TOMELILLA</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
           <t>S 3422-2024</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D137" s="1" t="n">
+      <c r="D138" s="1" t="n">
         <v>45537</v>
       </c>
-      <c r="E137" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>TOMELILLA</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
+      <c r="E138" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>TOMELILLA</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I137" t="n">
+      <c r="I138" t="n">
         <v>0.1</v>
       </c>
-      <c r="J137" t="n">
-        <v>0</v>
-      </c>
-      <c r="K137" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" t="n">
-        <v>0</v>
-      </c>
-      <c r="M137" t="n">
-        <v>0</v>
-      </c>
-      <c r="N137" t="n">
-        <v>0</v>
-      </c>
-      <c r="O137" t="n">
-        <v>0</v>
-      </c>
-      <c r="P137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
-      <c r="R137" t="n">
-        <v>0</v>
-      </c>
-      <c r="S137" t="n">
-        <v>0</v>
-      </c>
-      <c r="T137" t="n">
-        <v>0</v>
-      </c>
-      <c r="U137" t="n">
-        <v>0</v>
-      </c>
-      <c r="V137" s="2" t="inlineStr"/>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0</v>
+      </c>
+      <c r="V138" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TOMELILLA.xlsx
+++ b/Översikt TOMELILLA.xlsx
@@ -601,7 +601,7 @@
         <v>44756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45120</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45260</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 14152-2023</t>
+          <t>A 2018-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45009</v>
+        <v>45308</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.5</v>
+        <v>17.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1125,10 +1125,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1140,153 +1140,153 @@
         <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Västlig hakmossa
+Röd glada</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2018-2024 artfynd.xlsx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2018-2024 karta.png", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2018-2024 georefererad karta.tif", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2018-2024 FSC-klagomål.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2018-2024 FSC-klagomål mail.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2018-2024 tillsynsbegäran.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2018-2024 tillsynsbegäran mail.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 2018-2024 prioriterade fågelarter.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 14152-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45009</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TOMELILLA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Kråka
 Röd glada</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 14152-2023 artfynd.xlsx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 14152-2023 karta.png", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 14152-2023 georefererad karta.tif", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 14152-2023 FSC-klagomål.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 14152-2023 FSC-klagomål mail.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 14152-2023 tillsynsbegäran.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 14152-2023 tillsynsbegäran mail.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 14152-2023 prioriterade fågelarter.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 2018-2024</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45308</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>TOMELILLA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Västlig hakmossa
-Röd glada</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2018-2024 artfynd.xlsx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2018-2024 karta.png", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2018-2024 georefererad karta.tif", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2018-2024 FSC-klagomål.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2018-2024 FSC-klagomål mail.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2018-2024 tillsynsbegäran.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2018-2024 tillsynsbegäran mail.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 2018-2024 prioriterade fågelarter.docx", "A 2018-2024")</f>
         <v/>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
         <v>45299</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>45429</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45744</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>44613</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>44721</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>45337</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>44578</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 6261-2024</t>
+          <t>A 6262-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2077,7 +2077,7 @@
         <v>45337</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>12.6</v>
+        <v>4.5</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2130,42 +2130,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6262-2024 artfynd.xlsx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6262-2024 karta.png", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6262-2024 georefererad karta.tif", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6262-2024 FSC-klagomål.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6262-2024 FSC-klagomål mail.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6262-2024 tillsynsbegäran.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6262-2024 tillsynsbegäran mail.docx", "A 6262-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 26958-2025</t>
+          <t>A 49813-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45811</v>
+        <v>45940</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2235,42 +2235,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26958-2025 artfynd.xlsx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 49813-2025 artfynd.xlsx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26958-2025 karta.png", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 49813-2025 karta.png", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26958-2025 georefererad karta.tif", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 49813-2025 georefererad karta.tif", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26958-2025 FSC-klagomål.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 49813-2025 FSC-klagomål.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26958-2025 FSC-klagomål mail.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 49813-2025 FSC-klagomål mail.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26958-2025 tillsynsbegäran.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 49813-2025 tillsynsbegäran.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26958-2025 tillsynsbegäran mail.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 49813-2025 tillsynsbegäran mail.docx", "A 49813-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6262-2024</t>
+          <t>A 60820-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45337</v>
+        <v>45260</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2300,13 +2300,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2336,46 +2336,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6262-2024 artfynd.xlsx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 60820-2023 artfynd.xlsx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6262-2024 karta.png", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 60820-2023 karta.png", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6262-2024 georefererad karta.tif", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 60820-2023 georefererad karta.tif", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6262-2024 FSC-klagomål.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 60820-2023 FSC-klagomål.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6262-2024 FSC-klagomål mail.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 60820-2023 FSC-klagomål mail.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6262-2024 tillsynsbegäran.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 60820-2023 tillsynsbegäran.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6262-2024 tillsynsbegäran mail.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 60820-2023 tillsynsbegäran mail.docx", "A 60820-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 28862-2023</t>
+          <t>A 61314-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2389,10 +2389,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45104</v>
+        <v>46000</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2404,13 +2404,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>6.6</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2450,42 +2445,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 28862-2023 georefererad karta.tif", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 28862-2023 FSC-klagomål.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 28862-2023 FSC-klagomål mail.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 28862-2023 tillsynsbegäran.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 28862-2023 tillsynsbegäran mail.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 32949-2026</t>
+          <t>A 28862-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2499,10 +2494,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46244</v>
+        <v>45104</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2514,8 +2509,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2555,46 +2555,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 32949-2026 artfynd.xlsx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 32949-2026 karta.png", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 32949-2026 georefererad karta.tif", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 28862-2023 georefererad karta.tif", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 32949-2026 FSC-klagomål.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 28862-2023 FSC-klagomål.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 32949-2026 FSC-klagomål mail.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 28862-2023 FSC-klagomål mail.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 32949-2026 tillsynsbegäran.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 28862-2023 tillsynsbegäran.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 32949-2026 tillsynsbegäran mail.docx", "A 32949-2026")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 32949-2026 prioriterade fågelarter.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 28862-2023 tillsynsbegäran mail.docx", "A 28862-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 60820-2023</t>
+          <t>A 756-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2608,10 +2604,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45260</v>
+        <v>45300</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2623,18 +2619,23 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>4.6</v>
+        <v>13.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
@@ -2648,7 +2649,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2664,42 +2665,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 60820-2023 artfynd.xlsx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 756-2024 artfynd.xlsx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 60820-2023 karta.png", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 756-2024 karta.png", "A 756-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 60820-2023 georefererad karta.tif", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 756-2024 georefererad karta.tif", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 60820-2023 FSC-klagomål.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 756-2024 FSC-klagomål.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 60820-2023 FSC-klagomål mail.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 756-2024 FSC-klagomål mail.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 60820-2023 tillsynsbegäran.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 756-2024 tillsynsbegäran.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 60820-2023 tillsynsbegäran mail.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 756-2024 tillsynsbegäran mail.docx", "A 756-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 20397-2026</t>
+          <t>A 32949-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2713,10 +2714,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46139</v>
+        <v>46244</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2729,7 +2730,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2769,35 +2770,39 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 20397-2026 artfynd.xlsx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 32949-2026 artfynd.xlsx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 20397-2026 karta.png", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 32949-2026 karta.png", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 20397-2026 georefererad karta.tif", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 32949-2026 georefererad karta.tif", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 20397-2026 FSC-klagomål.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 32949-2026 FSC-klagomål.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 20397-2026 FSC-klagomål mail.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 32949-2026 FSC-klagomål mail.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 20397-2026 tillsynsbegäran.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 32949-2026 tillsynsbegäran.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 20397-2026 tillsynsbegäran mail.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 32949-2026 tillsynsbegäran mail.docx", "A 32949-2026")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 32949-2026 prioriterade fågelarter.docx", "A 32949-2026")</f>
         <v/>
       </c>
     </row>
@@ -2821,7 +2826,7 @@
         <v>44830</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2909,7 +2914,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 756-2024</t>
+          <t>A 20397-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2923,10 +2928,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45300</v>
+        <v>46139</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2938,22 +2943,17 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>13.1</v>
+        <v>4.2</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2984,42 +2984,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 756-2024 artfynd.xlsx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 20397-2026 artfynd.xlsx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 756-2024 karta.png", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 20397-2026 karta.png", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 756-2024 georefererad karta.tif", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 20397-2026 georefererad karta.tif", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 756-2024 FSC-klagomål.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 20397-2026 FSC-klagomål.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 756-2024 FSC-klagomål mail.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 20397-2026 FSC-klagomål mail.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 756-2024 tillsynsbegäran.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 20397-2026 tillsynsbegäran.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 756-2024 tillsynsbegäran mail.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 20397-2026 tillsynsbegäran mail.docx", "A 20397-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 26823-2026</t>
+          <t>A 17907-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46183</v>
+        <v>45419</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>12.1</v>
+        <v>3.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3058,7 +3058,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3073,7 +3073,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3085,46 +3085,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Gulplister</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26823-2026 artfynd.xlsx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 17907-2024 artfynd.xlsx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26823-2026 karta.png", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 17907-2024 karta.png", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26823-2026 georefererad karta.tif", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 17907-2024 georefererad karta.tif", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26823-2026 FSC-klagomål.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 17907-2024 FSC-klagomål.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26823-2026 FSC-klagomål mail.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 17907-2024 FSC-klagomål mail.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26823-2026 tillsynsbegäran.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 17907-2024 tillsynsbegäran.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26823-2026 tillsynsbegäran mail.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 17907-2024 tillsynsbegäran mail.docx", "A 17907-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 49813-2025</t>
+          <t>A 26823-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3138,10 +3138,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45940</v>
+        <v>46183</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3154,17 +3154,17 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.5</v>
+        <v>12.1</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
@@ -3178,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3194,42 +3194,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 49813-2025 artfynd.xlsx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26823-2026 artfynd.xlsx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 49813-2025 karta.png", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26823-2026 karta.png", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 49813-2025 georefererad karta.tif", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26823-2026 georefererad karta.tif", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 49813-2025 FSC-klagomål.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26823-2026 FSC-klagomål.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 49813-2025 FSC-klagomål mail.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26823-2026 FSC-klagomål mail.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 49813-2025 tillsynsbegäran.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26823-2026 tillsynsbegäran.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 49813-2025 tillsynsbegäran mail.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26823-2026 tillsynsbegäran mail.docx", "A 26823-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 61314-2025</t>
+          <t>A 6261-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46000</v>
+        <v>45337</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3259,13 +3259,13 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>12.6</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3295,46 +3295,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 17907-2024</t>
+          <t>A 26958-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45419</v>
+        <v>45811</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3364,13 +3364,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3400,39 +3400,39 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Gulplister</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 17907-2024 artfynd.xlsx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26958-2025 artfynd.xlsx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 17907-2024 karta.png", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26958-2025 karta.png", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 17907-2024 georefererad karta.tif", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26958-2025 georefererad karta.tif", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 17907-2024 FSC-klagomål.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26958-2025 FSC-klagomål.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 17907-2024 FSC-klagomål mail.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26958-2025 FSC-klagomål mail.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 17907-2024 tillsynsbegäran.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26958-2025 tillsynsbegäran.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 17907-2024 tillsynsbegäran mail.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26958-2025 tillsynsbegäran mail.docx", "A 26958-2025")</f>
         <v/>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
         <v>44684</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44560</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44490</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44642</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44721</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 4023-2024</t>
+          <t>A 36180-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45323</v>
+        <v>45534</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3994,13 +3994,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>15.2</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4043,7 +4038,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 47231-2023</t>
+          <t>A 2548-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4057,10 +4052,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45202</v>
+        <v>45313</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4073,7 +4068,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4116,7 +4111,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 11802-2024</t>
+          <t>A 13159-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4130,10 +4125,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45375</v>
+        <v>45386</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4145,13 +4140,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4194,7 +4184,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 19454-2024</t>
+          <t>A 2555-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4208,10 +4198,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45429</v>
+        <v>44579</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4224,7 +4214,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4267,7 +4257,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 23813-2024</t>
+          <t>A 743-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4281,10 +4271,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45455</v>
+        <v>45300</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4296,8 +4286,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>11.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4340,7 +4335,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 24248-2024</t>
+          <t>A 15075-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4350,14 +4345,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45457</v>
+        <v>45399</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4370,7 +4365,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4413,7 +4408,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2548-2024</t>
+          <t>A 11887-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4427,10 +4422,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45313</v>
+        <v>45376</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4442,8 +4437,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>6.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4486,7 +4486,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 44675-2024</t>
+          <t>A 10272-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4496,14 +4496,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45574</v>
+        <v>44986</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4517,11 +4517,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>11.2</v>
+        <v>7.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4564,7 +4564,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 17316-2024</t>
+          <t>A 15012-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4578,10 +4578,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45414</v>
+        <v>45399</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4593,13 +4593,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>4.3</v>
+        <v>6.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4642,7 +4637,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60817-2023</t>
+          <t>A 47231-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4656,10 +4651,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45260</v>
+        <v>45202</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4672,7 +4667,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4715,7 +4710,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 7955-2024</t>
+          <t>A 8190-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4729,10 +4724,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45350</v>
+        <v>45338</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4744,8 +4739,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 42794-2024</t>
+          <t>A 8192-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4802,10 +4802,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45566</v>
+        <v>45338</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4817,8 +4817,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4861,7 +4866,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 16568-2024</t>
+          <t>A 28966-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4871,14 +4876,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45408</v>
+        <v>44749</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4891,7 +4896,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4934,7 +4939,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 12310-2023</t>
+          <t>A 578-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4948,10 +4953,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44999</v>
+        <v>45299</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4965,11 +4970,11 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5012,7 +5017,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2190-2022</t>
+          <t>A 6357-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5026,10 +5031,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44578</v>
+        <v>45338</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5043,11 +5048,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.9</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5090,7 +5095,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 10272-2023</t>
+          <t>A 23813-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5104,10 +5109,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44986</v>
+        <v>45455</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5119,13 +5124,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>7.7</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5168,7 +5168,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 55676-2022</t>
+          <t>A 19454-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5182,10 +5182,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44888</v>
+        <v>45429</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5241,7 +5241,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 61970-2025</t>
+          <t>A 59528-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5251,14 +5251,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46003</v>
+        <v>44907</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5270,8 +5270,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5314,7 +5319,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30806-2023</t>
+          <t>A 1199-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5328,10 +5333,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45112</v>
+        <v>45302</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5349,7 +5354,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>16.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5392,7 +5397,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 6316-2024</t>
+          <t>A 30673-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5406,10 +5411,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45338</v>
+        <v>45112</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5427,7 +5432,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>28.6</v>
+        <v>2.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5470,7 +5475,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 35792-2025</t>
+          <t>A 4018-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5484,10 +5489,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45861</v>
+        <v>45323</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5505,7 +5510,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5548,7 +5553,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 35971-2025</t>
+          <t>A 61841-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5562,10 +5567,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45863</v>
+        <v>46003</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5578,7 +5583,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5621,7 +5626,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 6124-2026</t>
+          <t>A 4482-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5635,10 +5640,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46053</v>
+        <v>46045</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5650,8 +5655,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>6.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5694,7 +5704,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16621-2026</t>
+          <t>A 6259-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5708,10 +5718,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46112</v>
+        <v>45337</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5723,13 +5733,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5772,7 +5777,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8455-2024</t>
+          <t>A 6316-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5786,10 +5791,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45354</v>
+        <v>45338</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5807,7 +5812,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.1</v>
+        <v>28.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5850,7 +5855,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 13159-2024</t>
+          <t>A 42794-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5864,10 +5869,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45386</v>
+        <v>45566</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5880,7 +5885,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5940,7 +5945,7 @@
         <v>45744</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5996,7 +6001,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 43306-2025</t>
+          <t>A 6852-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6010,10 +6015,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45910</v>
+        <v>46057</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6025,8 +6030,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6069,7 +6079,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 61841-2025</t>
+          <t>A 43306-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6083,10 +6093,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46003</v>
+        <v>45910</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6099,7 +6109,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6142,7 +6152,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 7745-2025</t>
+          <t>A 4188-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6152,14 +6162,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45706</v>
+        <v>45324</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6171,8 +6181,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>9.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6215,7 +6230,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 15921-2025</t>
+          <t>A 2190-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6229,10 +6244,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45749</v>
+        <v>44578</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6244,8 +6259,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6288,7 +6308,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 15305-2025</t>
+          <t>A 53977-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6298,14 +6318,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45746</v>
+        <v>44876</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6318,7 +6338,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6361,7 +6381,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 4482-2026</t>
+          <t>A 12903-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6375,10 +6395,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46045</v>
+        <v>45385</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6390,13 +6410,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>6.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6439,7 +6454,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 6852-2026</t>
+          <t>A 17151-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6453,10 +6468,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46057</v>
+        <v>45412</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6474,7 +6489,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6517,7 +6532,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 28966-2022</t>
+          <t>A 48171-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6527,14 +6542,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44749</v>
+        <v>45933</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6547,7 +6562,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6590,7 +6605,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 578-2024</t>
+          <t>A 30040-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6600,14 +6615,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45299</v>
+        <v>45488</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6619,13 +6634,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>67.40000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6668,7 +6678,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 12988-2024</t>
+          <t>A 21291-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6682,10 +6692,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45385</v>
+        <v>46147</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6697,13 +6707,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>16.2</v>
+        <v>3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6746,7 +6751,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 21291-2026</t>
+          <t>A 21293-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6763,7 +6768,7 @@
         <v>46147</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6776,7 +6781,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6819,7 +6824,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 21293-2026</t>
+          <t>A 39791-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6833,10 +6838,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46147</v>
+        <v>45891</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6849,7 +6854,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6892,7 +6897,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 48171-2025</t>
+          <t>A 16483-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6906,10 +6911,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45933</v>
+        <v>45408</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6922,7 +6927,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6965,7 +6970,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 15288-2026</t>
+          <t>A 12663-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6979,10 +6984,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46105</v>
+        <v>44641</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6994,8 +6999,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>4.8</v>
+        <v>12.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7038,7 +7048,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 39796-2025</t>
+          <t>A 30806-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7052,10 +7062,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45891</v>
+        <v>45112</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7067,8 +7077,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7111,7 +7126,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 4677-2023</t>
+          <t>A 17316-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7125,10 +7140,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44952</v>
+        <v>45414</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7140,8 +7155,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7184,7 +7204,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 4018-2024</t>
+          <t>A 15288-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7198,10 +7218,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45323</v>
+        <v>46105</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7213,13 +7233,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7262,7 +7277,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 16611-2026</t>
+          <t>A 49913-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7272,14 +7287,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46112</v>
+        <v>45940</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7291,13 +7306,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7340,7 +7350,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 39791-2025</t>
+          <t>A 39796-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7357,7 +7367,7 @@
         <v>45891</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7370,7 +7380,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7413,7 +7423,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 15012-2024</t>
+          <t>A 31993-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7427,10 +7437,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45399</v>
+        <v>45119</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7443,7 +7453,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7486,7 +7496,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 24002-2026</t>
+          <t>A 16568-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7496,14 +7506,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46167</v>
+        <v>45408</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7516,7 +7526,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>6.4</v>
+        <v>0.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7559,7 +7569,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 2555-2022</t>
+          <t>A 4677-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7573,10 +7583,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44579</v>
+        <v>44952</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7589,7 +7599,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7632,7 +7642,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 4651-2024</t>
+          <t>A 11802-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7646,10 +7656,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45328</v>
+        <v>45375</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7661,8 +7671,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>4.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7705,7 +7720,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 15296-2026</t>
+          <t>A 11894-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7719,10 +7734,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46105</v>
+        <v>45376</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7734,8 +7749,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>0.3</v>
+        <v>4.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7778,7 +7798,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 30040-2024</t>
+          <t>A 24248-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7788,14 +7808,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45488</v>
+        <v>45457</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7808,7 +7828,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.3</v>
+        <v>2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7851,7 +7871,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 6357-2024</t>
+          <t>A 16611-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7865,10 +7885,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45338</v>
+        <v>46112</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7882,11 +7902,11 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7929,7 +7949,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 30673-2023</t>
+          <t>A 5027-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7943,10 +7963,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45112</v>
+        <v>45329</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7964,7 +7984,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8007,7 +8027,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 32955-2026</t>
+          <t>A 49815-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8021,10 +8041,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46244</v>
+        <v>45940</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8037,7 +8057,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8080,7 +8100,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 31993-2023</t>
+          <t>A 24002-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8090,14 +8110,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45119</v>
+        <v>46167</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8110,7 +8130,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8153,7 +8173,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 23621-2026</t>
+          <t>A 12181-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8167,10 +8187,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46162</v>
+        <v>44998</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8183,7 +8203,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8226,7 +8246,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 11894-2024</t>
+          <t>A 15296-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8240,10 +8260,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45376</v>
+        <v>46105</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8255,13 +8275,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>4.4</v>
+        <v>0.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8304,7 +8319,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 32948-2026</t>
+          <t>A 4969-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8318,10 +8333,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46244</v>
+        <v>46049</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8333,8 +8348,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8377,7 +8397,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 16483-2024</t>
+          <t>A 38562-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8391,10 +8411,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45408</v>
+        <v>45162</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8407,7 +8427,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8450,7 +8470,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 24987-2026</t>
+          <t>A 17778-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8464,10 +8484,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46174</v>
+        <v>45418</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8479,8 +8499,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8523,7 +8548,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 38562-2023</t>
+          <t>A 44675-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8533,14 +8558,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45162</v>
+        <v>45574</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8552,8 +8577,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>2.2</v>
+        <v>11.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8596,7 +8626,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 51031-2023</t>
+          <t>A 26473-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8610,10 +8640,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45211</v>
+        <v>45469</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8626,7 +8656,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8669,7 +8699,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 59528-2022</t>
+          <t>A 51031-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8683,10 +8713,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44907</v>
+        <v>45211</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8698,13 +8728,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8747,7 +8772,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 16027-2022</t>
+          <t>A 7745-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8757,14 +8782,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44665</v>
+        <v>45706</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8776,13 +8801,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8825,7 +8845,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 49913-2025</t>
+          <t>A 61970-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8839,10 +8859,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45940</v>
+        <v>46003</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8855,7 +8875,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8898,7 +8918,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 6259-2024</t>
+          <t>A 5565-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8912,10 +8932,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45337</v>
+        <v>45334</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8928,7 +8948,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8971,7 +8991,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 10908-2026</t>
+          <t>A 23310-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8985,10 +9005,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46079</v>
+        <v>44720</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9000,8 +9020,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9044,7 +9069,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 31134-2026</t>
+          <t>A 6124-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9058,10 +9083,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46216</v>
+        <v>46053</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9073,13 +9098,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9122,7 +9142,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 1199-2024</t>
+          <t>A 23621-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9136,10 +9156,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45302</v>
+        <v>46162</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9151,13 +9171,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>16.1</v>
+        <v>3.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9200,7 +9215,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 35897-2026</t>
+          <t>A 16621-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9214,10 +9229,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46266</v>
+        <v>46112</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9229,8 +9244,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9273,7 +9293,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 26473-2024</t>
+          <t>A 7955-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9287,10 +9307,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45469</v>
+        <v>45350</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9303,7 +9323,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9346,7 +9366,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 17778-2024</t>
+          <t>A 32955-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9360,10 +9380,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45418</v>
+        <v>46244</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9375,13 +9395,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9424,7 +9439,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 8190-2024</t>
+          <t>A 32948-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9438,10 +9453,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45338</v>
+        <v>46244</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9453,13 +9468,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9502,7 +9512,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 8192-2024</t>
+          <t>A 55676-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9516,10 +9526,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45338</v>
+        <v>44888</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9531,13 +9541,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9580,7 +9585,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 25597-2026</t>
+          <t>A 8455-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9594,10 +9599,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46177</v>
+        <v>45354</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9609,8 +9614,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9653,7 +9663,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 25605-2026</t>
+          <t>A 24987-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9667,10 +9677,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46177</v>
+        <v>46174</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9683,7 +9693,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9726,7 +9736,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 17151-2024</t>
+          <t>A 16027-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9740,10 +9750,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45412</v>
+        <v>44665</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9761,7 +9771,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9804,7 +9814,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 12181-2023</t>
+          <t>A 4651-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9818,10 +9828,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44998</v>
+        <v>45328</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9834,7 +9844,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9877,7 +9887,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 37743-2026</t>
+          <t>A 12988-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9891,10 +9901,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46279</v>
+        <v>45385</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9906,8 +9916,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>1.2</v>
+        <v>16.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9950,7 +9965,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 23310-2022</t>
+          <t>A 15305-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9960,14 +9975,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44720</v>
+        <v>45746</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9979,13 +9994,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10028,7 +10038,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 38074-2026</t>
+          <t>A 60817-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10042,10 +10052,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46280</v>
+        <v>45260</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10058,7 +10068,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10101,7 +10111,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 5027-2024</t>
+          <t>A 31134-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10115,10 +10125,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45329</v>
+        <v>46216</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10136,7 +10146,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10179,7 +10189,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 743-2024</t>
+          <t>A 4023-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10193,10 +10203,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45300</v>
+        <v>45323</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10214,7 +10224,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>11.1</v>
+        <v>15.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10257,7 +10267,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 53977-2022</t>
+          <t>A 10908-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10271,10 +10281,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44876</v>
+        <v>46079</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10287,7 +10297,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10330,7 +10340,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 49815-2025</t>
+          <t>A 35897-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10344,10 +10354,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45940</v>
+        <v>46266</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10360,7 +10370,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10403,7 +10413,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 4969-2026</t>
+          <t>A 12310-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10417,10 +10427,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46049</v>
+        <v>44999</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10434,11 +10444,11 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10481,7 +10491,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 4188-2024</t>
+          <t>A 15921-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10495,10 +10505,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45324</v>
+        <v>45749</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10510,13 +10520,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>9.6</v>
+        <v>2.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10559,7 +10564,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 12663-2022</t>
+          <t>A 35742-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10573,10 +10578,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44641</v>
+        <v>45532</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10588,13 +10593,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>12.4</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10637,7 +10637,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 36180-2024</t>
+          <t>A 35715-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10651,10 +10651,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45534</v>
+        <v>45532</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10710,7 +10710,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 12903-2024</t>
+          <t>A 11806-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10724,10 +10724,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45385</v>
+        <v>45727</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>9.199999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10783,7 +10783,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 15075-2024</t>
+          <t>A 11810-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10793,14 +10793,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45399</v>
+        <v>45727</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10856,7 +10856,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 11887-2024</t>
+          <t>A 25597-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10870,10 +10870,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45376</v>
+        <v>46177</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10885,13 +10885,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>6.3</v>
+        <v>2.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10934,7 +10929,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 5565-2024</t>
+          <t>A 25605-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10948,10 +10943,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45334</v>
+        <v>46177</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10964,7 +10959,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11007,7 +11002,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 35742-2024</t>
+          <t>A 23185-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11017,14 +11012,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45532</v>
+        <v>45791</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11037,7 +11032,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11080,7 +11075,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 35715-2024</t>
+          <t>A 38074-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11094,10 +11089,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45532</v>
+        <v>46280</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11110,7 +11105,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11153,7 +11148,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 11806-2025</t>
+          <t>A 17760-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11167,10 +11162,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45727</v>
+        <v>45758</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11183,7 +11178,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11226,7 +11221,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 11810-2025</t>
+          <t>A 37743-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11240,10 +11235,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45727</v>
+        <v>46279</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11256,7 +11251,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11299,7 +11294,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 23185-2025</t>
+          <t>A 45729-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11309,14 +11304,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45791</v>
+        <v>45579</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11329,7 +11324,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.8</v>
+        <v>10.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11372,7 +11367,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 17760-2025</t>
+          <t>A 38787-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11386,10 +11381,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45758</v>
+        <v>45547</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11402,7 +11397,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11445,7 +11440,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 38787-2024</t>
+          <t>A 11811-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11459,10 +11454,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45547</v>
+        <v>45727</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11475,7 +11470,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11518,7 +11513,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 45729-2024</t>
+          <t>A 35792-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11532,10 +11527,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45579</v>
+        <v>45861</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11547,8 +11542,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>10.1</v>
+        <v>1.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11591,7 +11591,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 11811-2025</t>
+          <t>A 35971-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11605,10 +11605,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45727</v>
+        <v>45863</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>9.699999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11681,7 +11681,7 @@
         <v>45537</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>

--- a/Översikt TOMELILLA.xlsx
+++ b/Översikt TOMELILLA.xlsx
@@ -601,7 +601,7 @@
         <v>44756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45120</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45260</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>45308</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>45009</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45299</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>45429</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45744</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>44613</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>44721</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>45337</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>44578</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>45337</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>45940</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>45260</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>46000</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45104</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>45300</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>46244</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>44830</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>46139</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45419</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>46183</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>45337</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45811</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>44684</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44560</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44490</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44642</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44721</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>45534</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>45313</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>45386</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44579</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>45300</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>45399</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>45376</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>44986</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>45399</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>45202</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>45338</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45338</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>44749</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>45299</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>45338</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>45455</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>45429</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>44907</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>45302</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>45112</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>45323</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>46003</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>46045</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>45337</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>45338</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>45566</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>45744</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>46057</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>45910</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>45324</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>44578</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>44876</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>45385</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>45412</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>45933</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>45488</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>46147</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>46147</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>45891</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>45408</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>44641</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>45112</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>45414</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>46105</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>45940</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>45891</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>45119</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>45408</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>44952</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>45375</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>45376</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>45457</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>46112</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>45329</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         <v>45940</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>46167</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>44998</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>46105</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>46049</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>45162</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>45418</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>45574</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>45469</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         <v>45211</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>45706</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>46003</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>45334</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>44720</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>46053</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>46162</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>46112</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>45350</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>46244</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>46244</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>44888</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>45354</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>46174</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>44665</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>45328</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>45385</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>45746</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>45260</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>46216</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>45323</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>46079</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>46266</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>44999</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>45749</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>45532</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>45532</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>45727</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>45727</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>46177</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>46177</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>45791</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>46280</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>45758</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>46279</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>45579</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>45547</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>45727</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>45861</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>45863</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>45537</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>

--- a/Översikt TOMELILLA.xlsx
+++ b/Översikt TOMELILLA.xlsx
@@ -601,7 +601,7 @@
         <v>44756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45120</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45260</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>45308</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>45009</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45299</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>45429</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45744</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>44613</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>44721</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>45337</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>44578</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>45337</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>45940</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 60820-2023</t>
+          <t>A 61314-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45260</v>
+        <v>46000</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2300,13 +2300,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2340,42 +2340,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 60820-2023 artfynd.xlsx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 60820-2023 karta.png", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 60820-2023 georefererad karta.tif", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 60820-2023 FSC-klagomål.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 60820-2023 FSC-klagomål mail.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 60820-2023 tillsynsbegäran.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 60820-2023 tillsynsbegäran mail.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 61314-2025</t>
+          <t>A 60820-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2389,10 +2389,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46000</v>
+        <v>45260</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2445,35 +2445,35 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 60820-2023 artfynd.xlsx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 60820-2023 karta.png", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 60820-2023 georefererad karta.tif", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 60820-2023 FSC-klagomål.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 60820-2023 FSC-klagomål mail.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 60820-2023 tillsynsbegäran.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 60820-2023 tillsynsbegäran mail.docx", "A 60820-2023")</f>
         <v/>
       </c>
     </row>
@@ -2497,7 +2497,7 @@
         <v>45104</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>45300</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 32949-2026</t>
+          <t>A 20397-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46244</v>
+        <v>46139</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2770,39 +2770,35 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 32949-2026 artfynd.xlsx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 20397-2026 artfynd.xlsx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 32949-2026 karta.png", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 20397-2026 karta.png", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 32949-2026 georefererad karta.tif", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 20397-2026 georefererad karta.tif", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 32949-2026 FSC-klagomål.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 20397-2026 FSC-klagomål.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 32949-2026 FSC-klagomål mail.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 20397-2026 FSC-klagomål mail.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 32949-2026 tillsynsbegäran.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 20397-2026 tillsynsbegäran.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 32949-2026 tillsynsbegäran mail.docx", "A 32949-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 32949-2026 prioriterade fågelarter.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 20397-2026 tillsynsbegäran mail.docx", "A 20397-2026")</f>
         <v/>
       </c>
     </row>
@@ -2826,7 +2822,7 @@
         <v>44830</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2914,7 +2910,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 20397-2026</t>
+          <t>A 26823-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2928,10 +2924,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46139</v>
+        <v>46183</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2944,17 +2940,17 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.2</v>
+        <v>12.1</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
@@ -2968,7 +2964,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2984,42 +2980,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 20397-2026 artfynd.xlsx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26823-2026 artfynd.xlsx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 20397-2026 karta.png", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26823-2026 karta.png", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 20397-2026 georefererad karta.tif", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26823-2026 georefererad karta.tif", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 20397-2026 FSC-klagomål.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26823-2026 FSC-klagomål.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 20397-2026 FSC-klagomål mail.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26823-2026 FSC-klagomål mail.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 20397-2026 tillsynsbegäran.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26823-2026 tillsynsbegäran.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 20397-2026 tillsynsbegäran mail.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26823-2026 tillsynsbegäran mail.docx", "A 26823-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 17907-2024</t>
+          <t>A 32949-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3033,10 +3029,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45419</v>
+        <v>46244</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3049,10 +3045,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3085,46 +3081,50 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Gulplister</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 17907-2024 artfynd.xlsx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 32949-2026 artfynd.xlsx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 17907-2024 karta.png", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 32949-2026 karta.png", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 17907-2024 georefererad karta.tif", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 32949-2026 georefererad karta.tif", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 17907-2024 FSC-klagomål.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 32949-2026 FSC-klagomål.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 17907-2024 FSC-klagomål mail.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 32949-2026 FSC-klagomål mail.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 17907-2024 tillsynsbegäran.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 32949-2026 tillsynsbegäran.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 17907-2024 tillsynsbegäran mail.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 32949-2026 tillsynsbegäran mail.docx", "A 32949-2026")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 32949-2026 prioriterade fågelarter.docx", "A 32949-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 26823-2026</t>
+          <t>A 17907-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3138,10 +3138,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46183</v>
+        <v>45419</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>12.1</v>
+        <v>3.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3163,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3178,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3190,39 +3190,39 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Gulplister</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26823-2026 artfynd.xlsx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 17907-2024 artfynd.xlsx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26823-2026 karta.png", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 17907-2024 karta.png", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26823-2026 georefererad karta.tif", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 17907-2024 georefererad karta.tif", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26823-2026 FSC-klagomål.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 17907-2024 FSC-klagomål.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26823-2026 FSC-klagomål mail.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 17907-2024 FSC-klagomål mail.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26823-2026 tillsynsbegäran.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 17907-2024 tillsynsbegäran.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26823-2026 tillsynsbegäran mail.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 17907-2024 tillsynsbegäran mail.docx", "A 17907-2024")</f>
         <v/>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
         <v>45337</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45811</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>44684</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44560</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44490</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44642</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44721</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>45534</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>45313</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>45386</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44579</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>45300</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>45399</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>45376</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>44986</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>45399</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>45202</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>45338</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45338</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 28966-2022</t>
+          <t>A 578-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4876,14 +4876,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44749</v>
+        <v>45299</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4895,8 +4895,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>3.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4939,7 +4944,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 578-2024</t>
+          <t>A 28966-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4949,14 +4954,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45299</v>
+        <v>44749</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4968,13 +4973,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>67.40000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5034,7 +5034,7 @@
         <v>45338</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>45455</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>45429</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>44907</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 1199-2024</t>
+          <t>A 30673-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45302</v>
+        <v>45112</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>16.1</v>
+        <v>2.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5397,7 +5397,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 30673-2023</t>
+          <t>A 1199-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45112</v>
+        <v>45302</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.4</v>
+        <v>16.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5475,7 +5475,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 4018-2024</t>
+          <t>A 61841-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45323</v>
+        <v>46003</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5504,13 +5504,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5553,7 +5548,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 61841-2025</t>
+          <t>A 4482-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5567,10 +5562,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46003</v>
+        <v>46045</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5582,8 +5577,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>6.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5626,7 +5626,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 4482-2026</t>
+          <t>A 4018-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5640,10 +5640,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46045</v>
+        <v>45323</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5704,7 +5704,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 6259-2024</t>
+          <t>A 15158-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45337</v>
+        <v>45744</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5777,7 +5777,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 6316-2024</t>
+          <t>A 43306-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5791,10 +5791,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45338</v>
+        <v>45910</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5806,13 +5806,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>28.6</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5855,7 +5850,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 42794-2024</t>
+          <t>A 6259-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5869,10 +5864,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45566</v>
+        <v>45337</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5885,7 +5880,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5928,7 +5923,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 15158-2025</t>
+          <t>A 6316-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5942,10 +5937,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45744</v>
+        <v>45338</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5957,8 +5952,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1.8</v>
+        <v>28.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6001,7 +6001,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 6852-2026</t>
+          <t>A 42794-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46057</v>
+        <v>45566</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6030,13 +6030,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>4.8</v>
+        <v>1.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6079,7 +6074,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 43306-2025</t>
+          <t>A 48171-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6093,10 +6088,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45910</v>
+        <v>45933</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6109,7 +6104,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6152,7 +6147,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 4188-2024</t>
+          <t>A 6852-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6166,10 +6161,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45324</v>
+        <v>46057</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6187,7 +6182,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>9.6</v>
+        <v>4.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6230,7 +6225,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 2190-2022</t>
+          <t>A 21291-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6244,10 +6239,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44578</v>
+        <v>46147</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6259,13 +6254,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6308,7 +6298,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 53977-2022</t>
+          <t>A 21293-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6322,10 +6312,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44876</v>
+        <v>46147</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6338,7 +6328,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6381,7 +6371,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 12903-2024</t>
+          <t>A 39791-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6395,10 +6385,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45385</v>
+        <v>45891</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6411,7 +6401,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>9.199999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6454,7 +6444,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 17151-2024</t>
+          <t>A 4188-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6468,10 +6458,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45412</v>
+        <v>45324</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6489,7 +6479,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.6</v>
+        <v>9.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6532,7 +6522,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 48171-2025</t>
+          <t>A 2190-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6546,10 +6536,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45933</v>
+        <v>44578</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6561,8 +6551,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6605,7 +6600,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 30040-2024</t>
+          <t>A 15288-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6615,14 +6610,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45488</v>
+        <v>46105</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6635,7 +6630,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6678,7 +6673,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 21291-2026</t>
+          <t>A 53977-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6692,10 +6687,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46147</v>
+        <v>44876</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6708,7 +6703,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6751,7 +6746,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 21293-2026</t>
+          <t>A 12903-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6765,10 +6760,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46147</v>
+        <v>45385</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6781,7 +6776,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6824,7 +6819,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 39791-2025</t>
+          <t>A 39796-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6841,7 +6836,7 @@
         <v>45891</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6854,7 +6849,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6897,7 +6892,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 16483-2024</t>
+          <t>A 17151-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6911,10 +6906,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45408</v>
+        <v>45412</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6926,8 +6921,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6970,7 +6970,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 12663-2022</t>
+          <t>A 30040-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6980,14 +6980,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44641</v>
+        <v>45488</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6999,13 +6999,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>12.4</v>
+        <v>4.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7048,7 +7043,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 30806-2023</t>
+          <t>A 49913-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7058,14 +7053,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45112</v>
+        <v>45940</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7077,13 +7072,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7126,7 +7116,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 17316-2024</t>
+          <t>A 16611-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7140,10 +7130,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45414</v>
+        <v>46112</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7157,11 +7147,11 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7204,7 +7194,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 15288-2026</t>
+          <t>A 16483-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7218,10 +7208,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46105</v>
+        <v>45408</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7234,7 +7224,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7277,7 +7267,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 49913-2025</t>
+          <t>A 12663-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7287,14 +7277,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45940</v>
+        <v>44641</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7306,8 +7296,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>12.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7350,7 +7345,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 39796-2025</t>
+          <t>A 24002-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7360,14 +7355,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45891</v>
+        <v>46167</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7380,7 +7375,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7423,7 +7418,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 31993-2023</t>
+          <t>A 30806-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7437,10 +7432,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45119</v>
+        <v>45112</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7452,8 +7447,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>6.8</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7496,7 +7496,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 16568-2024</t>
+          <t>A 15296-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7510,10 +7510,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45408</v>
+        <v>46105</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7569,7 +7569,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 4677-2023</t>
+          <t>A 17316-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7583,10 +7583,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44952</v>
+        <v>45414</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7598,8 +7598,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7642,7 +7647,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 11802-2024</t>
+          <t>A 49815-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7656,10 +7661,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45375</v>
+        <v>45940</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7671,13 +7676,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7720,7 +7720,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 11894-2024</t>
+          <t>A 31993-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7734,10 +7734,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45376</v>
+        <v>45119</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7749,13 +7749,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7798,7 +7793,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 24248-2024</t>
+          <t>A 4969-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7812,10 +7807,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45457</v>
+        <v>46049</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7827,8 +7822,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7871,7 +7871,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 16611-2026</t>
+          <t>A 16568-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7885,10 +7885,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46112</v>
+        <v>45408</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7900,13 +7900,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7949,7 +7944,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 5027-2024</t>
+          <t>A 4677-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7963,10 +7958,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45329</v>
+        <v>44952</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7978,13 +7973,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8027,7 +8017,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 49815-2025</t>
+          <t>A 11802-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8041,10 +8031,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45940</v>
+        <v>45375</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8056,8 +8046,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8100,7 +8095,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 24002-2026</t>
+          <t>A 11894-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8110,14 +8105,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46167</v>
+        <v>45376</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8129,8 +8124,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8173,7 +8173,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 12181-2023</t>
+          <t>A 23621-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44998</v>
+        <v>46162</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8246,7 +8246,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 15296-2026</t>
+          <t>A 24248-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8260,10 +8260,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46105</v>
+        <v>45457</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8319,7 +8319,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 4969-2026</t>
+          <t>A 61970-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8329,14 +8329,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46049</v>
+        <v>46003</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8348,13 +8348,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8397,7 +8392,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 38562-2023</t>
+          <t>A 5027-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8411,10 +8406,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45162</v>
+        <v>45329</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8426,8 +8421,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8470,7 +8470,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 17778-2024</t>
+          <t>A 6124-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8484,10 +8484,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45418</v>
+        <v>46053</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8499,13 +8499,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8548,7 +8543,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 44675-2024</t>
+          <t>A 16621-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8558,14 +8553,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45574</v>
+        <v>46112</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8579,11 +8574,11 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>11.2</v>
+        <v>0.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8626,7 +8621,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 26473-2024</t>
+          <t>A 12181-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8640,10 +8635,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45469</v>
+        <v>44998</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8656,7 +8651,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8699,7 +8694,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 51031-2023</t>
+          <t>A 38562-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8713,10 +8708,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45211</v>
+        <v>45162</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8729,7 +8724,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8772,7 +8767,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 7745-2025</t>
+          <t>A 17778-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8782,14 +8777,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45706</v>
+        <v>45418</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8801,8 +8796,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8845,7 +8845,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 61970-2025</t>
+          <t>A 24987-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8855,14 +8855,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46003</v>
+        <v>46174</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8918,7 +8918,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 5565-2024</t>
+          <t>A 44675-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8928,14 +8928,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45334</v>
+        <v>45574</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8947,8 +8947,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>2.9</v>
+        <v>11.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8991,7 +8996,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 23310-2022</t>
+          <t>A 26473-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9005,10 +9010,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44720</v>
+        <v>45469</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9020,13 +9025,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 6124-2026</t>
+          <t>A 51031-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9083,10 +9083,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46053</v>
+        <v>45211</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9142,7 +9142,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 23621-2026</t>
+          <t>A 7745-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9152,14 +9152,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46162</v>
+        <v>45706</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.8</v>
+        <v>0.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9215,7 +9215,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 16621-2026</t>
+          <t>A 31134-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9229,10 +9229,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46112</v>
+        <v>46216</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9246,11 +9246,11 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.4</v>
+        <v>4.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9293,7 +9293,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 7955-2024</t>
+          <t>A 5565-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9307,10 +9307,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45350</v>
+        <v>45334</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9366,7 +9366,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 32955-2026</t>
+          <t>A 23310-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9380,10 +9380,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46244</v>
+        <v>44720</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9395,8 +9395,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9439,7 +9444,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 32948-2026</t>
+          <t>A 10908-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9453,10 +9458,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46244</v>
+        <v>46079</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9469,7 +9474,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9512,7 +9517,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 55676-2022</t>
+          <t>A 7955-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9526,10 +9531,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44888</v>
+        <v>45350</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9542,7 +9547,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9585,7 +9590,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 8455-2024</t>
+          <t>A 35897-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9599,10 +9604,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45354</v>
+        <v>46266</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9614,13 +9619,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>5.1</v>
+        <v>3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 24987-2026</t>
+          <t>A 55676-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9677,10 +9677,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46174</v>
+        <v>44888</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 16027-2022</t>
+          <t>A 8455-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9750,10 +9750,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44665</v>
+        <v>45354</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.9</v>
+        <v>5.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9814,7 +9814,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 4651-2024</t>
+          <t>A 16027-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45328</v>
+        <v>44665</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9843,8 +9843,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9887,7 +9892,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 12988-2024</t>
+          <t>A 25597-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9901,10 +9906,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45385</v>
+        <v>46177</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9916,13 +9921,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>16.2</v>
+        <v>2.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9965,7 +9965,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 15305-2025</t>
+          <t>A 25605-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9975,14 +9975,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45746</v>
+        <v>46177</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10038,7 +10038,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 60817-2023</t>
+          <t>A 38074-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10052,10 +10052,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45260</v>
+        <v>46280</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10111,7 +10111,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 31134-2026</t>
+          <t>A 4651-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10125,10 +10125,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46216</v>
+        <v>45328</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10140,13 +10140,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10189,7 +10184,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 4023-2024</t>
+          <t>A 37743-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10203,10 +10198,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45323</v>
+        <v>46279</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10218,13 +10213,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>15.2</v>
+        <v>1.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10267,7 +10257,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 10908-2026</t>
+          <t>A 12988-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10281,10 +10271,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46079</v>
+        <v>45385</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10296,8 +10286,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>16.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10340,7 +10335,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 35897-2026</t>
+          <t>A 15305-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10350,14 +10345,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46266</v>
+        <v>45746</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10370,7 +10365,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10413,7 +10408,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 12310-2023</t>
+          <t>A 60817-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10427,10 +10422,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44999</v>
+        <v>45260</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10442,13 +10437,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10491,7 +10481,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 15921-2025</t>
+          <t>A 4023-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10505,10 +10495,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45749</v>
+        <v>45323</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10520,8 +10510,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>2.8</v>
+        <v>15.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10564,7 +10559,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 35742-2024</t>
+          <t>A 32948-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10578,10 +10573,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45532</v>
+        <v>46244</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10594,7 +10589,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10637,7 +10632,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 35715-2024</t>
+          <t>A 32955-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10651,10 +10646,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45532</v>
+        <v>46244</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10667,7 +10662,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10710,7 +10705,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 11806-2025</t>
+          <t>A 12310-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10724,10 +10719,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45727</v>
+        <v>44999</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10739,8 +10734,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10783,7 +10783,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 11810-2025</t>
+          <t>A 15921-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10797,10 +10797,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45727</v>
+        <v>45749</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10856,7 +10856,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 25597-2026</t>
+          <t>A 35742-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10870,10 +10870,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46177</v>
+        <v>45532</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10929,7 +10929,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 25605-2026</t>
+          <t>A 35715-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10943,10 +10943,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46177</v>
+        <v>45532</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11002,7 +11002,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 23185-2025</t>
+          <t>A 11806-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11012,14 +11012,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45791</v>
+        <v>45727</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11075,7 +11075,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 38074-2026</t>
+          <t>A 11810-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11089,10 +11089,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46280</v>
+        <v>45727</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11148,7 +11148,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 17760-2025</t>
+          <t>A 23185-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11158,14 +11158,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45758</v>
+        <v>45791</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11221,7 +11221,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 37743-2026</t>
+          <t>A 17760-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11235,10 +11235,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46279</v>
+        <v>45758</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11311,7 +11311,7 @@
         <v>45579</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>45547</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>45727</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>45861</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>45863</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>45537</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>

--- a/Översikt TOMELILLA.xlsx
+++ b/Översikt TOMELILLA.xlsx
@@ -601,7 +601,7 @@
         <v>44756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45120</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45260</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2018-2024</t>
+          <t>A 14152-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45308</v>
+        <v>45009</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>17.2</v>
+        <v>3.5</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1125,10 +1125,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1140,153 +1140,153 @@
         <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Kråka
+Röd glada</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 14152-2023 artfynd.xlsx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 14152-2023 karta.png", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 14152-2023 georefererad karta.tif", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 14152-2023 FSC-klagomål.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 14152-2023 FSC-klagomål mail.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 14152-2023 tillsynsbegäran.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 14152-2023 tillsynsbegäran mail.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 14152-2023 prioriterade fågelarter.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 2018-2024</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45308</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TOMELILLA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Västlig hakmossa
 Röd glada</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2018-2024 artfynd.xlsx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2018-2024 karta.png", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2018-2024 georefererad karta.tif", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2018-2024 FSC-klagomål.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2018-2024 FSC-klagomål mail.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2018-2024 tillsynsbegäran.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2018-2024 tillsynsbegäran mail.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 2018-2024 prioriterade fågelarter.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 14152-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45009</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>TOMELILLA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Kråka
-Röd glada</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 14152-2023 artfynd.xlsx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 14152-2023 karta.png", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 14152-2023 georefererad karta.tif", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 14152-2023 FSC-klagomål.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 14152-2023 FSC-klagomål mail.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 14152-2023 tillsynsbegäran.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 14152-2023 tillsynsbegäran mail.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 14152-2023 prioriterade fågelarter.docx", "A 14152-2023")</f>
         <v/>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
         <v>45299</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>45429</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45744</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>44613</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>44721</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 6261-2024</t>
+          <t>A 17907-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45337</v>
+        <v>45419</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1875,13 +1875,13 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>12.6</v>
+        <v>3.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1915,42 +1915,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Gulplister</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 17907-2024 artfynd.xlsx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 17907-2024 karta.png", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 17907-2024 georefererad karta.tif", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 17907-2024 FSC-klagomål.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 17907-2024 FSC-klagomål mail.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 17907-2024 tillsynsbegäran.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 17907-2024 tillsynsbegäran mail.docx", "A 17907-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 2193-2022</t>
+          <t>A 6261-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44578</v>
+        <v>45337</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1979,22 +1979,17 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>12.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2009,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2025,35 +2020,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Skogslysing</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2193-2022 artfynd.xlsx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2193-2022 karta.png", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2193-2022 georefererad karta.tif", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2193-2022 FSC-klagomål.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2193-2022 FSC-klagomål mail.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2193-2022 tillsynsbegäran.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2193-2022 tillsynsbegäran mail.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
     </row>
@@ -2077,7 +2072,7 @@
         <v>45337</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2165,7 +2160,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 49813-2025</t>
+          <t>A 28862-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2179,10 +2174,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45940</v>
+        <v>45104</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2194,8 +2189,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2239,38 +2239,38 @@
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 49813-2025 artfynd.xlsx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 49813-2025 karta.png", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 49813-2025 georefererad karta.tif", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 28862-2023 georefererad karta.tif", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 49813-2025 FSC-klagomål.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 28862-2023 FSC-klagomål.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 49813-2025 FSC-klagomål mail.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 28862-2023 FSC-klagomål mail.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 49813-2025 tillsynsbegäran.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 28862-2023 tillsynsbegäran.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 49813-2025 tillsynsbegäran mail.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 28862-2023 tillsynsbegäran mail.docx", "A 28862-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 61314-2025</t>
+          <t>A 2193-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46000</v>
+        <v>44578</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2299,18 +2299,23 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
@@ -2324,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2336,39 +2341,39 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Skogslysing</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2193-2022 artfynd.xlsx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2193-2022 karta.png", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2193-2022 georefererad karta.tif", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2193-2022 FSC-klagomål.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2193-2022 FSC-klagomål mail.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2193-2022 tillsynsbegäran.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2193-2022 tillsynsbegäran mail.docx", "A 2193-2022")</f>
         <v/>
       </c>
     </row>
@@ -2392,7 +2397,7 @@
         <v>45260</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2480,7 +2485,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 28862-2023</t>
+          <t>A 6261-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2494,10 +2499,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45104</v>
+        <v>45337</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2509,19 +2514,14 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>6.6</v>
+        <v>12.6</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2551,46 +2551,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 28862-2023 georefererad karta.tif", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 28862-2023 FSC-klagomål.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 28862-2023 FSC-klagomål mail.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 28862-2023 tillsynsbegäran.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 28862-2023 tillsynsbegäran mail.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 756-2024</t>
+          <t>A 42387-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45300</v>
+        <v>44830</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2619,13 +2619,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>13.1</v>
+        <v>1.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2665,42 +2660,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 756-2024 artfynd.xlsx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 42387-2022 artfynd.xlsx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 756-2024 karta.png", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 42387-2022 karta.png", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 756-2024 georefererad karta.tif", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 42387-2022 georefererad karta.tif", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 756-2024 FSC-klagomål.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 42387-2022 FSC-klagomål.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 756-2024 FSC-klagomål mail.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 42387-2022 FSC-klagomål mail.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 756-2024 tillsynsbegäran.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 42387-2022 tillsynsbegäran.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 756-2024 tillsynsbegäran mail.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 42387-2022 tillsynsbegäran mail.docx", "A 42387-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 20397-2026</t>
+          <t>A 49813-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2714,10 +2709,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46139</v>
+        <v>45940</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2730,7 +2725,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2774,38 +2769,38 @@
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 20397-2026 artfynd.xlsx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 49813-2025 artfynd.xlsx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 20397-2026 karta.png", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 49813-2025 karta.png", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 20397-2026 georefererad karta.tif", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 49813-2025 georefererad karta.tif", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 20397-2026 FSC-klagomål.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 49813-2025 FSC-klagomål.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 20397-2026 FSC-klagomål mail.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 49813-2025 FSC-klagomål mail.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 20397-2026 tillsynsbegäran.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 49813-2025 tillsynsbegäran.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 20397-2026 tillsynsbegäran mail.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 49813-2025 tillsynsbegäran mail.docx", "A 49813-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 42387-2022</t>
+          <t>A 61314-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2819,10 +2814,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44830</v>
+        <v>46000</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2835,16 +2830,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2859,7 +2854,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2875,35 +2870,35 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 42387-2022 artfynd.xlsx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 42387-2022 karta.png", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 42387-2022 georefererad karta.tif", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 42387-2022 FSC-klagomål.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 42387-2022 FSC-klagomål mail.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 42387-2022 tillsynsbegäran.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 42387-2022 tillsynsbegäran mail.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
     </row>
@@ -2927,7 +2922,7 @@
         <v>46183</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3015,7 +3010,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32949-2026</t>
+          <t>A 756-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3029,10 +3024,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46244</v>
+        <v>45300</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3044,18 +3039,23 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>4.8</v>
+        <v>13.1</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3085,46 +3085,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 32949-2026 artfynd.xlsx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 756-2024 artfynd.xlsx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 32949-2026 karta.png", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 756-2024 karta.png", "A 756-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 32949-2026 georefererad karta.tif", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 756-2024 georefererad karta.tif", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 32949-2026 FSC-klagomål.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 756-2024 FSC-klagomål.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 32949-2026 FSC-klagomål mail.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 756-2024 FSC-klagomål mail.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 32949-2026 tillsynsbegäran.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 756-2024 tillsynsbegäran.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 32949-2026 tillsynsbegäran mail.docx", "A 32949-2026")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 32949-2026 prioriterade fågelarter.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 756-2024 tillsynsbegäran mail.docx", "A 756-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 17907-2024</t>
+          <t>A 32949-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3138,10 +3134,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45419</v>
+        <v>46244</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3154,10 +3150,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3190,46 +3186,50 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Gulplister</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 17907-2024 artfynd.xlsx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 32949-2026 artfynd.xlsx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 17907-2024 karta.png", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 32949-2026 karta.png", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 17907-2024 georefererad karta.tif", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 32949-2026 georefererad karta.tif", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 17907-2024 FSC-klagomål.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 32949-2026 FSC-klagomål.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 17907-2024 FSC-klagomål mail.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 32949-2026 FSC-klagomål mail.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 17907-2024 tillsynsbegäran.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 32949-2026 tillsynsbegäran.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 17907-2024 tillsynsbegäran mail.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 32949-2026 tillsynsbegäran mail.docx", "A 32949-2026")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 32949-2026 prioriterade fågelarter.docx", "A 32949-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 6261-2024</t>
+          <t>A 26958-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45337</v>
+        <v>45811</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>12.6</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3295,46 +3295,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26958-2025 artfynd.xlsx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26958-2025 karta.png", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26958-2025 georefererad karta.tif", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26958-2025 FSC-klagomål.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26958-2025 FSC-klagomål mail.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26958-2025 tillsynsbegäran.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26958-2025 tillsynsbegäran mail.docx", "A 26958-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 26958-2025</t>
+          <t>A 20397-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45811</v>
+        <v>46139</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3364,13 +3364,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3404,35 +3404,35 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26958-2025 artfynd.xlsx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 20397-2026 artfynd.xlsx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26958-2025 karta.png", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 20397-2026 karta.png", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26958-2025 georefererad karta.tif", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 20397-2026 georefererad karta.tif", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26958-2025 FSC-klagomål.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 20397-2026 FSC-klagomål.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26958-2025 FSC-klagomål mail.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 20397-2026 FSC-klagomål mail.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26958-2025 tillsynsbegäran.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 20397-2026 tillsynsbegäran.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26958-2025 tillsynsbegäran mail.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 20397-2026 tillsynsbegäran mail.docx", "A 20397-2026")</f>
         <v/>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
         <v>44684</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44560</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44490</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44642</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44721</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 36180-2024</t>
+          <t>A 11806-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45534</v>
+        <v>45727</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4038,7 +4038,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 2548-2024</t>
+          <t>A 11810-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45313</v>
+        <v>45727</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4111,7 +4111,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 13159-2024</t>
+          <t>A 7745-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4121,14 +4121,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45386</v>
+        <v>45706</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 2555-2022</t>
+          <t>A 15921-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44579</v>
+        <v>45749</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4257,7 +4257,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 743-2024</t>
+          <t>A 47231-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45300</v>
+        <v>45202</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4286,13 +4286,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>11.1</v>
+        <v>1.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4335,7 +4330,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 15075-2024</t>
+          <t>A 4023-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4345,14 +4340,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45399</v>
+        <v>45323</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4364,8 +4359,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>15.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4408,7 +4408,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 11887-2024</t>
+          <t>A 11802-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45376</v>
+        <v>45375</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6.3</v>
+        <v>4.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4486,7 +4486,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 10272-2023</t>
+          <t>A 15305-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4496,14 +4496,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44986</v>
+        <v>45746</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4515,13 +4515,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>7.7</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4564,7 +4559,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 15012-2024</t>
+          <t>A 23185-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4574,14 +4569,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45399</v>
+        <v>45791</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4594,7 +4589,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.9</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4637,7 +4632,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 47231-2023</t>
+          <t>A 28966-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4647,14 +4642,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45202</v>
+        <v>44749</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4667,7 +4662,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4710,7 +4705,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8190-2024</t>
+          <t>A 17760-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4724,10 +4719,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45338</v>
+        <v>45758</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4739,13 +4734,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4788,7 +4778,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 8192-2024</t>
+          <t>A 578-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4802,10 +4792,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45338</v>
+        <v>45299</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4819,11 +4809,11 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4866,7 +4856,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 578-2024</t>
+          <t>A 19454-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4880,10 +4870,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45299</v>
+        <v>45429</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4895,13 +4885,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>67.40000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4944,7 +4929,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 28966-2022</t>
+          <t>A 23813-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4954,14 +4939,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44749</v>
+        <v>45455</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4974,7 +4959,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5017,7 +5002,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 6357-2024</t>
+          <t>A 24248-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5031,10 +5016,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45338</v>
+        <v>45457</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5046,13 +5031,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5095,7 +5075,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 23813-2024</t>
+          <t>A 12988-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5109,10 +5089,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45455</v>
+        <v>45385</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5124,8 +5104,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>16.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5168,7 +5153,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 19454-2024</t>
+          <t>A 2548-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5182,10 +5167,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45429</v>
+        <v>45313</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5198,7 +5183,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5241,7 +5226,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 59528-2022</t>
+          <t>A 38787-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5255,10 +5240,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44907</v>
+        <v>45547</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5270,13 +5255,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5319,7 +5299,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30673-2023</t>
+          <t>A 4677-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5333,10 +5313,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45112</v>
+        <v>44952</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5348,13 +5328,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5397,7 +5372,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 1199-2024</t>
+          <t>A 15158-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5411,10 +5386,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45302</v>
+        <v>45744</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5426,13 +5401,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>16.1</v>
+        <v>1.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5475,7 +5445,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 61841-2025</t>
+          <t>A 4018-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5489,10 +5459,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46003</v>
+        <v>45323</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5504,8 +5474,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5548,7 +5523,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 4482-2026</t>
+          <t>A 43306-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5562,10 +5537,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46045</v>
+        <v>45910</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5577,13 +5552,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5626,7 +5596,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 4018-2024</t>
+          <t>A 44675-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5636,14 +5606,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45323</v>
+        <v>45574</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5657,11 +5627,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.5</v>
+        <v>11.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5704,7 +5674,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 15158-2025</t>
+          <t>A 45729-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5718,10 +5688,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45744</v>
+        <v>45579</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5734,7 +5704,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.8</v>
+        <v>10.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5777,7 +5747,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 43306-2025</t>
+          <t>A 17316-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5791,10 +5761,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45910</v>
+        <v>45414</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5806,8 +5776,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5850,7 +5825,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 6259-2024</t>
+          <t>A 15012-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5864,10 +5839,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45337</v>
+        <v>45399</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5880,7 +5855,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5</v>
+        <v>6.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5923,7 +5898,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 6316-2024</t>
+          <t>A 2555-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5937,10 +5912,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45338</v>
+        <v>44579</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5952,13 +5927,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>28.6</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6001,7 +5971,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 42794-2024</t>
+          <t>A 4651-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6015,10 +5985,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45566</v>
+        <v>45328</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6031,7 +6001,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6074,7 +6044,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 48171-2025</t>
+          <t>A 30040-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6084,14 +6054,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45933</v>
+        <v>45488</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6104,7 +6074,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.9</v>
+        <v>4.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6147,7 +6117,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 6852-2026</t>
+          <t>A 48171-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6161,10 +6131,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46057</v>
+        <v>45933</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6176,13 +6146,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>4.8</v>
+        <v>1.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6225,7 +6190,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 21291-2026</t>
+          <t>A 16568-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6239,10 +6204,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46147</v>
+        <v>45408</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6255,7 +6220,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6298,7 +6263,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 21293-2026</t>
+          <t>A 12310-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6312,10 +6277,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46147</v>
+        <v>44999</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6327,8 +6292,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6371,7 +6341,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39791-2025</t>
+          <t>A 60817-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6385,10 +6355,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45891</v>
+        <v>45260</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6401,7 +6371,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6444,7 +6414,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 4188-2024</t>
+          <t>A 7955-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6458,10 +6428,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45324</v>
+        <v>45350</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6473,13 +6443,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>9.6</v>
+        <v>2.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6522,7 +6487,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 2190-2022</t>
+          <t>A 42794-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6536,10 +6501,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44578</v>
+        <v>45566</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6551,13 +6516,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>4.9</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6600,7 +6560,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 15288-2026</t>
+          <t>A 39791-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6614,10 +6574,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46105</v>
+        <v>45891</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6630,7 +6590,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6673,7 +6633,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 53977-2022</t>
+          <t>A 6357-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6687,10 +6647,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44876</v>
+        <v>45338</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6702,8 +6662,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6746,7 +6711,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 12903-2024</t>
+          <t>A 30673-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6760,10 +6725,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45385</v>
+        <v>45112</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6775,8 +6740,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>9.199999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6819,7 +6789,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 39796-2025</t>
+          <t>A 2190-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6833,10 +6803,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45891</v>
+        <v>44578</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6848,8 +6818,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6892,7 +6867,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17151-2024</t>
+          <t>A 11811-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6906,10 +6881,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45412</v>
+        <v>45727</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6921,13 +6896,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>3.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6970,7 +6940,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30040-2024</t>
+          <t>A 10272-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6980,14 +6950,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45488</v>
+        <v>44986</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6999,8 +6969,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>4.3</v>
+        <v>7.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7043,7 +7018,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 49913-2025</t>
+          <t>A 55676-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7053,14 +7028,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45940</v>
+        <v>44888</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7073,7 +7048,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7116,7 +7091,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 16611-2026</t>
+          <t>A 31993-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7130,10 +7105,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46112</v>
+        <v>45119</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7145,13 +7120,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>6.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7194,7 +7164,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 16483-2024</t>
+          <t>A 11894-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7208,10 +7178,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45408</v>
+        <v>45376</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7223,8 +7193,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7267,7 +7242,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 12663-2022</t>
+          <t>A 30806-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7281,10 +7256,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44641</v>
+        <v>45112</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7302,7 +7277,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>12.4</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7345,7 +7320,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 24002-2026</t>
+          <t>A 16483-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7355,14 +7330,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46167</v>
+        <v>45408</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7375,7 +7350,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>6.4</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7418,7 +7393,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 30806-2023</t>
+          <t>A 6316-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7432,10 +7407,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45112</v>
+        <v>45338</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7453,7 +7428,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>28.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7496,7 +7471,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 15296-2026</t>
+          <t>A 38562-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7510,10 +7485,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46105</v>
+        <v>45162</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7526,7 +7501,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7569,7 +7544,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 17316-2024</t>
+          <t>A 8455-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7583,10 +7558,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45414</v>
+        <v>45354</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7604,7 +7579,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7647,7 +7622,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 49815-2025</t>
+          <t>A 51031-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7661,10 +7636,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45940</v>
+        <v>45211</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7677,7 +7652,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7720,7 +7695,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 31993-2023</t>
+          <t>A 13159-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7734,10 +7709,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45119</v>
+        <v>45386</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7750,7 +7725,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>6.8</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7793,7 +7768,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 4969-2026</t>
+          <t>A 49913-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7803,14 +7778,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46049</v>
+        <v>45940</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7822,13 +7797,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7871,7 +7841,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 16568-2024</t>
+          <t>A 59528-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7885,10 +7855,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45408</v>
+        <v>44907</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7900,8 +7870,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7944,7 +7919,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 4677-2023</t>
+          <t>A 16027-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7958,10 +7933,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44952</v>
+        <v>44665</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7973,8 +7948,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8017,7 +7997,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 11802-2024</t>
+          <t>A 6259-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8031,10 +8011,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45375</v>
+        <v>45337</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8046,13 +8026,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8095,7 +8070,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 11894-2024</t>
+          <t>A 1199-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8109,10 +8084,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45376</v>
+        <v>45302</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8130,7 +8105,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.4</v>
+        <v>16.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8173,7 +8148,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 23621-2026</t>
+          <t>A 49815-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8187,10 +8162,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46162</v>
+        <v>45940</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8203,7 +8178,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8246,7 +8221,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 24248-2024</t>
+          <t>A 4969-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8260,10 +8235,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45457</v>
+        <v>46049</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8275,8 +8250,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8319,7 +8299,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 61970-2025</t>
+          <t>A 26473-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8329,14 +8309,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46003</v>
+        <v>45469</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8349,7 +8329,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8392,7 +8372,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 5027-2024</t>
+          <t>A 17778-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8406,10 +8386,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45329</v>
+        <v>45418</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8427,7 +8407,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8470,7 +8450,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 6124-2026</t>
+          <t>A 8190-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8484,10 +8464,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46053</v>
+        <v>45338</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8499,8 +8479,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8543,7 +8528,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 16621-2026</t>
+          <t>A 8192-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8557,10 +8542,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46112</v>
+        <v>45338</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8574,11 +8559,11 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8621,7 +8606,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 12181-2023</t>
+          <t>A 32955-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8635,10 +8620,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44998</v>
+        <v>46244</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8651,7 +8636,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8694,7 +8679,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 38562-2023</t>
+          <t>A 32948-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8708,10 +8693,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45162</v>
+        <v>46244</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8724,7 +8709,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8767,7 +8752,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 17778-2024</t>
+          <t>A 17151-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8781,10 +8766,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45418</v>
+        <v>45412</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8802,7 +8787,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8845,7 +8830,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 24987-2026</t>
+          <t>A 12181-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8859,10 +8844,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46174</v>
+        <v>44998</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8875,7 +8860,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8918,7 +8903,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 44675-2024</t>
+          <t>A 61970-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8928,14 +8913,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45574</v>
+        <v>46003</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8947,13 +8932,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>11.2</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8996,7 +8976,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 26473-2024</t>
+          <t>A 23310-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9010,10 +8990,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45469</v>
+        <v>44720</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9025,8 +9005,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9069,7 +9054,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 51031-2023</t>
+          <t>A 5027-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9083,10 +9068,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45211</v>
+        <v>45329</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9098,8 +9083,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9142,7 +9132,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 7745-2025</t>
+          <t>A 743-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9152,14 +9142,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45706</v>
+        <v>45300</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9171,8 +9161,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>0.4</v>
+        <v>11.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9215,7 +9210,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 31134-2026</t>
+          <t>A 6124-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9229,10 +9224,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46216</v>
+        <v>46053</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9244,13 +9239,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9293,7 +9283,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 5565-2024</t>
+          <t>A 35792-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9307,10 +9297,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45334</v>
+        <v>45861</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9322,8 +9312,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9366,7 +9361,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 23310-2022</t>
+          <t>A 35971-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9380,10 +9375,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44720</v>
+        <v>45863</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9395,13 +9390,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>5.3</v>
+        <v>1.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9444,7 +9434,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 10908-2026</t>
+          <t>A 53977-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9458,10 +9448,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46079</v>
+        <v>44876</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9474,7 +9464,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9517,7 +9507,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 7955-2024</t>
+          <t>A 16621-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9531,10 +9521,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45350</v>
+        <v>46112</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9546,8 +9536,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9590,7 +9585,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 35897-2026</t>
+          <t>A 4188-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9604,10 +9599,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46266</v>
+        <v>45324</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9619,8 +9614,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>3</v>
+        <v>9.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 55676-2022</t>
+          <t>A 12663-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9677,10 +9677,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44888</v>
+        <v>44641</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9692,8 +9692,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>12.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9736,7 +9741,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 8455-2024</t>
+          <t>A 61841-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9750,10 +9755,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45354</v>
+        <v>46003</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9765,13 +9770,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9814,7 +9814,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 16027-2022</t>
+          <t>A 36180-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44665</v>
+        <v>45534</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9843,13 +9843,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9892,7 +9887,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 25597-2026</t>
+          <t>A 12903-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9906,10 +9901,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46177</v>
+        <v>45385</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9922,7 +9917,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9965,7 +9960,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 25605-2026</t>
+          <t>A 15075-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9975,14 +9970,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46177</v>
+        <v>45399</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9995,7 +9990,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10038,7 +10033,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 38074-2026</t>
+          <t>A 11887-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10052,10 +10047,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46280</v>
+        <v>45376</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10067,8 +10062,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>4.6</v>
+        <v>6.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10111,7 +10111,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 4651-2024</t>
+          <t>A 5565-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10125,10 +10125,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45328</v>
+        <v>45334</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10184,7 +10184,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 37743-2026</t>
+          <t>A 4482-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10198,10 +10198,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46279</v>
+        <v>46045</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10213,8 +10213,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>1.2</v>
+        <v>6.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10257,7 +10262,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 12988-2024</t>
+          <t>A 6852-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10271,10 +10276,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45385</v>
+        <v>46057</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10292,7 +10297,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>16.2</v>
+        <v>4.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10335,7 +10340,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 15305-2025</t>
+          <t>A 35742-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10345,14 +10350,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45746</v>
+        <v>45532</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10365,7 +10370,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10408,7 +10413,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 60817-2023</t>
+          <t>A 21291-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10422,10 +10427,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45260</v>
+        <v>46147</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10438,7 +10443,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10481,7 +10486,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 4023-2024</t>
+          <t>A 21293-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10495,10 +10500,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45323</v>
+        <v>46147</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10510,13 +10515,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>15.2</v>
+        <v>2.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10559,7 +10559,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 32948-2026</t>
+          <t>A 35715-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10573,10 +10573,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46244</v>
+        <v>45532</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10632,7 +10632,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 32955-2026</t>
+          <t>A 15288-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10646,10 +10646,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46244</v>
+        <v>46105</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10705,7 +10705,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 12310-2023</t>
+          <t>A 39796-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10719,10 +10719,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44999</v>
+        <v>45891</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10734,13 +10734,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10783,7 +10778,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 15921-2025</t>
+          <t>A 16611-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10797,10 +10792,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45749</v>
+        <v>46112</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10812,8 +10807,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10856,7 +10856,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 35742-2024</t>
+          <t>A 24002-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10866,14 +10866,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45532</v>
+        <v>46167</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1</v>
+        <v>6.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10929,7 +10929,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 35715-2024</t>
+          <t>A 15296-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10943,10 +10943,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45532</v>
+        <v>46105</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11002,7 +11002,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 11806-2025</t>
+          <t>A 23621-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11016,10 +11016,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45727</v>
+        <v>46162</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11075,7 +11075,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 11810-2025</t>
+          <t>A 24987-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11089,10 +11089,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45727</v>
+        <v>46174</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11148,7 +11148,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 23185-2025</t>
+          <t>A 10908-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11158,14 +11158,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45791</v>
+        <v>46079</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11221,7 +11221,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 17760-2025</t>
+          <t>A 31134-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11235,10 +11235,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45758</v>
+        <v>46216</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11250,8 +11250,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11294,7 +11299,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 45729-2024</t>
+          <t>A 35897-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11308,10 +11313,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45579</v>
+        <v>46266</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11324,7 +11329,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>10.1</v>
+        <v>3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11367,7 +11372,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 38787-2024</t>
+          <t>A 25597-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11381,10 +11386,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45547</v>
+        <v>46177</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11397,7 +11402,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11440,7 +11445,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 11811-2025</t>
+          <t>A 25605-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11454,10 +11459,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45727</v>
+        <v>46177</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11470,7 +11475,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>9.699999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11513,7 +11518,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 35792-2025</t>
+          <t>A 37743-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11527,10 +11532,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45861</v>
+        <v>46279</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11542,13 +11547,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11591,7 +11591,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 35971-2025</t>
+          <t>A 38074-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11605,10 +11605,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45863</v>
+        <v>46280</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11681,7 +11681,7 @@
         <v>45537</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>

--- a/Översikt TOMELILLA.xlsx
+++ b/Översikt TOMELILLA.xlsx
@@ -601,7 +601,7 @@
         <v>44756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45120</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45260</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 14152-2023</t>
+          <t>A 2018-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45009</v>
+        <v>45308</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.5</v>
+        <v>17.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1125,10 +1125,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1140,153 +1140,153 @@
         <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Västlig hakmossa
+Röd glada</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2018-2024 artfynd.xlsx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2018-2024 karta.png", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2018-2024 georefererad karta.tif", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2018-2024 FSC-klagomål.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2018-2024 FSC-klagomål mail.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2018-2024 tillsynsbegäran.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2018-2024 tillsynsbegäran mail.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 2018-2024 prioriterade fågelarter.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 14152-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45009</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TOMELILLA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Kråka
 Röd glada</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 14152-2023 artfynd.xlsx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 14152-2023 karta.png", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 14152-2023 georefererad karta.tif", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 14152-2023 FSC-klagomål.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 14152-2023 FSC-klagomål mail.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 14152-2023 tillsynsbegäran.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 14152-2023 tillsynsbegäran mail.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 14152-2023 prioriterade fågelarter.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 2018-2024</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45308</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>TOMELILLA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Västlig hakmossa
-Röd glada</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2018-2024 artfynd.xlsx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2018-2024 karta.png", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2018-2024 georefererad karta.tif", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2018-2024 FSC-klagomål.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2018-2024 FSC-klagomål mail.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2018-2024 tillsynsbegäran.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2018-2024 tillsynsbegäran mail.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 2018-2024 prioriterade fågelarter.docx", "A 2018-2024")</f>
         <v/>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
         <v>45299</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>45429</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45744</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>44613</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>44721</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17907-2024</t>
+          <t>A 6261-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45419</v>
+        <v>45337</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1875,13 +1875,13 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.1</v>
+        <v>12.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1915,42 +1915,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Gulplister</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 17907-2024 artfynd.xlsx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 17907-2024 karta.png", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 17907-2024 georefererad karta.tif", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 17907-2024 FSC-klagomål.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 17907-2024 FSC-klagomål mail.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 17907-2024 tillsynsbegäran.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 17907-2024 tillsynsbegäran mail.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 6261-2024</t>
+          <t>A 2193-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45337</v>
+        <v>44578</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1979,18 +1979,23 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>12.6</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -2004,7 +2009,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2020,35 +2025,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Skogslysing</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2193-2022 artfynd.xlsx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2193-2022 karta.png", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2193-2022 georefererad karta.tif", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2193-2022 FSC-klagomål.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2193-2022 FSC-klagomål mail.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2193-2022 tillsynsbegäran.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2193-2022 tillsynsbegäran mail.docx", "A 2193-2022")</f>
         <v/>
       </c>
     </row>
@@ -2072,7 +2077,7 @@
         <v>45337</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2160,7 +2165,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28862-2023</t>
+          <t>A 49813-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2174,10 +2179,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45104</v>
+        <v>45940</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2189,13 +2194,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2239,38 +2239,38 @@
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 49813-2025 artfynd.xlsx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 49813-2025 karta.png", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 28862-2023 georefererad karta.tif", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 49813-2025 georefererad karta.tif", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 28862-2023 FSC-klagomål.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 49813-2025 FSC-klagomål.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 28862-2023 FSC-klagomål mail.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 49813-2025 FSC-klagomål mail.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 28862-2023 tillsynsbegäran.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 49813-2025 tillsynsbegäran.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 28862-2023 tillsynsbegäran mail.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 49813-2025 tillsynsbegäran mail.docx", "A 49813-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 2193-2022</t>
+          <t>A 61314-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44578</v>
+        <v>46000</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2299,22 +2299,17 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2329,7 +2324,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2341,39 +2336,39 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Skogslysing</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2193-2022 artfynd.xlsx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2193-2022 karta.png", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2193-2022 georefererad karta.tif", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2193-2022 FSC-klagomål.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2193-2022 FSC-klagomål mail.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2193-2022 tillsynsbegäran.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2193-2022 tillsynsbegäran mail.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
     </row>
@@ -2397,7 +2392,7 @@
         <v>45260</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2485,7 +2480,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 6261-2024</t>
+          <t>A 28862-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2499,10 +2494,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45337</v>
+        <v>45104</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2514,14 +2509,19 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>12.6</v>
+        <v>6.6</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2551,46 +2551,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 28862-2023 georefererad karta.tif", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 28862-2023 FSC-klagomål.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 28862-2023 FSC-klagomål mail.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 28862-2023 tillsynsbegäran.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 28862-2023 tillsynsbegäran mail.docx", "A 28862-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 42387-2022</t>
+          <t>A 756-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44830</v>
+        <v>45300</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2619,8 +2619,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1.1</v>
+        <v>13.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2660,42 +2665,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 42387-2022 artfynd.xlsx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 756-2024 artfynd.xlsx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 42387-2022 karta.png", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 756-2024 karta.png", "A 756-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 42387-2022 georefererad karta.tif", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 756-2024 georefererad karta.tif", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 42387-2022 FSC-klagomål.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 756-2024 FSC-klagomål.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 42387-2022 FSC-klagomål mail.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 756-2024 FSC-klagomål mail.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 42387-2022 tillsynsbegäran.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 756-2024 tillsynsbegäran.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 42387-2022 tillsynsbegäran mail.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 756-2024 tillsynsbegäran mail.docx", "A 756-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 49813-2025</t>
+          <t>A 20397-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2709,10 +2714,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45940</v>
+        <v>46139</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2725,7 +2730,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2769,38 +2774,38 @@
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 49813-2025 artfynd.xlsx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 20397-2026 artfynd.xlsx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 49813-2025 karta.png", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 20397-2026 karta.png", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 49813-2025 georefererad karta.tif", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 20397-2026 georefererad karta.tif", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 49813-2025 FSC-klagomål.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 20397-2026 FSC-klagomål.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 49813-2025 FSC-klagomål mail.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 20397-2026 FSC-klagomål mail.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 49813-2025 tillsynsbegäran.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 20397-2026 tillsynsbegäran.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 49813-2025 tillsynsbegäran mail.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 20397-2026 tillsynsbegäran mail.docx", "A 20397-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 61314-2025</t>
+          <t>A 42387-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2814,10 +2819,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46000</v>
+        <v>44830</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2830,17 +2835,17 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
@@ -2854,7 +2859,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2870,35 +2875,35 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 42387-2022 artfynd.xlsx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 42387-2022 karta.png", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 42387-2022 georefererad karta.tif", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 42387-2022 FSC-klagomål.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 42387-2022 FSC-klagomål mail.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 42387-2022 tillsynsbegäran.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 42387-2022 tillsynsbegäran mail.docx", "A 42387-2022")</f>
         <v/>
       </c>
     </row>
@@ -2922,7 +2927,7 @@
         <v>46183</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3010,7 +3015,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 756-2024</t>
+          <t>A 17907-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3024,10 +3029,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45300</v>
+        <v>45419</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3039,13 +3044,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>13.1</v>
+        <v>3.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3081,39 +3081,39 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Gulplister</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 756-2024 artfynd.xlsx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 17907-2024 artfynd.xlsx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 756-2024 karta.png", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 17907-2024 karta.png", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 756-2024 georefererad karta.tif", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 17907-2024 georefererad karta.tif", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 756-2024 FSC-klagomål.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 17907-2024 FSC-klagomål.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 756-2024 FSC-klagomål mail.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 17907-2024 FSC-klagomål mail.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 756-2024 tillsynsbegäran.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 17907-2024 tillsynsbegäran.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 756-2024 tillsynsbegäran mail.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 17907-2024 tillsynsbegäran mail.docx", "A 17907-2024")</f>
         <v/>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
         <v>46244</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 26958-2025</t>
+          <t>A 6261-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45811</v>
+        <v>45337</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>12.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3295,46 +3295,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26958-2025 artfynd.xlsx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26958-2025 karta.png", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26958-2025 georefererad karta.tif", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26958-2025 FSC-klagomål.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26958-2025 FSC-klagomål mail.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26958-2025 tillsynsbegäran.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26958-2025 tillsynsbegäran mail.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 20397-2026</t>
+          <t>A 26958-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46139</v>
+        <v>45811</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3364,13 +3364,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
         <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3404,35 +3404,35 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 20397-2026 artfynd.xlsx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26958-2025 artfynd.xlsx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 20397-2026 karta.png", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26958-2025 karta.png", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 20397-2026 georefererad karta.tif", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26958-2025 georefererad karta.tif", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 20397-2026 FSC-klagomål.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26958-2025 FSC-klagomål.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 20397-2026 FSC-klagomål mail.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26958-2025 FSC-klagomål mail.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 20397-2026 tillsynsbegäran.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26958-2025 tillsynsbegäran.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 20397-2026 tillsynsbegäran mail.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26958-2025 tillsynsbegäran mail.docx", "A 26958-2025")</f>
         <v/>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
         <v>44684</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44560</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44490</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44642</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44721</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 11806-2025</t>
+          <t>A 36180-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45727</v>
+        <v>45534</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4038,7 +4038,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 11810-2025</t>
+          <t>A 2548-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45727</v>
+        <v>45313</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4111,7 +4111,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 7745-2025</t>
+          <t>A 13159-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4121,14 +4121,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45706</v>
+        <v>45386</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 15921-2025</t>
+          <t>A 2555-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45749</v>
+        <v>44579</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4257,7 +4257,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 47231-2023</t>
+          <t>A 743-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45202</v>
+        <v>45300</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4286,8 +4286,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.3</v>
+        <v>11.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4330,7 +4335,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 4023-2024</t>
+          <t>A 15075-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4340,14 +4345,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45323</v>
+        <v>45399</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4359,13 +4364,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>15.2</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4408,7 +4408,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 11802-2024</t>
+          <t>A 11887-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45375</v>
+        <v>45376</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.7</v>
+        <v>6.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4486,7 +4486,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 15305-2025</t>
+          <t>A 10272-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4496,14 +4496,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45746</v>
+        <v>44986</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4515,8 +4515,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>7.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4559,7 +4564,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 23185-2025</t>
+          <t>A 15012-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4569,14 +4574,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45791</v>
+        <v>45399</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4589,7 +4594,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>6.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4632,7 +4637,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 28966-2022</t>
+          <t>A 47231-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4642,14 +4647,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44749</v>
+        <v>45202</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4662,7 +4667,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4705,7 +4710,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 17760-2025</t>
+          <t>A 8190-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4719,10 +4724,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45758</v>
+        <v>45338</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4734,8 +4739,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4778,7 +4788,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 578-2024</t>
+          <t>A 8192-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4792,10 +4802,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45299</v>
+        <v>45338</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4809,11 +4819,11 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>67.40000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4856,7 +4866,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 19454-2024</t>
+          <t>A 578-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4870,10 +4880,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45429</v>
+        <v>45299</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4885,8 +4895,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>2.1</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4929,7 +4944,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 23813-2024</t>
+          <t>A 28966-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4939,14 +4954,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45455</v>
+        <v>44749</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4959,7 +4974,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5002,7 +5017,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 24248-2024</t>
+          <t>A 6357-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5016,10 +5031,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45457</v>
+        <v>45338</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5031,8 +5046,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5075,7 +5095,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 12988-2024</t>
+          <t>A 23813-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5089,10 +5109,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45385</v>
+        <v>45455</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5104,13 +5124,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>16.2</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5153,7 +5168,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2548-2024</t>
+          <t>A 19454-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5167,10 +5182,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45313</v>
+        <v>45429</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5183,7 +5198,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5226,7 +5241,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 38787-2024</t>
+          <t>A 59528-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5240,10 +5255,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45547</v>
+        <v>44907</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5255,8 +5270,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5299,7 +5319,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 4677-2023</t>
+          <t>A 30673-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5313,10 +5333,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44952</v>
+        <v>45112</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5328,8 +5348,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5372,7 +5397,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 15158-2025</t>
+          <t>A 1199-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5386,10 +5411,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45744</v>
+        <v>45302</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5401,8 +5426,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.8</v>
+        <v>16.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5445,7 +5475,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 4018-2024</t>
+          <t>A 15158-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5459,10 +5489,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45323</v>
+        <v>45744</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5474,13 +5504,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5523,7 +5548,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 43306-2025</t>
+          <t>A 4018-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5537,10 +5562,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45910</v>
+        <v>45323</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5552,8 +5577,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5596,7 +5626,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 44675-2024</t>
+          <t>A 61841-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5606,14 +5636,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45574</v>
+        <v>46003</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5625,13 +5655,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>11.2</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5674,7 +5699,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 45729-2024</t>
+          <t>A 43306-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5688,10 +5713,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45579</v>
+        <v>45910</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5704,7 +5729,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>10.1</v>
+        <v>1.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5747,7 +5772,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 17316-2024</t>
+          <t>A 6259-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5761,10 +5786,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45414</v>
+        <v>45337</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5776,13 +5801,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5825,7 +5845,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 15012-2024</t>
+          <t>A 6316-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5839,10 +5859,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45399</v>
+        <v>45338</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5854,8 +5874,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>6.9</v>
+        <v>28.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5898,7 +5923,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 2555-2022</t>
+          <t>A 4482-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5912,10 +5937,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44579</v>
+        <v>46045</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5927,8 +5952,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5971,7 +6001,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 4651-2024</t>
+          <t>A 42794-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5985,10 +6015,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45328</v>
+        <v>45566</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6001,7 +6031,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6044,7 +6074,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30040-2024</t>
+          <t>A 48171-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6054,14 +6084,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45488</v>
+        <v>45933</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6074,7 +6104,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6117,7 +6147,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 48171-2025</t>
+          <t>A 39791-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6131,10 +6161,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45933</v>
+        <v>45891</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6147,7 +6177,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6190,7 +6220,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 16568-2024</t>
+          <t>A 4188-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6204,10 +6234,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45408</v>
+        <v>45324</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6219,8 +6249,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>9.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6263,7 +6298,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 12310-2023</t>
+          <t>A 2190-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6277,10 +6312,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44999</v>
+        <v>44578</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6298,7 +6333,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6341,7 +6376,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 60817-2023</t>
+          <t>A 53977-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6355,10 +6390,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45260</v>
+        <v>44876</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6371,7 +6406,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6414,7 +6449,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 7955-2024</t>
+          <t>A 12903-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6428,10 +6463,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45350</v>
+        <v>45385</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6444,7 +6479,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6487,7 +6522,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 42794-2024</t>
+          <t>A 17151-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6501,10 +6536,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45566</v>
+        <v>45412</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6516,8 +6551,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6560,7 +6600,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 39791-2025</t>
+          <t>A 30040-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6570,14 +6610,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45891</v>
+        <v>45488</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6590,7 +6630,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6633,7 +6673,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 6357-2024</t>
+          <t>A 6852-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6647,10 +6687,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45338</v>
+        <v>46057</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6664,11 +6704,11 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6711,7 +6751,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 30673-2023</t>
+          <t>A 49913-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6721,14 +6761,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45112</v>
+        <v>45940</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6740,13 +6780,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6789,7 +6824,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 2190-2022</t>
+          <t>A 16483-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6803,10 +6838,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44578</v>
+        <v>45408</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6818,13 +6853,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>4.9</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6867,7 +6897,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 11811-2025</t>
+          <t>A 21291-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6881,10 +6911,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45727</v>
+        <v>46147</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6897,7 +6927,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>9.699999999999999</v>
+        <v>3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6940,7 +6970,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 10272-2023</t>
+          <t>A 21293-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6954,10 +6984,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44986</v>
+        <v>46147</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6969,13 +6999,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>7.7</v>
+        <v>2.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7018,7 +7043,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 55676-2022</t>
+          <t>A 12663-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7032,10 +7057,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44888</v>
+        <v>44641</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7047,8 +7072,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>12.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7091,7 +7121,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 31993-2023</t>
+          <t>A 30806-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7105,10 +7135,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45119</v>
+        <v>45112</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7120,8 +7150,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>6.8</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7164,7 +7199,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 11894-2024</t>
+          <t>A 15288-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7178,10 +7213,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45376</v>
+        <v>46105</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7193,13 +7228,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7242,7 +7272,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 30806-2023</t>
+          <t>A 17316-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7256,10 +7286,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45112</v>
+        <v>45414</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7277,7 +7307,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7320,7 +7350,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 16483-2024</t>
+          <t>A 39796-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7334,10 +7364,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45408</v>
+        <v>45891</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7350,7 +7380,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7393,7 +7423,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 6316-2024</t>
+          <t>A 31993-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7407,10 +7437,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45338</v>
+        <v>45119</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7422,13 +7452,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>28.6</v>
+        <v>6.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7471,7 +7496,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 38562-2023</t>
+          <t>A 16568-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7485,10 +7510,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45162</v>
+        <v>45408</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7501,7 +7526,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7544,7 +7569,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 8455-2024</t>
+          <t>A 4677-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7558,10 +7583,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45354</v>
+        <v>44952</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7573,13 +7598,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>5.1</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7622,7 +7642,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 51031-2023</t>
+          <t>A 49815-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7636,10 +7656,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45211</v>
+        <v>45940</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7652,7 +7672,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7695,7 +7715,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 13159-2024</t>
+          <t>A 4969-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7709,10 +7729,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45386</v>
+        <v>46049</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7724,8 +7744,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7768,7 +7793,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 49913-2025</t>
+          <t>A 11802-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7778,14 +7803,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45940</v>
+        <v>45375</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7797,8 +7822,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>4.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7841,7 +7871,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 59528-2022</t>
+          <t>A 11894-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7855,10 +7885,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44907</v>
+        <v>45376</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7876,7 +7906,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7919,7 +7949,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 16027-2022</t>
+          <t>A 24248-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7933,10 +7963,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44665</v>
+        <v>45457</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7948,13 +7978,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7997,7 +8022,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 6259-2024</t>
+          <t>A 16611-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8011,10 +8036,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45337</v>
+        <v>46112</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8026,8 +8051,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8070,7 +8100,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 1199-2024</t>
+          <t>A 5027-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8084,10 +8114,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45302</v>
+        <v>45329</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8105,7 +8135,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>16.1</v>
+        <v>4.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8148,7 +8178,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 49815-2025</t>
+          <t>A 61970-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8158,14 +8188,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45940</v>
+        <v>46003</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8178,7 +8208,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8221,7 +8251,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 4969-2026</t>
+          <t>A 24002-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8231,14 +8261,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46049</v>
+        <v>46167</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8250,13 +8280,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>2.6</v>
+        <v>6.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8299,7 +8324,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 26473-2024</t>
+          <t>A 15296-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8313,10 +8338,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45469</v>
+        <v>46105</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8329,7 +8354,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.4</v>
+        <v>0.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8372,7 +8397,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 17778-2024</t>
+          <t>A 12181-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8386,10 +8411,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45418</v>
+        <v>44998</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8401,13 +8426,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8450,7 +8470,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 8190-2024</t>
+          <t>A 6124-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8464,10 +8484,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45338</v>
+        <v>46053</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8479,13 +8499,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8528,7 +8543,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 8192-2024</t>
+          <t>A 16621-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8542,10 +8557,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45338</v>
+        <v>46112</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8559,11 +8574,11 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8606,7 +8621,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 32955-2026</t>
+          <t>A 38562-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8620,10 +8635,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46244</v>
+        <v>45162</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8636,7 +8651,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8679,7 +8694,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 32948-2026</t>
+          <t>A 17778-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8693,10 +8708,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46244</v>
+        <v>45418</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8708,8 +8723,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8752,7 +8772,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 17151-2024</t>
+          <t>A 44675-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8762,14 +8782,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45412</v>
+        <v>45574</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8783,11 +8803,11 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.6</v>
+        <v>11.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8830,7 +8850,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 12181-2023</t>
+          <t>A 26473-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8844,10 +8864,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44998</v>
+        <v>45469</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8860,7 +8880,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8903,7 +8923,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 61970-2025</t>
+          <t>A 51031-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8913,14 +8933,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46003</v>
+        <v>45211</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8933,7 +8953,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8976,7 +8996,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 23310-2022</t>
+          <t>A 7745-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8986,14 +9006,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44720</v>
+        <v>45706</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9005,13 +9025,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>5.3</v>
+        <v>0.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9054,7 +9069,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 5027-2024</t>
+          <t>A 23621-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9068,10 +9083,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45329</v>
+        <v>46162</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9083,13 +9098,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9132,7 +9142,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 743-2024</t>
+          <t>A 5565-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9146,10 +9156,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45300</v>
+        <v>45334</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9161,13 +9171,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>11.1</v>
+        <v>2.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9210,7 +9215,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 6124-2026</t>
+          <t>A 23310-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9224,10 +9229,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46053</v>
+        <v>44720</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9239,8 +9244,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9283,7 +9293,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 35792-2025</t>
+          <t>A 24987-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9297,10 +9307,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45861</v>
+        <v>46174</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9312,13 +9322,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9361,7 +9366,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 35971-2025</t>
+          <t>A 7955-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9375,10 +9380,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45863</v>
+        <v>45350</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9391,7 +9396,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9434,7 +9439,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 53977-2022</t>
+          <t>A 55676-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9448,10 +9453,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44876</v>
+        <v>44888</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9464,7 +9469,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9507,7 +9512,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 16621-2026</t>
+          <t>A 31134-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9521,10 +9526,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46112</v>
+        <v>46216</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9538,11 +9543,11 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.4</v>
+        <v>4.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9585,7 +9590,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 4188-2024</t>
+          <t>A 8455-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9599,10 +9604,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45324</v>
+        <v>45354</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9620,7 +9625,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>9.6</v>
+        <v>5.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9663,7 +9668,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 12663-2022</t>
+          <t>A 16027-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9677,10 +9682,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44641</v>
+        <v>44665</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9698,7 +9703,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>12.4</v>
+        <v>1.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9741,7 +9746,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 61841-2025</t>
+          <t>A 35897-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9755,10 +9760,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46003</v>
+        <v>46266</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9771,7 +9776,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9814,7 +9819,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 36180-2024</t>
+          <t>A 4651-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9828,10 +9833,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45534</v>
+        <v>45328</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9844,7 +9849,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9887,7 +9892,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 12903-2024</t>
+          <t>A 12988-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9904,7 +9909,7 @@
         <v>45385</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9916,8 +9921,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>9.199999999999999</v>
+        <v>16.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9960,7 +9970,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 15075-2024</t>
+          <t>A 15305-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9974,10 +9984,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45399</v>
+        <v>45746</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9990,7 +10000,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10033,7 +10043,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 11887-2024</t>
+          <t>A 60817-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10047,10 +10057,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45376</v>
+        <v>45260</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10062,13 +10072,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>6.3</v>
+        <v>4.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10111,7 +10116,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 5565-2024</t>
+          <t>A 4023-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10125,10 +10130,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45334</v>
+        <v>45323</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10140,8 +10145,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>2.9</v>
+        <v>15.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10184,7 +10194,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 4482-2026</t>
+          <t>A 25597-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10198,10 +10208,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46045</v>
+        <v>46177</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10213,13 +10223,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10262,7 +10267,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 6852-2026</t>
+          <t>A 25605-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10276,10 +10281,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46057</v>
+        <v>46177</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10291,13 +10296,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10340,7 +10340,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 35742-2024</t>
+          <t>A 38074-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10354,10 +10354,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45532</v>
+        <v>46280</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10413,7 +10413,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 21291-2026</t>
+          <t>A 12310-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10427,10 +10427,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46147</v>
+        <v>44999</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10442,8 +10442,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10486,7 +10491,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 21293-2026</t>
+          <t>A 37743-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10500,10 +10505,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46147</v>
+        <v>46279</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10516,7 +10521,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10559,7 +10564,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 35715-2024</t>
+          <t>A 15921-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10573,10 +10578,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45532</v>
+        <v>45749</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10589,7 +10594,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10632,7 +10637,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 15288-2026</t>
+          <t>A 35742-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10646,10 +10651,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46105</v>
+        <v>45532</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10662,7 +10667,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10705,7 +10710,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 39796-2025</t>
+          <t>A 35715-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10719,10 +10724,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45891</v>
+        <v>45532</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10735,7 +10740,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10778,7 +10783,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 16611-2026</t>
+          <t>A 11806-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10792,10 +10797,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46112</v>
+        <v>45727</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10807,13 +10812,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10856,7 +10856,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 24002-2026</t>
+          <t>A 11810-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10866,14 +10866,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46167</v>
+        <v>45727</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>6.4</v>
+        <v>2.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10929,7 +10929,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 15296-2026</t>
+          <t>A 32948-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10943,10 +10943,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46105</v>
+        <v>46244</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11002,7 +11002,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 23621-2026</t>
+          <t>A 32955-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11016,10 +11016,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46162</v>
+        <v>46244</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11075,7 +11075,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 24987-2026</t>
+          <t>A 23185-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11085,14 +11085,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46174</v>
+        <v>45791</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 10908-2026</t>
+          <t>A 17760-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11162,10 +11162,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46079</v>
+        <v>45758</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11221,7 +11221,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 31134-2026</t>
+          <t>A 45729-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11235,10 +11235,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46216</v>
+        <v>45579</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11250,13 +11250,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>4.5</v>
+        <v>10.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11299,7 +11294,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 35897-2026</t>
+          <t>A 38787-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11313,10 +11308,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46266</v>
+        <v>45547</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11329,7 +11324,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11372,7 +11367,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 25597-2026</t>
+          <t>A 10908-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11386,10 +11381,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46177</v>
+        <v>46079</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11402,7 +11397,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11445,7 +11440,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 25605-2026</t>
+          <t>A 11811-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11459,10 +11454,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46177</v>
+        <v>45727</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11475,7 +11470,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11518,7 +11513,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 37743-2026</t>
+          <t>A 35792-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11532,10 +11527,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46279</v>
+        <v>45861</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11547,8 +11542,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11591,7 +11591,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 38074-2026</t>
+          <t>A 35971-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11605,10 +11605,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46280</v>
+        <v>45863</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11681,7 +11681,7 @@
         <v>45537</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>

--- a/Översikt TOMELILLA.xlsx
+++ b/Översikt TOMELILLA.xlsx
@@ -601,7 +601,7 @@
         <v>44756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45120</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45260</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2018-2024</t>
+          <t>A 14152-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45308</v>
+        <v>45009</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>17.2</v>
+        <v>3.5</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1125,10 +1125,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1140,153 +1140,153 @@
         <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Kråka
+Röd glada</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 14152-2023 artfynd.xlsx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 14152-2023 karta.png", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 14152-2023 georefererad karta.tif", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 14152-2023 FSC-klagomål.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 14152-2023 FSC-klagomål mail.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 14152-2023 tillsynsbegäran.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 14152-2023 tillsynsbegäran mail.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 14152-2023 prioriterade fågelarter.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 2018-2024</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45308</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TOMELILLA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Västlig hakmossa
 Röd glada</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2018-2024 artfynd.xlsx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2018-2024 karta.png", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2018-2024 georefererad karta.tif", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2018-2024 FSC-klagomål.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2018-2024 FSC-klagomål mail.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2018-2024 tillsynsbegäran.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2018-2024 tillsynsbegäran mail.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 2018-2024 prioriterade fågelarter.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 14152-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45009</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>TOMELILLA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Kråka
-Röd glada</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 14152-2023 artfynd.xlsx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 14152-2023 karta.png", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 14152-2023 georefererad karta.tif", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 14152-2023 FSC-klagomål.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 14152-2023 FSC-klagomål mail.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 14152-2023 tillsynsbegäran.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 14152-2023 tillsynsbegäran mail.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 14152-2023 prioriterade fågelarter.docx", "A 14152-2023")</f>
         <v/>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
         <v>45299</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>45429</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45744</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>44613</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>44721</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>45337</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 2193-2022</t>
+          <t>A 49813-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44578</v>
+        <v>45940</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1979,22 +1979,17 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2009,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2021,46 +2016,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Skogslysing</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2193-2022 artfynd.xlsx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 49813-2025 artfynd.xlsx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2193-2022 karta.png", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 49813-2025 karta.png", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2193-2022 georefererad karta.tif", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 49813-2025 georefererad karta.tif", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2193-2022 FSC-klagomål.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 49813-2025 FSC-klagomål.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2193-2022 FSC-klagomål mail.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 49813-2025 FSC-klagomål mail.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2193-2022 tillsynsbegäran.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 49813-2025 tillsynsbegäran.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2193-2022 tillsynsbegäran mail.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 49813-2025 tillsynsbegäran mail.docx", "A 49813-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 6262-2024</t>
+          <t>A 61314-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2074,10 +2069,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45337</v>
+        <v>46000</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2090,7 +2085,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2126,46 +2121,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6262-2024 artfynd.xlsx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6262-2024 karta.png", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6262-2024 georefererad karta.tif", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6262-2024 FSC-klagomål.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6262-2024 FSC-klagomål mail.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6262-2024 tillsynsbegäran.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6262-2024 tillsynsbegäran mail.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 49813-2025</t>
+          <t>A 2193-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2179,10 +2174,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45940</v>
+        <v>44578</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2194,18 +2189,23 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2231,46 +2231,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Skogslysing</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 49813-2025 artfynd.xlsx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2193-2022 artfynd.xlsx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 49813-2025 karta.png", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2193-2022 karta.png", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 49813-2025 georefererad karta.tif", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2193-2022 georefererad karta.tif", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 49813-2025 FSC-klagomål.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2193-2022 FSC-klagomål.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 49813-2025 FSC-klagomål mail.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2193-2022 FSC-klagomål mail.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 49813-2025 tillsynsbegäran.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2193-2022 tillsynsbegäran.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 49813-2025 tillsynsbegäran mail.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2193-2022 tillsynsbegäran mail.docx", "A 2193-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 61314-2025</t>
+          <t>A 6261-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46000</v>
+        <v>45337</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2300,13 +2300,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>12.6</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2336,46 +2336,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 60820-2023</t>
+          <t>A 26958-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2389,10 +2389,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45260</v>
+        <v>45811</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2445,42 +2445,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 60820-2023 artfynd.xlsx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26958-2025 artfynd.xlsx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 60820-2023 karta.png", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26958-2025 karta.png", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 60820-2023 georefererad karta.tif", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26958-2025 georefererad karta.tif", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 60820-2023 FSC-klagomål.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26958-2025 FSC-klagomål.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 60820-2023 FSC-klagomål mail.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26958-2025 FSC-klagomål mail.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 60820-2023 tillsynsbegäran.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26958-2025 tillsynsbegäran.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 60820-2023 tillsynsbegäran mail.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26958-2025 tillsynsbegäran mail.docx", "A 26958-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 28862-2023</t>
+          <t>A 6262-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45104</v>
+        <v>45337</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2509,13 +2509,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2551,46 +2546,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6262-2024 artfynd.xlsx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6262-2024 karta.png", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 28862-2023 georefererad karta.tif", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6262-2024 georefererad karta.tif", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 28862-2023 FSC-klagomål.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6262-2024 FSC-klagomål.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 28862-2023 FSC-klagomål mail.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6262-2024 FSC-klagomål mail.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 28862-2023 tillsynsbegäran.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6262-2024 tillsynsbegäran.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 28862-2023 tillsynsbegäran mail.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6262-2024 tillsynsbegäran mail.docx", "A 6262-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 756-2024</t>
+          <t>A 28862-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2604,10 +2599,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45300</v>
+        <v>45104</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2625,16 +2620,16 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>13.1</v>
+        <v>6.6</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2649,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2665,35 +2660,35 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 756-2024 artfynd.xlsx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 756-2024 karta.png", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 756-2024 georefererad karta.tif", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 28862-2023 georefererad karta.tif", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 756-2024 FSC-klagomål.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 28862-2023 FSC-klagomål.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 756-2024 FSC-klagomål mail.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 28862-2023 FSC-klagomål mail.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 756-2024 tillsynsbegäran.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 28862-2023 tillsynsbegäran.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 756-2024 tillsynsbegäran mail.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 28862-2023 tillsynsbegäran mail.docx", "A 28862-2023")</f>
         <v/>
       </c>
     </row>
@@ -2717,7 +2712,7 @@
         <v>46139</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2805,7 +2800,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 42387-2022</t>
+          <t>A 60820-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2819,10 +2814,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44830</v>
+        <v>45260</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2835,16 +2830,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2859,7 +2854,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2875,42 +2870,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 42387-2022 artfynd.xlsx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 60820-2023 artfynd.xlsx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 42387-2022 karta.png", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 60820-2023 karta.png", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 42387-2022 georefererad karta.tif", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 60820-2023 georefererad karta.tif", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 42387-2022 FSC-klagomål.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 60820-2023 FSC-klagomål.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 42387-2022 FSC-klagomål mail.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 60820-2023 FSC-klagomål mail.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 42387-2022 tillsynsbegäran.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 60820-2023 tillsynsbegäran.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 42387-2022 tillsynsbegäran mail.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 60820-2023 tillsynsbegäran mail.docx", "A 60820-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 26823-2026</t>
+          <t>A 42387-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2924,10 +2919,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46183</v>
+        <v>44830</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2940,7 +2935,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>12.1</v>
+        <v>1.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2980,42 +2975,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26823-2026 artfynd.xlsx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 42387-2022 artfynd.xlsx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26823-2026 karta.png", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 42387-2022 karta.png", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26823-2026 georefererad karta.tif", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 42387-2022 georefererad karta.tif", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26823-2026 FSC-klagomål.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 42387-2022 FSC-klagomål.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26823-2026 FSC-klagomål mail.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 42387-2022 FSC-klagomål mail.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26823-2026 tillsynsbegäran.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 42387-2022 tillsynsbegäran.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26823-2026 tillsynsbegäran mail.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 42387-2022 tillsynsbegäran mail.docx", "A 42387-2022")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 17907-2024</t>
+          <t>A 756-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3029,10 +3024,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45419</v>
+        <v>45300</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3044,8 +3039,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>13.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3081,46 +3081,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Gulplister</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 17907-2024 artfynd.xlsx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 756-2024 artfynd.xlsx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 17907-2024 karta.png", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 756-2024 karta.png", "A 756-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 17907-2024 georefererad karta.tif", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 756-2024 georefererad karta.tif", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 17907-2024 FSC-klagomål.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 756-2024 FSC-klagomål.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 17907-2024 FSC-klagomål mail.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 756-2024 FSC-klagomål mail.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 17907-2024 tillsynsbegäran.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 756-2024 tillsynsbegäran.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 17907-2024 tillsynsbegäran mail.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 756-2024 tillsynsbegäran mail.docx", "A 756-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32949-2026</t>
+          <t>A 26823-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3134,10 +3134,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46244</v>
+        <v>46183</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3150,17 +3150,17 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.8</v>
+        <v>12.1</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
@@ -3174,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3190,46 +3190,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 32949-2026 artfynd.xlsx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26823-2026 artfynd.xlsx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 32949-2026 karta.png", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26823-2026 karta.png", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 32949-2026 georefererad karta.tif", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26823-2026 georefererad karta.tif", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 32949-2026 FSC-klagomål.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26823-2026 FSC-klagomål.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 32949-2026 FSC-klagomål mail.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26823-2026 FSC-klagomål mail.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 32949-2026 tillsynsbegäran.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26823-2026 tillsynsbegäran.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 32949-2026 tillsynsbegäran mail.docx", "A 32949-2026")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 32949-2026 prioriterade fågelarter.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26823-2026 tillsynsbegäran mail.docx", "A 26823-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 6261-2024</t>
+          <t>A 32949-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3243,10 +3239,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45337</v>
+        <v>46244</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3259,13 +3255,13 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>12.6</v>
+        <v>4.8</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3295,46 +3291,50 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 32949-2026 artfynd.xlsx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 32949-2026 karta.png", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 32949-2026 georefererad karta.tif", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 32949-2026 FSC-klagomål.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 32949-2026 FSC-klagomål mail.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 32949-2026 tillsynsbegäran.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 32949-2026 tillsynsbegäran mail.docx", "A 32949-2026")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 32949-2026 prioriterade fågelarter.docx", "A 32949-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 26958-2025</t>
+          <t>A 17907-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45811</v>
+        <v>45419</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3364,13 +3364,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3400,39 +3400,39 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Gulplister</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26958-2025 artfynd.xlsx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 17907-2024 artfynd.xlsx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26958-2025 karta.png", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 17907-2024 karta.png", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26958-2025 georefererad karta.tif", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 17907-2024 georefererad karta.tif", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26958-2025 FSC-klagomål.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 17907-2024 FSC-klagomål.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26958-2025 FSC-klagomål mail.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 17907-2024 FSC-klagomål mail.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26958-2025 tillsynsbegäran.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 17907-2024 tillsynsbegäran.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26958-2025 tillsynsbegäran mail.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 17907-2024 tillsynsbegäran mail.docx", "A 17907-2024")</f>
         <v/>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
         <v>44684</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44560</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44490</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44642</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44721</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 36180-2024</t>
+          <t>A 47231-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45534</v>
+        <v>45202</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4038,7 +4038,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 2548-2024</t>
+          <t>A 11802-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45313</v>
+        <v>45375</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4067,8 +4067,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4111,7 +4116,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 13159-2024</t>
+          <t>A 4023-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4125,10 +4130,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45386</v>
+        <v>45323</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4140,8 +4145,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>15.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4184,7 +4194,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 2555-2022</t>
+          <t>A 19454-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4198,10 +4208,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44579</v>
+        <v>45429</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4214,7 +4224,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4257,7 +4267,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 743-2024</t>
+          <t>A 23813-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4271,10 +4281,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45300</v>
+        <v>45455</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4286,13 +4296,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>11.1</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4335,7 +4340,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 15075-2024</t>
+          <t>A 24248-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4345,14 +4350,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45399</v>
+        <v>45457</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4365,7 +4370,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4408,7 +4413,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 11887-2024</t>
+          <t>A 2548-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4422,10 +4427,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45376</v>
+        <v>45313</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4437,13 +4442,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>6.3</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4486,7 +4486,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 10272-2023</t>
+          <t>A 17760-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44986</v>
+        <v>45758</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4515,13 +4515,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>7.7</v>
+        <v>3.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4564,7 +4559,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 15012-2024</t>
+          <t>A 44675-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4574,14 +4569,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45399</v>
+        <v>45574</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4593,8 +4588,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>6.9</v>
+        <v>11.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4637,7 +4637,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 47231-2023</t>
+          <t>A 38787-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4651,10 +4651,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45202</v>
+        <v>45547</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4710,7 +4710,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8190-2024</t>
+          <t>A 17316-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45338</v>
+        <v>45414</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4741,11 +4741,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 8192-2024</t>
+          <t>A 15158-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4802,10 +4802,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45338</v>
+        <v>45744</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4817,13 +4817,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4866,7 +4861,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 578-2024</t>
+          <t>A 45729-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4880,10 +4875,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45299</v>
+        <v>45579</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4895,13 +4890,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>67.40000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4944,7 +4934,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 28966-2022</t>
+          <t>A 49815-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4954,14 +4944,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44749</v>
+        <v>45940</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4974,7 +4964,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5017,7 +5007,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 6357-2024</t>
+          <t>A 43306-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5031,10 +5021,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45338</v>
+        <v>45910</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5046,13 +5036,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5095,7 +5080,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 23813-2024</t>
+          <t>A 4969-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5109,10 +5094,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45455</v>
+        <v>46049</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5124,8 +5109,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5168,7 +5158,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 19454-2024</t>
+          <t>A 16568-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5182,10 +5172,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45429</v>
+        <v>45408</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5198,7 +5188,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5241,7 +5231,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 59528-2022</t>
+          <t>A 12310-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5255,10 +5245,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44907</v>
+        <v>44999</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5272,11 +5262,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5319,7 +5309,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30673-2023</t>
+          <t>A 60817-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5333,10 +5323,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45112</v>
+        <v>45260</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5348,13 +5338,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5397,7 +5382,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 1199-2024</t>
+          <t>A 7955-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5411,10 +5396,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45302</v>
+        <v>45350</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5426,13 +5411,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>16.1</v>
+        <v>2.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5475,7 +5455,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 15158-2025</t>
+          <t>A 42794-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5489,10 +5469,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45744</v>
+        <v>45566</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5505,7 +5485,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5548,7 +5528,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 4018-2024</t>
+          <t>A 48171-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5562,10 +5542,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45323</v>
+        <v>45933</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5577,13 +5557,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5626,7 +5601,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 61841-2025</t>
+          <t>A 61970-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5636,14 +5611,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5656,7 +5631,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5699,7 +5674,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 43306-2025</t>
+          <t>A 2190-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5713,10 +5688,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45910</v>
+        <v>44578</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5728,8 +5703,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.3</v>
+        <v>4.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5772,7 +5752,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 6259-2024</t>
+          <t>A 10272-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5786,10 +5766,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45337</v>
+        <v>44986</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5801,8 +5781,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>7.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5845,7 +5830,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 6316-2024</t>
+          <t>A 55676-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5859,10 +5844,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45338</v>
+        <v>44888</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5874,13 +5859,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>28.6</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5923,7 +5903,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 4482-2026</t>
+          <t>A 39791-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5937,10 +5917,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46045</v>
+        <v>45891</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5952,13 +5932,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6001,7 +5976,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 42794-2024</t>
+          <t>A 30806-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6015,10 +5990,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45566</v>
+        <v>45112</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6030,8 +6005,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6074,7 +6054,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 48171-2025</t>
+          <t>A 6124-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6088,10 +6068,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45933</v>
+        <v>46053</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6104,7 +6084,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6147,7 +6127,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 39791-2025</t>
+          <t>A 16621-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6161,10 +6141,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45891</v>
+        <v>46112</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6176,8 +6156,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>3.8</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6220,7 +6205,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 4188-2024</t>
+          <t>A 6316-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6234,10 +6219,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45324</v>
+        <v>45338</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6255,7 +6240,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>9.6</v>
+        <v>28.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6298,7 +6283,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 2190-2022</t>
+          <t>A 8455-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6312,10 +6297,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44578</v>
+        <v>45354</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6329,11 +6314,11 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6376,7 +6361,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 53977-2022</t>
+          <t>A 13159-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6390,10 +6375,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44876</v>
+        <v>45386</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6406,7 +6391,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6449,7 +6434,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 12903-2024</t>
+          <t>A 61841-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6463,10 +6448,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45385</v>
+        <v>46003</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6479,7 +6464,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>9.199999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6522,7 +6507,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 17151-2024</t>
+          <t>A 49913-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6532,14 +6517,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45412</v>
+        <v>45940</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6551,13 +6536,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6600,7 +6580,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 30040-2024</t>
+          <t>A 11811-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6610,14 +6590,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45488</v>
+        <v>45727</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6630,7 +6610,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6673,7 +6653,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 6852-2026</t>
+          <t>A 7745-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6683,14 +6663,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46057</v>
+        <v>45706</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6702,13 +6682,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>4.8</v>
+        <v>0.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6751,7 +6726,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 49913-2025</t>
+          <t>A 15921-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6761,14 +6736,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45940</v>
+        <v>45749</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6781,7 +6756,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6824,7 +6799,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 16483-2024</t>
+          <t>A 4482-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6838,10 +6813,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45408</v>
+        <v>46045</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6853,8 +6828,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>6.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6897,7 +6877,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 21291-2026</t>
+          <t>A 6852-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6911,10 +6891,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46147</v>
+        <v>46057</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6926,8 +6906,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6970,7 +6955,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 21293-2026</t>
+          <t>A 15305-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6980,14 +6965,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46147</v>
+        <v>45746</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7000,7 +6985,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7043,7 +7028,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 12663-2022</t>
+          <t>A 28966-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7053,14 +7038,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44641</v>
+        <v>44749</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7072,13 +7057,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>12.4</v>
+        <v>3.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7121,7 +7101,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 30806-2023</t>
+          <t>A 578-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7135,10 +7115,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45112</v>
+        <v>45299</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7156,7 +7136,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7199,7 +7179,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 15288-2026</t>
+          <t>A 21291-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7213,10 +7193,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46105</v>
+        <v>46147</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7229,7 +7209,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7272,7 +7252,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 17316-2024</t>
+          <t>A 21293-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7286,10 +7266,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45414</v>
+        <v>46147</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7301,13 +7281,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7350,7 +7325,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 39796-2025</t>
+          <t>A 12988-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7364,10 +7339,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45891</v>
+        <v>45385</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7379,8 +7354,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>3.9</v>
+        <v>16.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7423,7 +7403,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 31993-2023</t>
+          <t>A 15288-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7437,10 +7417,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45119</v>
+        <v>46105</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7453,7 +7433,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7496,7 +7476,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 16568-2024</t>
+          <t>A 39796-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7510,10 +7490,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45408</v>
+        <v>45891</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7526,7 +7506,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7586,7 +7566,7 @@
         <v>44952</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7642,7 +7622,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 49815-2025</t>
+          <t>A 4018-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7656,10 +7636,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45940</v>
+        <v>45323</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7671,8 +7651,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7715,7 +7700,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 4969-2026</t>
+          <t>A 16611-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7729,10 +7714,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46049</v>
+        <v>46112</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7746,11 +7731,11 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7793,7 +7778,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 11802-2024</t>
+          <t>A 35792-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7807,10 +7792,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45375</v>
+        <v>45861</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7828,7 +7813,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7871,7 +7856,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 11894-2024</t>
+          <t>A 35971-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7885,10 +7870,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45376</v>
+        <v>45863</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7900,13 +7885,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7949,7 +7929,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 24248-2024</t>
+          <t>A 24002-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7959,14 +7939,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45457</v>
+        <v>46167</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7979,7 +7959,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>6.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8022,7 +8002,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 16611-2026</t>
+          <t>A 15296-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8036,10 +8016,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46112</v>
+        <v>46105</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8051,13 +8031,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8100,7 +8075,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 5027-2024</t>
+          <t>A 15012-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8114,10 +8089,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45329</v>
+        <v>45399</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8129,13 +8104,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>4.7</v>
+        <v>6.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8178,7 +8148,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 61970-2025</t>
+          <t>A 2555-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8188,14 +8158,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46003</v>
+        <v>44579</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8208,7 +8178,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8251,7 +8221,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 24002-2026</t>
+          <t>A 4651-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8261,14 +8231,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46167</v>
+        <v>45328</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8281,7 +8251,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>6.4</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8324,7 +8294,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 15296-2026</t>
+          <t>A 30040-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8334,14 +8304,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46105</v>
+        <v>45488</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8354,7 +8324,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.3</v>
+        <v>4.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8397,7 +8367,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 12181-2023</t>
+          <t>A 6357-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8411,10 +8381,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44998</v>
+        <v>45338</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8426,8 +8396,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8470,7 +8445,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 6124-2026</t>
+          <t>A 23621-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8484,10 +8459,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46053</v>
+        <v>46162</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8500,7 +8475,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8543,7 +8518,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 16621-2026</t>
+          <t>A 30673-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8557,10 +8532,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46112</v>
+        <v>45112</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8574,11 +8549,11 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8621,7 +8596,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 38562-2023</t>
+          <t>A 24987-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8635,10 +8610,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45162</v>
+        <v>46174</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8651,7 +8626,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8694,7 +8669,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 17778-2024</t>
+          <t>A 31993-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8708,10 +8683,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45418</v>
+        <v>45119</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8723,13 +8698,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>6.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8772,7 +8742,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 44675-2024</t>
+          <t>A 11894-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8782,14 +8752,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45574</v>
+        <v>45376</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8803,11 +8773,11 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>11.2</v>
+        <v>4.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8850,7 +8820,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 26473-2024</t>
+          <t>A 16483-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8864,10 +8834,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45469</v>
+        <v>45408</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8880,7 +8850,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8923,7 +8893,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 51031-2023</t>
+          <t>A 31134-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8937,10 +8907,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45211</v>
+        <v>46216</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8952,8 +8922,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8996,7 +8971,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 7745-2025</t>
+          <t>A 38562-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9006,14 +8981,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45706</v>
+        <v>45162</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9026,7 +9001,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9069,7 +9044,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 23621-2026</t>
+          <t>A 51031-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9083,10 +9058,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46162</v>
+        <v>45211</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9099,7 +9074,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9142,7 +9117,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 5565-2024</t>
+          <t>A 59528-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9156,10 +9131,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45334</v>
+        <v>44907</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9171,8 +9146,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9215,7 +9195,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 23310-2022</t>
+          <t>A 16027-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9229,10 +9209,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44720</v>
+        <v>44665</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9250,7 +9230,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>5.3</v>
+        <v>1.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9293,7 +9273,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 24987-2026</t>
+          <t>A 35897-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9307,10 +9287,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46174</v>
+        <v>46266</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9323,7 +9303,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9366,7 +9346,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 7955-2024</t>
+          <t>A 6259-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9380,10 +9360,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45350</v>
+        <v>45337</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9396,7 +9376,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9439,7 +9419,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 55676-2022</t>
+          <t>A 1199-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9453,10 +9433,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44888</v>
+        <v>45302</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9468,8 +9448,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>16.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9512,7 +9497,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 31134-2026</t>
+          <t>A 25597-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9526,10 +9511,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46216</v>
+        <v>46177</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9541,13 +9526,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9590,7 +9570,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 8455-2024</t>
+          <t>A 25605-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9604,10 +9584,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45354</v>
+        <v>46177</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9619,13 +9599,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>5.1</v>
+        <v>1.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9668,7 +9643,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 16027-2022</t>
+          <t>A 26473-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9682,10 +9657,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44665</v>
+        <v>45469</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9697,13 +9672,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9746,7 +9716,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 35897-2026</t>
+          <t>A 17778-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9760,10 +9730,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46266</v>
+        <v>45418</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9775,8 +9745,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9819,7 +9794,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 4651-2024</t>
+          <t>A 37743-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9833,10 +9808,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45328</v>
+        <v>46279</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9849,7 +9824,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9892,7 +9867,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 12988-2024</t>
+          <t>A 38074-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9906,10 +9881,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45385</v>
+        <v>46280</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9921,13 +9896,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>16.2</v>
+        <v>4.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9970,7 +9940,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 15305-2025</t>
+          <t>A 8190-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9980,14 +9950,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45746</v>
+        <v>45338</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9999,8 +9969,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10043,7 +10018,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 60817-2023</t>
+          <t>A 8192-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10057,10 +10032,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45260</v>
+        <v>45338</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10072,8 +10047,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10116,7 +10096,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 4023-2024</t>
+          <t>A 17151-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10130,10 +10110,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45323</v>
+        <v>45412</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10151,7 +10131,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>15.2</v>
+        <v>3.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10194,7 +10174,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 25597-2026</t>
+          <t>A 32955-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10208,10 +10188,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46177</v>
+        <v>46244</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10224,7 +10204,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10267,7 +10247,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 25605-2026</t>
+          <t>A 32948-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10281,10 +10261,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46177</v>
+        <v>46244</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10297,7 +10277,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10340,7 +10320,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 38074-2026</t>
+          <t>A 12181-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10354,10 +10334,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46280</v>
+        <v>44998</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10370,7 +10350,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10413,7 +10393,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 12310-2023</t>
+          <t>A 10908-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10427,10 +10407,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44999</v>
+        <v>46079</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10442,13 +10422,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10491,7 +10466,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 37743-2026</t>
+          <t>A 23310-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10505,10 +10480,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46279</v>
+        <v>44720</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10520,8 +10495,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10564,7 +10544,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 15921-2025</t>
+          <t>A 5027-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10578,10 +10558,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45749</v>
+        <v>45329</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10593,8 +10573,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10637,7 +10622,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 35742-2024</t>
+          <t>A 743-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10651,10 +10636,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45532</v>
+        <v>45300</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10666,8 +10651,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>11.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10710,7 +10700,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 35715-2024</t>
+          <t>A 53977-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10724,10 +10714,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45532</v>
+        <v>44876</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10740,7 +10730,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10783,7 +10773,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 11806-2025</t>
+          <t>A 4188-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10797,10 +10787,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45727</v>
+        <v>45324</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10812,8 +10802,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>3.1</v>
+        <v>9.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10856,7 +10851,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 11810-2025</t>
+          <t>A 12663-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10870,10 +10865,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45727</v>
+        <v>44641</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10885,8 +10880,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>2.9</v>
+        <v>12.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10929,7 +10929,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 32948-2026</t>
+          <t>A 36180-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10943,10 +10943,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46244</v>
+        <v>45534</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11002,7 +11002,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 32955-2026</t>
+          <t>A 12903-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11016,10 +11016,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46244</v>
+        <v>45385</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11075,7 +11075,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 23185-2025</t>
+          <t>A 15075-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11085,14 +11085,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45791</v>
+        <v>45399</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11148,7 +11148,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 17760-2025</t>
+          <t>A 11887-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11162,10 +11162,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45758</v>
+        <v>45376</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11177,8 +11177,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>3.7</v>
+        <v>6.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11221,7 +11226,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 45729-2024</t>
+          <t>A 5565-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11235,10 +11240,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45579</v>
+        <v>45334</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11251,7 +11256,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>10.1</v>
+        <v>2.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11294,7 +11299,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 38787-2024</t>
+          <t>A 35742-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11308,10 +11313,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45547</v>
+        <v>45532</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11324,7 +11329,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11367,7 +11372,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 10908-2026</t>
+          <t>A 35715-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11381,10 +11386,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46079</v>
+        <v>45532</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11397,7 +11402,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11440,7 +11445,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 11811-2025</t>
+          <t>A 11806-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11457,7 +11462,7 @@
         <v>45727</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11470,7 +11475,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>9.699999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11513,7 +11518,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 35792-2025</t>
+          <t>A 11810-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11527,10 +11532,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45861</v>
+        <v>45727</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11542,13 +11547,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11591,7 +11591,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 35971-2025</t>
+          <t>A 23185-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11601,14 +11601,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45863</v>
+        <v>45791</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11681,7 +11681,7 @@
         <v>45537</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>

--- a/Översikt TOMELILLA.xlsx
+++ b/Översikt TOMELILLA.xlsx
@@ -601,7 +601,7 @@
         <v>44756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45120</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45260</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>45009</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>45308</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45299</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>45429</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45744</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>44613</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>44721</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>45337</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>45940</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>46000</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>44578</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>45337</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>45811</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45337</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>45104</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>46139</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>45260</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>44830</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>45300</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>46183</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>46244</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45419</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>44684</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44560</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44490</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44642</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44721</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>45202</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>45375</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>45323</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>45429</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>45455</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>45457</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>45313</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>45758</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>45574</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>45547</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>45414</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45744</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45579</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45940</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45910</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>46049</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>45408</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>44999</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>45260</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>45350</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>45566</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>45933</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>46003</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>44578</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>44986</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>44888</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>45891</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45112</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>46053</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>46112</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>45338</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>45354</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>45386</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>46003</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>45940</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>45727</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>45706</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>45749</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>46045</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>46057</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>45746</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>44749</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>45299</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>46147</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>46147</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>45385</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>46105</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>45891</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>44952</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>45323</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>46112</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>45861</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>45863</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>46167</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>46105</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>45399</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>44579</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>45328</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>45488</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>45338</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         <v>46162</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>45112</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>46174</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>45119</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>45376</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>45408</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>46216</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>45162</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>45211</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44907</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>44665</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>46266</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>45337</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>45302</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
         <v>46177</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
         <v>46177</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>45469</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>45418</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>46279</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>46280</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>45338</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>45338</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>45412</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>46244</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         <v>46244</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
         <v>44998</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>46079</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>44720</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>45329</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10639,7 +10639,7 @@
         <v>45300</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>44876</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>45324</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>44641</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>45534</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>45385</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>45399</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>45376</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>45334</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>45532</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>45532</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>45727</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>45727</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>45791</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>45537</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>

--- a/Översikt TOMELILLA.xlsx
+++ b/Översikt TOMELILLA.xlsx
@@ -601,7 +601,7 @@
         <v>44756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45120</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45260</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>45009</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>45308</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45299</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>45429</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45744</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>44613</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>44721</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>45337</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>45940</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>46000</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>44578</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>45337</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>45811</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45337</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>45104</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>46139</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>45260</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>44830</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>45300</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>46183</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>46244</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45419</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>44684</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44560</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44490</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44642</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44721</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>45202</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>45375</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>45323</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>45429</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>45455</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>45457</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>45313</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>45758</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>45574</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>45547</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>45414</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45744</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45579</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45940</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45910</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>46049</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>45408</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>44999</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>45260</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>45350</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>45566</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>45933</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>46003</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>44578</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>44986</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>44888</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>45891</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45112</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>46053</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>46112</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>45338</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>45354</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>45386</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>46003</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>45940</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>45727</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>45706</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>45749</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>46045</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>46057</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>45746</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>44749</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>45299</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>46147</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>46147</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>45385</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>46105</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>45891</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>44952</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>45323</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>46112</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>45861</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>45863</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>46167</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>46105</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>45399</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>44579</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>45328</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>45488</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>45338</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         <v>46162</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>45112</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>46174</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>45119</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>45376</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>45408</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>46216</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>45162</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>45211</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44907</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>44665</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>46266</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>45337</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>45302</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
         <v>46177</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
         <v>46177</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>45469</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>45418</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>46279</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>46280</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>45338</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>45338</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>45412</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>46244</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         <v>46244</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
         <v>44998</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>46079</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>44720</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>45329</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10639,7 +10639,7 @@
         <v>45300</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>44876</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>45324</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>44641</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>45534</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>45385</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>45399</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>45376</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>45334</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>45532</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>45532</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>45727</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>45727</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>45791</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>45537</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>

--- a/Översikt TOMELILLA.xlsx
+++ b/Översikt TOMELILLA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE138"/>
+  <dimension ref="A1:AE140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45120</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45260</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 14152-2023</t>
+          <t>A 2018-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45009</v>
+        <v>45308</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.5</v>
+        <v>17.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1125,10 +1125,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1140,153 +1140,153 @@
         <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Västlig hakmossa
+Röd glada</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2018-2024 artfynd.xlsx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2018-2024 karta.png", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2018-2024 georefererad karta.tif", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2018-2024 FSC-klagomål.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2018-2024 FSC-klagomål mail.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2018-2024 tillsynsbegäran.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2018-2024 tillsynsbegäran mail.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 2018-2024 prioriterade fågelarter.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 14152-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45009</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TOMELILLA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Kråka
 Röd glada</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 14152-2023 artfynd.xlsx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 14152-2023 karta.png", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 14152-2023 georefererad karta.tif", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 14152-2023 FSC-klagomål.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 14152-2023 FSC-klagomål mail.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 14152-2023 tillsynsbegäran.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 14152-2023 tillsynsbegäran mail.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 14152-2023 prioriterade fågelarter.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 2018-2024</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45308</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>TOMELILLA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Västlig hakmossa
-Röd glada</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2018-2024 artfynd.xlsx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2018-2024 karta.png", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2018-2024 georefererad karta.tif", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2018-2024 FSC-klagomål.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2018-2024 FSC-klagomål mail.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2018-2024 tillsynsbegäran.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2018-2024 tillsynsbegäran mail.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 2018-2024 prioriterade fågelarter.docx", "A 2018-2024")</f>
         <v/>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
         <v>45299</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>45429</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45744</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>44613</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>44721</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 6261-2024</t>
+          <t>A 17907-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45337</v>
+        <v>45419</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1875,13 +1875,13 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>12.6</v>
+        <v>3.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1915,42 +1915,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Gulplister</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 17907-2024 artfynd.xlsx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 17907-2024 karta.png", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 17907-2024 georefererad karta.tif", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 17907-2024 FSC-klagomål.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 17907-2024 FSC-klagomål mail.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 17907-2024 tillsynsbegäran.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 17907-2024 tillsynsbegäran mail.docx", "A 17907-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 49813-2025</t>
+          <t>A 6261-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45940</v>
+        <v>45337</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1980,13 +1980,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.5</v>
+        <v>12.6</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -2016,46 +2016,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 49813-2025 artfynd.xlsx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 49813-2025 karta.png", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 49813-2025 georefererad karta.tif", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 49813-2025 FSC-klagomål.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 49813-2025 FSC-klagomål mail.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 49813-2025 tillsynsbegäran.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 49813-2025 tillsynsbegäran mail.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 61314-2025</t>
+          <t>A 6261-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46000</v>
+        <v>45337</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2085,13 +2085,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>12.6</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2121,46 +2121,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 2193-2022</t>
+          <t>A 26958-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44578</v>
+        <v>45811</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2189,22 +2189,17 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2219,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2231,46 +2226,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Skogslysing</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2193-2022 artfynd.xlsx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26958-2025 artfynd.xlsx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2193-2022 karta.png", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26958-2025 karta.png", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2193-2022 georefererad karta.tif", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26958-2025 georefererad karta.tif", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2193-2022 FSC-klagomål.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26958-2025 FSC-klagomål.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2193-2022 FSC-klagomål mail.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26958-2025 FSC-klagomål mail.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2193-2022 tillsynsbegäran.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26958-2025 tillsynsbegäran.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2193-2022 tillsynsbegäran mail.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26958-2025 tillsynsbegäran mail.docx", "A 26958-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6261-2024</t>
+          <t>A 49813-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2284,10 +2279,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45337</v>
+        <v>45940</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2300,13 +2295,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>12.6</v>
+        <v>4.5</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2336,46 +2331,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 49813-2025 artfynd.xlsx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 49813-2025 karta.png", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 49813-2025 georefererad karta.tif", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 49813-2025 FSC-klagomål.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 49813-2025 FSC-klagomål mail.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 49813-2025 tillsynsbegäran.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 49813-2025 tillsynsbegäran mail.docx", "A 49813-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 26958-2025</t>
+          <t>A 61314-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2389,10 +2384,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45811</v>
+        <v>46000</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2405,13 +2400,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2445,42 +2440,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26958-2025 artfynd.xlsx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26958-2025 karta.png", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26958-2025 georefererad karta.tif", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26958-2025 FSC-klagomål.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26958-2025 FSC-klagomål mail.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26958-2025 tillsynsbegäran.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26958-2025 tillsynsbegäran mail.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 6262-2024</t>
+          <t>A 2193-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2494,10 +2489,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45337</v>
+        <v>44578</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2509,18 +2504,23 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2550,42 +2550,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skogslysing</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6262-2024 artfynd.xlsx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2193-2022 artfynd.xlsx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6262-2024 karta.png", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2193-2022 karta.png", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6262-2024 georefererad karta.tif", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2193-2022 georefererad karta.tif", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6262-2024 FSC-klagomål.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2193-2022 FSC-klagomål.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6262-2024 FSC-klagomål mail.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2193-2022 FSC-klagomål mail.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6262-2024 tillsynsbegäran.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2193-2022 tillsynsbegäran.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6262-2024 tillsynsbegäran mail.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2193-2022 tillsynsbegäran mail.docx", "A 2193-2022")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 28862-2023</t>
+          <t>A 6262-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45104</v>
+        <v>45337</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2614,13 +2614,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2656,46 +2651,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6262-2024 artfynd.xlsx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6262-2024 karta.png", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 28862-2023 georefererad karta.tif", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6262-2024 georefererad karta.tif", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 28862-2023 FSC-klagomål.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6262-2024 FSC-klagomål.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 28862-2023 FSC-klagomål mail.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6262-2024 FSC-klagomål mail.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 28862-2023 tillsynsbegäran.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6262-2024 tillsynsbegäran.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 28862-2023 tillsynsbegäran mail.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6262-2024 tillsynsbegäran mail.docx", "A 6262-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 20397-2026</t>
+          <t>A 60820-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2709,10 +2704,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46139</v>
+        <v>45260</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2725,13 +2720,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2765,42 +2760,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 20397-2026 artfynd.xlsx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 60820-2023 artfynd.xlsx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 20397-2026 karta.png", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 60820-2023 karta.png", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 20397-2026 georefererad karta.tif", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 60820-2023 georefererad karta.tif", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 20397-2026 FSC-klagomål.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 60820-2023 FSC-klagomål.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 20397-2026 FSC-klagomål mail.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 60820-2023 FSC-klagomål mail.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 20397-2026 tillsynsbegäran.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 60820-2023 tillsynsbegäran.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 20397-2026 tillsynsbegäran mail.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 60820-2023 tillsynsbegäran mail.docx", "A 60820-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 60820-2023</t>
+          <t>A 28862-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2814,10 +2809,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45260</v>
+        <v>45104</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2829,14 +2824,19 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2870,42 +2870,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 60820-2023 artfynd.xlsx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 60820-2023 karta.png", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 60820-2023 georefererad karta.tif", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 28862-2023 georefererad karta.tif", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 60820-2023 FSC-klagomål.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 28862-2023 FSC-klagomål.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 60820-2023 FSC-klagomål mail.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 28862-2023 FSC-klagomål mail.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 60820-2023 tillsynsbegäran.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 28862-2023 tillsynsbegäran.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 60820-2023 tillsynsbegäran mail.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 28862-2023 tillsynsbegäran mail.docx", "A 28862-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 42387-2022</t>
+          <t>A 756-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2919,10 +2919,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44830</v>
+        <v>45300</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2934,8 +2934,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>13.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2975,42 +2980,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 42387-2022 artfynd.xlsx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 756-2024 artfynd.xlsx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 42387-2022 karta.png", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 756-2024 karta.png", "A 756-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 42387-2022 georefererad karta.tif", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 756-2024 georefererad karta.tif", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 42387-2022 FSC-klagomål.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 756-2024 FSC-klagomål.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 42387-2022 FSC-klagomål mail.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 756-2024 FSC-klagomål mail.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 42387-2022 tillsynsbegäran.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 756-2024 tillsynsbegäran.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 42387-2022 tillsynsbegäran mail.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 756-2024 tillsynsbegäran mail.docx", "A 756-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 756-2024</t>
+          <t>A 42387-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3024,10 +3029,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45300</v>
+        <v>44830</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3039,13 +3044,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>13.1</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3085,42 +3085,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 756-2024 artfynd.xlsx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 42387-2022 artfynd.xlsx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 756-2024 karta.png", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 42387-2022 karta.png", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 756-2024 georefererad karta.tif", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 42387-2022 georefererad karta.tif", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 756-2024 FSC-klagomål.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 42387-2022 FSC-klagomål.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 756-2024 FSC-klagomål mail.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 42387-2022 FSC-klagomål mail.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 756-2024 tillsynsbegäran.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 42387-2022 tillsynsbegäran.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 756-2024 tillsynsbegäran mail.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 42387-2022 tillsynsbegäran mail.docx", "A 42387-2022")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 26823-2026</t>
+          <t>A 20397-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3134,10 +3134,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46183</v>
+        <v>46139</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3150,16 +3150,16 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>12.1</v>
+        <v>4.2</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3174,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3190,42 +3190,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26823-2026 artfynd.xlsx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 20397-2026 artfynd.xlsx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26823-2026 karta.png", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 20397-2026 karta.png", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26823-2026 georefererad karta.tif", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 20397-2026 georefererad karta.tif", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26823-2026 FSC-klagomål.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 20397-2026 FSC-klagomål.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26823-2026 FSC-klagomål mail.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 20397-2026 FSC-klagomål mail.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26823-2026 tillsynsbegäran.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 20397-2026 tillsynsbegäran.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26823-2026 tillsynsbegäran mail.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 20397-2026 tillsynsbegäran mail.docx", "A 20397-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32949-2026</t>
+          <t>A 26823-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3239,10 +3239,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46244</v>
+        <v>46183</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3255,17 +3255,17 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.8</v>
+        <v>12.1</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
@@ -3279,7 +3279,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3295,46 +3295,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 32949-2026 artfynd.xlsx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26823-2026 artfynd.xlsx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 32949-2026 karta.png", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26823-2026 karta.png", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 32949-2026 georefererad karta.tif", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26823-2026 georefererad karta.tif", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 32949-2026 FSC-klagomål.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26823-2026 FSC-klagomål.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 32949-2026 FSC-klagomål mail.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26823-2026 FSC-klagomål mail.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 32949-2026 tillsynsbegäran.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26823-2026 tillsynsbegäran.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 32949-2026 tillsynsbegäran mail.docx", "A 32949-2026")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 32949-2026 prioriterade fågelarter.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26823-2026 tillsynsbegäran mail.docx", "A 26823-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 17907-2024</t>
+          <t>A 32949-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3348,10 +3344,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45419</v>
+        <v>46244</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3364,10 +3360,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3400,39 +3396,43 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Gulplister</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 17907-2024 artfynd.xlsx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 32949-2026 artfynd.xlsx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 17907-2024 karta.png", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 32949-2026 karta.png", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 17907-2024 georefererad karta.tif", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 32949-2026 georefererad karta.tif", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 17907-2024 FSC-klagomål.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 32949-2026 FSC-klagomål.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 17907-2024 FSC-klagomål mail.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 32949-2026 FSC-klagomål mail.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 17907-2024 tillsynsbegäran.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 32949-2026 tillsynsbegäran.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 17907-2024 tillsynsbegäran mail.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 32949-2026 tillsynsbegäran mail.docx", "A 32949-2026")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 32949-2026 prioriterade fågelarter.docx", "A 32949-2026")</f>
         <v/>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
         <v>44684</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44560</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44490</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44642</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44721</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 47231-2023</t>
+          <t>A 36180-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45202</v>
+        <v>45534</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4038,7 +4038,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 11802-2024</t>
+          <t>A 23185-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4048,14 +4048,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45375</v>
+        <v>45791</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4067,13 +4067,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4116,7 +4111,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 4023-2024</t>
+          <t>A 17760-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4130,10 +4125,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45323</v>
+        <v>45758</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4145,13 +4140,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>15.2</v>
+        <v>3.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4194,7 +4184,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 19454-2024</t>
+          <t>A 45729-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4208,10 +4198,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45429</v>
+        <v>45579</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4224,7 +4214,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>10.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4267,7 +4257,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 23813-2024</t>
+          <t>A 38787-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4281,10 +4271,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45455</v>
+        <v>45547</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4297,7 +4287,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4340,7 +4330,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 24248-2024</t>
+          <t>A 2548-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4354,10 +4344,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45457</v>
+        <v>45313</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4370,7 +4360,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4413,7 +4403,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2548-2024</t>
+          <t>A 13159-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4427,10 +4417,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45313</v>
+        <v>45386</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4443,7 +4433,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4486,7 +4476,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 17760-2025</t>
+          <t>A 2555-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4500,10 +4490,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45758</v>
+        <v>44579</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4516,7 +4506,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4559,7 +4549,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 44675-2024</t>
+          <t>A 743-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4569,14 +4559,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45574</v>
+        <v>45300</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4590,11 +4580,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4637,7 +4627,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38787-2024</t>
+          <t>A 15158-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4651,10 +4641,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45547</v>
+        <v>45744</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4667,7 +4657,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4710,7 +4700,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 17316-2024</t>
+          <t>A 15075-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4720,14 +4710,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45414</v>
+        <v>45399</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4739,13 +4729,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4788,7 +4773,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 15158-2025</t>
+          <t>A 43306-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4802,10 +4787,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45744</v>
+        <v>45910</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4818,7 +4803,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4861,7 +4846,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 45729-2024</t>
+          <t>A 11887-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4875,10 +4860,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45579</v>
+        <v>45376</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4890,8 +4875,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>10.1</v>
+        <v>6.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4934,7 +4924,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 49815-2025</t>
+          <t>A 10272-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4948,10 +4938,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45940</v>
+        <v>44986</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4963,8 +4953,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>7.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5007,7 +5002,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 43306-2025</t>
+          <t>A 11811-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5021,10 +5016,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45910</v>
+        <v>45727</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5037,7 +5032,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5080,7 +5075,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 4969-2026</t>
+          <t>A 15012-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5094,10 +5089,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46049</v>
+        <v>45399</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5109,13 +5104,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>2.6</v>
+        <v>6.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5158,7 +5148,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 16568-2024</t>
+          <t>A 48171-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5172,10 +5162,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45408</v>
+        <v>45933</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5188,7 +5178,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5231,7 +5221,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 12310-2023</t>
+          <t>A 8190-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5245,10 +5235,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44999</v>
+        <v>45338</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5262,11 +5252,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5309,7 +5299,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 60817-2023</t>
+          <t>A 8192-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5323,10 +5313,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45260</v>
+        <v>45338</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5338,8 +5328,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5382,7 +5377,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 7955-2024</t>
+          <t>A 47231-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5396,10 +5391,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45350</v>
+        <v>45202</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5412,7 +5407,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5455,7 +5450,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 42794-2024</t>
+          <t>A 28966-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5465,14 +5460,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45566</v>
+        <v>44749</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5485,7 +5480,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5528,7 +5523,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 48171-2025</t>
+          <t>A 39791-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5542,10 +5537,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45933</v>
+        <v>45891</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5558,7 +5553,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5601,7 +5596,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 61970-2025</t>
+          <t>A 578-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5611,14 +5606,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46003</v>
+        <v>45299</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5630,8 +5625,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5674,7 +5674,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 2190-2022</t>
+          <t>A 6357-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44578</v>
+        <v>45338</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5705,11 +5705,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.9</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5752,7 +5752,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 10272-2023</t>
+          <t>A 35792-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5766,10 +5766,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44986</v>
+        <v>45861</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>7.7</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5830,7 +5830,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55676-2022</t>
+          <t>A 35971-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5844,10 +5844,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44888</v>
+        <v>45863</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5903,7 +5903,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 39791-2025</t>
+          <t>A 23813-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45891</v>
+        <v>45455</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 30806-2023</t>
+          <t>A 19454-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45112</v>
+        <v>45429</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6005,13 +6005,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6054,7 +6049,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 6124-2026</t>
+          <t>A 59528-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6068,10 +6063,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46053</v>
+        <v>44907</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6083,8 +6078,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6127,7 +6127,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 16621-2026</t>
+          <t>A 30673-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6141,10 +6141,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46112</v>
+        <v>45112</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6158,11 +6158,11 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6205,7 +6205,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 6316-2024</t>
+          <t>A 49913-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6215,14 +6215,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45338</v>
+        <v>45940</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6234,13 +6234,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>28.6</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6283,7 +6278,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 8455-2024</t>
+          <t>A 49815-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6297,10 +6292,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45354</v>
+        <v>45940</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6312,13 +6307,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>5.1</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6361,7 +6351,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 13159-2024</t>
+          <t>A 1199-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6375,10 +6365,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45386</v>
+        <v>45302</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6390,8 +6380,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>1.3</v>
+        <v>16.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6434,7 +6429,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 61841-2025</t>
+          <t>A 4969-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6448,10 +6443,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46003</v>
+        <v>46049</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6463,8 +6458,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6507,7 +6507,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 49913-2025</t>
+          <t>A 4018-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6517,14 +6517,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45940</v>
+        <v>45323</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6536,8 +6536,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6580,7 +6585,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 11811-2025</t>
+          <t>A 6259-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6594,10 +6599,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45727</v>
+        <v>45337</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6610,7 +6615,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>9.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6653,7 +6658,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 7745-2025</t>
+          <t>A 6316-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6663,14 +6668,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45706</v>
+        <v>45338</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6682,8 +6687,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>28.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6726,7 +6736,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 15921-2025</t>
+          <t>A 42794-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6740,10 +6750,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45749</v>
+        <v>45566</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6756,7 +6766,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6799,7 +6809,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 4482-2026</t>
+          <t>A 61970-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6809,14 +6819,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46045</v>
+        <v>46003</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6828,13 +6838,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6877,7 +6882,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 6852-2026</t>
+          <t>A 4188-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6891,10 +6896,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46057</v>
+        <v>45324</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6912,7 +6917,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.8</v>
+        <v>9.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6955,7 +6960,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 15305-2025</t>
+          <t>A 2190-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6965,14 +6970,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45746</v>
+        <v>44578</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6984,8 +6989,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7028,7 +7038,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 28966-2022</t>
+          <t>A 53977-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7038,14 +7048,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44749</v>
+        <v>44876</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7058,7 +7068,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7101,7 +7111,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 578-2024</t>
+          <t>A 12903-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7115,10 +7125,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45299</v>
+        <v>45385</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7130,13 +7140,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>67.40000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7179,7 +7184,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 21291-2026</t>
+          <t>A 6124-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7193,10 +7198,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46147</v>
+        <v>46053</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7209,7 +7214,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7252,7 +7257,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 21293-2026</t>
+          <t>A 17151-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7266,10 +7271,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46147</v>
+        <v>45412</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7281,8 +7286,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7325,7 +7335,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 12988-2024</t>
+          <t>A 16621-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7339,10 +7349,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45385</v>
+        <v>46112</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7356,11 +7366,11 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>16.2</v>
+        <v>0.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7403,7 +7413,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 15288-2026</t>
+          <t>A 30040-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7413,14 +7423,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46105</v>
+        <v>45488</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7433,7 +7443,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7476,7 +7486,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 39796-2025</t>
+          <t>A 16483-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7490,10 +7500,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45891</v>
+        <v>45408</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7506,7 +7516,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7549,7 +7559,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 4677-2023</t>
+          <t>A 12663-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7563,10 +7573,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44952</v>
+        <v>44641</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7578,8 +7588,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>12.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7622,7 +7637,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 4018-2024</t>
+          <t>A 61841-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7636,10 +7651,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45323</v>
+        <v>46003</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7651,13 +7666,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7700,7 +7710,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 16611-2026</t>
+          <t>A 30806-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7714,10 +7724,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46112</v>
+        <v>45112</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7731,7 +7741,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I85" t="n">
@@ -7778,7 +7788,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 35792-2025</t>
+          <t>A 4482-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7792,10 +7802,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45861</v>
+        <v>46045</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7813,7 +7823,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.3</v>
+        <v>6.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7856,7 +7866,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 35971-2025</t>
+          <t>A 17316-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7870,10 +7880,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45863</v>
+        <v>45414</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7885,8 +7895,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7929,7 +7944,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 24002-2026</t>
+          <t>A 6852-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7939,14 +7954,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46167</v>
+        <v>46057</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7958,8 +7973,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8002,7 +8022,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 15296-2026</t>
+          <t>A 31993-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8016,10 +8036,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46105</v>
+        <v>45119</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8032,7 +8052,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.3</v>
+        <v>6.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8075,7 +8095,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 15012-2024</t>
+          <t>A 21291-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8089,10 +8109,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45399</v>
+        <v>46147</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8105,7 +8125,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8148,7 +8168,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 2555-2022</t>
+          <t>A 21293-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8162,10 +8182,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44579</v>
+        <v>46147</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8178,7 +8198,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8221,7 +8241,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 4651-2024</t>
+          <t>A 16568-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8235,10 +8255,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45328</v>
+        <v>45408</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8251,7 +8271,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8294,7 +8314,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 30040-2024</t>
+          <t>A 4677-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8304,14 +8324,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45488</v>
+        <v>44952</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8324,7 +8344,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8367,7 +8387,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 6357-2024</t>
+          <t>A 11802-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8381,10 +8401,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45338</v>
+        <v>45375</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8398,11 +8418,11 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8445,7 +8465,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 23621-2026</t>
+          <t>A 11894-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8459,10 +8479,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46162</v>
+        <v>45376</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8474,8 +8494,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8518,7 +8543,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 30673-2023</t>
+          <t>A 15288-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8532,10 +8557,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45112</v>
+        <v>46105</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8547,13 +8572,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8596,7 +8616,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 24987-2026</t>
+          <t>A 24248-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8610,10 +8630,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46174</v>
+        <v>45457</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8626,7 +8646,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8669,7 +8689,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 31993-2023</t>
+          <t>A 39796-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8683,10 +8703,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45119</v>
+        <v>45891</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8699,7 +8719,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>6.8</v>
+        <v>3.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8742,7 +8762,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 11894-2024</t>
+          <t>A 5027-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8756,10 +8776,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45376</v>
+        <v>45329</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8777,7 +8797,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8820,7 +8840,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 16483-2024</t>
+          <t>A 16611-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8834,10 +8854,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45408</v>
+        <v>46112</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8847,6 +8867,11 @@
       <c r="G100" t="inlineStr">
         <is>
           <t>TOMELILLA</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I100" t="n">
@@ -8893,7 +8918,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 31134-2026</t>
+          <t>A 12181-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8907,10 +8932,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46216</v>
+        <v>44998</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8922,13 +8947,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8988,7 +9008,7 @@
         <v>45162</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9044,7 +9064,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 51031-2023</t>
+          <t>A 24002-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9054,14 +9074,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45211</v>
+        <v>46167</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9074,7 +9094,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.2</v>
+        <v>6.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9117,7 +9137,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 59528-2022</t>
+          <t>A 17778-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9131,10 +9151,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44907</v>
+        <v>45418</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9152,7 +9172,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9195,7 +9215,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 16027-2022</t>
+          <t>A 15296-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9209,10 +9229,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44665</v>
+        <v>46105</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9224,13 +9244,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9273,7 +9288,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 35897-2026</t>
+          <t>A 44675-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9283,14 +9298,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46266</v>
+        <v>45574</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9302,8 +9317,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>3</v>
+        <v>11.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9346,7 +9366,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 6259-2024</t>
+          <t>A 26473-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9360,10 +9380,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45337</v>
+        <v>45469</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9376,7 +9396,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9419,7 +9439,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 1199-2024</t>
+          <t>A 51031-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9433,10 +9453,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45302</v>
+        <v>45211</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9448,13 +9468,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>16.1</v>
+        <v>1.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9497,7 +9512,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 25597-2026</t>
+          <t>A 7745-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9507,14 +9522,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46177</v>
+        <v>45706</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9527,7 +9542,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9570,7 +9585,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 25605-2026</t>
+          <t>A 5565-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9584,10 +9599,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46177</v>
+        <v>45334</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9600,7 +9615,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9643,7 +9658,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 26473-2024</t>
+          <t>A 23310-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9657,10 +9672,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45469</v>
+        <v>44720</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9672,8 +9687,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9716,7 +9736,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 17778-2024</t>
+          <t>A 23621-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9730,10 +9750,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45418</v>
+        <v>46162</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9745,13 +9765,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9794,7 +9809,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 37743-2026</t>
+          <t>A 7955-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9808,10 +9823,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46279</v>
+        <v>45350</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9824,7 +9839,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9867,7 +9882,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 38074-2026</t>
+          <t>A 24987-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9881,10 +9896,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46280</v>
+        <v>46174</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9897,7 +9912,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9940,7 +9955,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 8190-2024</t>
+          <t>A 55676-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9954,10 +9969,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45338</v>
+        <v>44888</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9969,13 +9984,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10018,7 +10028,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 8192-2024</t>
+          <t>A 31134-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10032,10 +10042,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45338</v>
+        <v>46216</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10049,11 +10059,11 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10096,7 +10106,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 17151-2024</t>
+          <t>A 8455-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10110,10 +10120,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45412</v>
+        <v>45354</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10131,7 +10141,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10174,7 +10184,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 32955-2026</t>
+          <t>A 16027-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10188,10 +10198,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46244</v>
+        <v>44665</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10203,8 +10213,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>6</v>
+        <v>1.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10247,7 +10262,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 32948-2026</t>
+          <t>A 35897-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10261,10 +10276,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46244</v>
+        <v>46266</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10277,7 +10292,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10320,7 +10335,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 12181-2023</t>
+          <t>A 4651-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10334,10 +10349,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44998</v>
+        <v>45328</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10350,7 +10365,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10393,7 +10408,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 10908-2026</t>
+          <t>A 12988-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10407,10 +10422,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46079</v>
+        <v>45385</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10422,8 +10437,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>16.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10466,7 +10486,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 23310-2022</t>
+          <t>A 15305-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10476,14 +10496,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44720</v>
+        <v>45746</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10495,13 +10515,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10544,7 +10559,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 5027-2024</t>
+          <t>A 60817-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10558,10 +10573,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45329</v>
+        <v>45260</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10573,13 +10588,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10622,7 +10632,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 743-2024</t>
+          <t>A 4023-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10636,10 +10646,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45300</v>
+        <v>45323</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10657,7 +10667,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>11.1</v>
+        <v>15.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10700,7 +10710,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 53977-2022</t>
+          <t>A 25597-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10714,10 +10724,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44876</v>
+        <v>46177</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10730,7 +10740,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10773,7 +10783,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 4188-2024</t>
+          <t>A 25605-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10787,10 +10797,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45324</v>
+        <v>46177</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10802,13 +10812,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>9.6</v>
+        <v>1.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10851,7 +10856,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 12663-2022</t>
+          <t>A 12310-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10865,10 +10870,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44641</v>
+        <v>44999</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10882,11 +10887,11 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>12.4</v>
+        <v>2.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10929,7 +10934,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 36180-2024</t>
+          <t>A 15921-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10943,10 +10948,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45534</v>
+        <v>45749</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10959,7 +10964,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11002,7 +11007,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 12903-2024</t>
+          <t>A 38074-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11016,10 +11021,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45385</v>
+        <v>46280</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11032,7 +11037,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>9.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11075,7 +11080,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 15075-2024</t>
+          <t>A 35742-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11085,14 +11090,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45399</v>
+        <v>45532</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11105,7 +11110,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11148,7 +11153,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 11887-2024</t>
+          <t>A 35715-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11162,10 +11167,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45376</v>
+        <v>45532</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11177,13 +11182,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>6.3</v>
+        <v>1.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11226,7 +11226,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 5565-2024</t>
+          <t>A 37743-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11240,10 +11240,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45334</v>
+        <v>46279</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11299,7 +11299,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 35742-2024</t>
+          <t>A 11806-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11313,10 +11313,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45532</v>
+        <v>45727</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11372,7 +11372,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 35715-2024</t>
+          <t>A 11810-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11386,10 +11386,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45532</v>
+        <v>45727</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11445,7 +11445,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 11806-2025</t>
+          <t>A 32948-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11459,10 +11459,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45727</v>
+        <v>46244</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11518,7 +11518,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 11810-2025</t>
+          <t>A 32955-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11532,10 +11532,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45727</v>
+        <v>46244</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11591,7 +11591,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 23185-2025</t>
+          <t>A 10908-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11601,143 +11601,289 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45791</v>
+        <v>46079</v>
       </c>
       <c r="E137" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>TOMELILLA</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>1</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138" ht="15" customHeight="1">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>A 40128-2026</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D138" s="1" t="n">
         <v>46293</v>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>TOMELILLA</t>
-        </is>
-      </c>
-      <c r="I137" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J137" t="n">
-        <v>0</v>
-      </c>
-      <c r="K137" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" t="n">
-        <v>0</v>
-      </c>
-      <c r="M137" t="n">
-        <v>0</v>
-      </c>
-      <c r="N137" t="n">
-        <v>0</v>
-      </c>
-      <c r="O137" t="n">
-        <v>0</v>
-      </c>
-      <c r="P137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
-      <c r="R137" t="n">
-        <v>0</v>
-      </c>
-      <c r="S137" t="n">
-        <v>0</v>
-      </c>
-      <c r="T137" t="n">
-        <v>0</v>
-      </c>
-      <c r="U137" t="n">
-        <v>0</v>
-      </c>
-      <c r="V137" s="2" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
+      <c r="E138" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>TOMELILLA</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0</v>
+      </c>
+      <c r="V138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139" ht="15" customHeight="1">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>A 40129-2026</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D139" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="E139" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>TOMELILLA</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0</v>
+      </c>
+      <c r="V139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
         <is>
           <t>S 3422-2024</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D138" s="1" t="n">
+      <c r="D140" s="1" t="n">
         <v>45537</v>
       </c>
-      <c r="E138" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>TOMELILLA</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
+      <c r="E140" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>TOMELILLA</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I138" t="n">
+      <c r="I140" t="n">
         <v>0.1</v>
       </c>
-      <c r="J138" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" t="n">
-        <v>0</v>
-      </c>
-      <c r="M138" t="n">
-        <v>0</v>
-      </c>
-      <c r="N138" t="n">
-        <v>0</v>
-      </c>
-      <c r="O138" t="n">
-        <v>0</v>
-      </c>
-      <c r="P138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
-      <c r="R138" t="n">
-        <v>0</v>
-      </c>
-      <c r="S138" t="n">
-        <v>0</v>
-      </c>
-      <c r="T138" t="n">
-        <v>0</v>
-      </c>
-      <c r="U138" t="n">
-        <v>0</v>
-      </c>
-      <c r="V138" s="2" t="inlineStr"/>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0</v>
+      </c>
+      <c r="V140" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TOMELILLA.xlsx
+++ b/Översikt TOMELILLA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE140"/>
+  <dimension ref="A1:AE139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45120</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45260</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2018-2024</t>
+          <t>A 14152-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45308</v>
+        <v>45009</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>17.2</v>
+        <v>3.5</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1125,10 +1125,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1140,153 +1140,153 @@
         <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Kråka
+Röd glada</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 14152-2023 artfynd.xlsx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 14152-2023 karta.png", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 14152-2023 georefererad karta.tif", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 14152-2023 FSC-klagomål.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 14152-2023 FSC-klagomål mail.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 14152-2023 tillsynsbegäran.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 14152-2023 tillsynsbegäran mail.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 14152-2023 prioriterade fågelarter.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 2018-2024</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45308</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TOMELILLA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Västlig hakmossa
 Röd glada</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2018-2024 artfynd.xlsx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2018-2024 karta.png", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2018-2024 georefererad karta.tif", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2018-2024 FSC-klagomål.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2018-2024 FSC-klagomål mail.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2018-2024 tillsynsbegäran.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2018-2024 tillsynsbegäran mail.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 2018-2024 prioriterade fågelarter.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 14152-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45009</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>TOMELILLA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Kråka
-Röd glada</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 14152-2023 artfynd.xlsx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 14152-2023 karta.png", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 14152-2023 georefererad karta.tif", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 14152-2023 FSC-klagomål.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 14152-2023 FSC-klagomål mail.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 14152-2023 tillsynsbegäran.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 14152-2023 tillsynsbegäran mail.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 14152-2023 prioriterade fågelarter.docx", "A 14152-2023")</f>
         <v/>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
         <v>45299</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>45429</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45744</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>44613</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>44721</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17907-2024</t>
+          <t>A 6261-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45419</v>
+        <v>45337</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1875,13 +1875,13 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.1</v>
+        <v>12.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1915,35 +1915,35 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Gulplister</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 17907-2024 artfynd.xlsx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 17907-2024 karta.png", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 17907-2024 georefererad karta.tif", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 17907-2024 FSC-klagomål.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 17907-2024 FSC-klagomål mail.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 17907-2024 tillsynsbegäran.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 17907-2024 tillsynsbegäran mail.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
         <v>45337</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 6261-2024</t>
+          <t>A 2193-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45337</v>
+        <v>44578</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2084,18 +2084,23 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>12.6</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -2109,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2125,35 +2130,35 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Skogslysing</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2193-2022 artfynd.xlsx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2193-2022 karta.png", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2193-2022 georefererad karta.tif", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2193-2022 FSC-klagomål.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2193-2022 FSC-klagomål mail.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2193-2022 tillsynsbegäran.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2193-2022 tillsynsbegäran mail.docx", "A 2193-2022")</f>
         <v/>
       </c>
     </row>
@@ -2177,7 +2182,7 @@
         <v>45811</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2282,7 +2287,7 @@
         <v>45940</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2387,7 +2392,7 @@
         <v>46000</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2475,7 +2480,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 2193-2022</t>
+          <t>A 6262-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2489,10 +2494,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44578</v>
+        <v>45337</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2504,22 +2509,17 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2550,42 +2550,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Skogslysing</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2193-2022 artfynd.xlsx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6262-2024 artfynd.xlsx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2193-2022 karta.png", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6262-2024 karta.png", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2193-2022 georefererad karta.tif", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6262-2024 georefererad karta.tif", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2193-2022 FSC-klagomål.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6262-2024 FSC-klagomål.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2193-2022 FSC-klagomål mail.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6262-2024 FSC-klagomål mail.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2193-2022 tillsynsbegäran.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6262-2024 tillsynsbegäran.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2193-2022 tillsynsbegäran mail.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6262-2024 tillsynsbegäran mail.docx", "A 6262-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 6262-2024</t>
+          <t>A 28862-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45337</v>
+        <v>45104</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2614,8 +2614,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2651,39 +2656,39 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6262-2024 artfynd.xlsx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6262-2024 karta.png", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6262-2024 georefererad karta.tif", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 28862-2023 georefererad karta.tif", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6262-2024 FSC-klagomål.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 28862-2023 FSC-klagomål.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6262-2024 FSC-klagomål mail.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 28862-2023 FSC-klagomål mail.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6262-2024 tillsynsbegäran.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 28862-2023 tillsynsbegäran.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6262-2024 tillsynsbegäran mail.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 28862-2023 tillsynsbegäran mail.docx", "A 28862-2023")</f>
         <v/>
       </c>
     </row>
@@ -2707,7 +2712,7 @@
         <v>45260</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2795,7 +2800,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 28862-2023</t>
+          <t>A 42387-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2809,10 +2814,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45104</v>
+        <v>44830</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2824,23 +2829,18 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>6.6</v>
+        <v>1.1</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2870,35 +2870,35 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 42387-2022 artfynd.xlsx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 42387-2022 karta.png", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 28862-2023 georefererad karta.tif", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 42387-2022 georefererad karta.tif", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 28862-2023 FSC-klagomål.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 42387-2022 FSC-klagomål.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 28862-2023 FSC-klagomål mail.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 42387-2022 FSC-klagomål mail.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 28862-2023 tillsynsbegäran.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 42387-2022 tillsynsbegäran.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 28862-2023 tillsynsbegäran mail.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 42387-2022 tillsynsbegäran mail.docx", "A 42387-2022")</f>
         <v/>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
         <v>45300</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 42387-2022</t>
+          <t>A 20397-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3029,10 +3029,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44830</v>
+        <v>46139</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3045,16 +3045,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3085,42 +3085,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 42387-2022 artfynd.xlsx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 20397-2026 artfynd.xlsx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 42387-2022 karta.png", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 20397-2026 karta.png", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 42387-2022 georefererad karta.tif", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 20397-2026 georefererad karta.tif", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 42387-2022 FSC-klagomål.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 20397-2026 FSC-klagomål.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 42387-2022 FSC-klagomål mail.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 20397-2026 FSC-klagomål mail.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 42387-2022 tillsynsbegäran.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 20397-2026 tillsynsbegäran.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 42387-2022 tillsynsbegäran mail.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 20397-2026 tillsynsbegäran mail.docx", "A 20397-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 20397-2026</t>
+          <t>A 26823-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3134,10 +3134,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46139</v>
+        <v>46183</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3150,17 +3150,17 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.2</v>
+        <v>12.1</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
@@ -3174,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3190,42 +3190,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 20397-2026 artfynd.xlsx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26823-2026 artfynd.xlsx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 20397-2026 karta.png", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26823-2026 karta.png", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 20397-2026 georefererad karta.tif", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26823-2026 georefererad karta.tif", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 20397-2026 FSC-klagomål.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26823-2026 FSC-klagomål.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 20397-2026 FSC-klagomål mail.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26823-2026 FSC-klagomål mail.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 20397-2026 tillsynsbegäran.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26823-2026 tillsynsbegäran.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 20397-2026 tillsynsbegäran mail.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26823-2026 tillsynsbegäran mail.docx", "A 26823-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 26823-2026</t>
+          <t>A 32949-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3239,10 +3239,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46183</v>
+        <v>46244</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>12.1</v>
+        <v>4.8</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3279,7 +3279,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3295,42 +3295,46 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26823-2026 artfynd.xlsx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 32949-2026 artfynd.xlsx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26823-2026 karta.png", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 32949-2026 karta.png", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26823-2026 georefererad karta.tif", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 32949-2026 georefererad karta.tif", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26823-2026 FSC-klagomål.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 32949-2026 FSC-klagomål.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26823-2026 FSC-klagomål mail.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 32949-2026 FSC-klagomål mail.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26823-2026 tillsynsbegäran.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 32949-2026 tillsynsbegäran.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26823-2026 tillsynsbegäran mail.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 32949-2026 tillsynsbegäran mail.docx", "A 32949-2026")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 32949-2026 prioriterade fågelarter.docx", "A 32949-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32949-2026</t>
+          <t>A 17907-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3344,10 +3348,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46244</v>
+        <v>45419</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3360,10 +3364,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3396,43 +3400,39 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Gulplister</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 32949-2026 artfynd.xlsx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 17907-2024 artfynd.xlsx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 32949-2026 karta.png", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 17907-2024 karta.png", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 32949-2026 georefererad karta.tif", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 17907-2024 georefererad karta.tif", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 32949-2026 FSC-klagomål.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 17907-2024 FSC-klagomål.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 32949-2026 FSC-klagomål mail.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 17907-2024 FSC-klagomål mail.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 32949-2026 tillsynsbegäran.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 17907-2024 tillsynsbegäran.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 32949-2026 tillsynsbegäran mail.docx", "A 32949-2026")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 32949-2026 prioriterade fågelarter.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 17907-2024 tillsynsbegäran mail.docx", "A 17907-2024")</f>
         <v/>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
         <v>44684</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44560</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44490</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44642</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44721</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 36180-2024</t>
+          <t>A 47231-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45534</v>
+        <v>45202</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4038,7 +4038,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 23185-2025</t>
+          <t>A 11802-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4048,14 +4048,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45791</v>
+        <v>45375</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4067,8 +4067,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4111,7 +4116,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 17760-2025</t>
+          <t>A 4023-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4125,10 +4130,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45758</v>
+        <v>45323</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4140,8 +4145,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>3.7</v>
+        <v>15.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4184,7 +4194,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 45729-2024</t>
+          <t>A 19454-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4198,10 +4208,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45579</v>
+        <v>45429</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4214,7 +4224,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>10.1</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4257,7 +4267,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 38787-2024</t>
+          <t>A 23813-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4271,10 +4281,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45547</v>
+        <v>45455</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4287,7 +4297,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4330,7 +4340,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 2548-2024</t>
+          <t>A 24248-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4344,10 +4354,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45313</v>
+        <v>45457</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4360,7 +4370,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4403,7 +4413,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13159-2024</t>
+          <t>A 2548-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4417,10 +4427,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45386</v>
+        <v>45313</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4433,7 +4443,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4476,7 +4486,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 2555-2022</t>
+          <t>A 23185-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4486,14 +4496,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44579</v>
+        <v>45791</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4506,7 +4516,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4549,7 +4559,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 743-2024</t>
+          <t>A 17760-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4563,10 +4573,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45300</v>
+        <v>45758</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4578,13 +4588,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>11.1</v>
+        <v>3.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4627,7 +4632,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 15158-2025</t>
+          <t>A 38787-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4641,10 +4646,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45744</v>
+        <v>45547</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4657,7 +4662,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4700,7 +4705,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 15075-2024</t>
+          <t>A 44675-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4710,14 +4715,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45399</v>
+        <v>45574</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4729,8 +4734,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.7</v>
+        <v>11.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4773,7 +4783,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 43306-2025</t>
+          <t>A 45729-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4787,10 +4797,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45910</v>
+        <v>45579</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4803,7 +4813,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>10.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4846,7 +4856,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11887-2024</t>
+          <t>A 17316-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4860,10 +4870,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45376</v>
+        <v>45414</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4881,7 +4891,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6.3</v>
+        <v>4.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4924,7 +4934,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 10272-2023</t>
+          <t>A 15158-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4938,10 +4948,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44986</v>
+        <v>45744</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4953,13 +4963,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>7.7</v>
+        <v>1.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5002,7 +5007,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11811-2025</t>
+          <t>A 43306-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5016,10 +5021,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45727</v>
+        <v>45910</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5032,7 +5037,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>9.699999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5075,7 +5080,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 15012-2024</t>
+          <t>A 11811-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5089,10 +5094,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45399</v>
+        <v>45727</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5105,7 +5110,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5148,7 +5153,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 48171-2025</t>
+          <t>A 16568-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5162,10 +5167,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45933</v>
+        <v>45408</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5178,7 +5183,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5221,7 +5226,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 8190-2024</t>
+          <t>A 12310-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5235,10 +5240,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45338</v>
+        <v>44999</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5252,11 +5257,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5299,7 +5304,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8192-2024</t>
+          <t>A 60817-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5313,10 +5318,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45338</v>
+        <v>45260</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5328,13 +5333,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5377,7 +5377,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 47231-2023</t>
+          <t>A 7955-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5391,10 +5391,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45202</v>
+        <v>45350</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5450,7 +5450,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 28966-2022</t>
+          <t>A 42794-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5460,14 +5460,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44749</v>
+        <v>45566</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5523,7 +5523,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 39791-2025</t>
+          <t>A 48171-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45891</v>
+        <v>45933</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5596,7 +5596,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 578-2024</t>
+          <t>A 2190-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5610,10 +5610,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45299</v>
+        <v>44578</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5627,11 +5627,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>67.40000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5674,7 +5674,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 6357-2024</t>
+          <t>A 10272-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45338</v>
+        <v>44986</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5705,11 +5705,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>7.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5752,7 +5752,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 35792-2025</t>
+          <t>A 55676-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5766,10 +5766,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45861</v>
+        <v>44888</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5781,13 +5781,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5830,7 +5825,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 35971-2025</t>
+          <t>A 35792-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5844,10 +5839,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45863</v>
+        <v>45861</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5859,8 +5854,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5903,7 +5903,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 23813-2024</t>
+          <t>A 35971-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45455</v>
+        <v>45863</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 19454-2024</t>
+          <t>A 39791-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45429</v>
+        <v>45891</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6049,7 +6049,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 59528-2022</t>
+          <t>A 30806-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44907</v>
+        <v>45112</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6127,7 +6127,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 30673-2023</t>
+          <t>A 49815-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6141,10 +6141,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45112</v>
+        <v>45940</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6156,13 +6156,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6205,7 +6200,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 49913-2025</t>
+          <t>A 4969-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6215,14 +6210,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45940</v>
+        <v>46049</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6234,8 +6229,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6278,7 +6278,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 49815-2025</t>
+          <t>A 6316-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6292,10 +6292,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45940</v>
+        <v>45338</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6307,8 +6307,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>28.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6351,7 +6356,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 1199-2024</t>
+          <t>A 8455-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6365,10 +6370,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45302</v>
+        <v>45354</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6386,7 +6391,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>16.1</v>
+        <v>5.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6429,7 +6434,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 4969-2026</t>
+          <t>A 13159-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6443,10 +6448,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46049</v>
+        <v>45386</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6458,13 +6463,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6507,7 +6507,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 4018-2024</t>
+          <t>A 49913-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6517,14 +6517,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45323</v>
+        <v>45940</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6536,13 +6536,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6585,7 +6580,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 6259-2024</t>
+          <t>A 61970-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6595,14 +6590,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45337</v>
+        <v>46003</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6615,7 +6610,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6658,7 +6653,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 6316-2024</t>
+          <t>A 7745-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6668,14 +6663,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45338</v>
+        <v>45706</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6687,13 +6682,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>28.6</v>
+        <v>0.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6736,7 +6726,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 42794-2024</t>
+          <t>A 15921-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6750,10 +6740,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45566</v>
+        <v>45749</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6766,7 +6756,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6809,7 +6799,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61970-2025</t>
+          <t>A 15305-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6823,10 +6813,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46003</v>
+        <v>45746</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6839,7 +6829,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6882,7 +6872,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 4188-2024</t>
+          <t>A 6124-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6896,10 +6886,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45324</v>
+        <v>46053</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6911,13 +6901,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>9.6</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6960,7 +6945,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 2190-2022</t>
+          <t>A 16621-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6974,10 +6959,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44578</v>
+        <v>46112</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6991,11 +6976,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.9</v>
+        <v>0.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7038,7 +7023,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 53977-2022</t>
+          <t>A 28966-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7048,14 +7033,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44876</v>
+        <v>44749</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7068,7 +7053,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7111,7 +7096,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 12903-2024</t>
+          <t>A 578-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7125,10 +7110,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45385</v>
+        <v>45299</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7140,8 +7125,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>9.199999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7184,7 +7174,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 6124-2026</t>
+          <t>A 12988-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7198,10 +7188,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46053</v>
+        <v>45385</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7213,8 +7203,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>16.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7257,7 +7252,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 17151-2024</t>
+          <t>A 61841-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7271,10 +7266,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45412</v>
+        <v>46003</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7286,13 +7281,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7335,7 +7325,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 16621-2026</t>
+          <t>A 4677-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7349,10 +7339,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46112</v>
+        <v>44952</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7364,13 +7354,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7413,7 +7398,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 30040-2024</t>
+          <t>A 4018-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7423,14 +7408,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45488</v>
+        <v>45323</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7442,8 +7427,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7486,7 +7476,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 16483-2024</t>
+          <t>A 4482-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7500,10 +7490,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45408</v>
+        <v>46045</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7515,8 +7505,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>6.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7559,7 +7554,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 12663-2022</t>
+          <t>A 6852-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7573,10 +7568,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44641</v>
+        <v>46057</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7594,7 +7589,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>12.4</v>
+        <v>4.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7637,7 +7632,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 61841-2025</t>
+          <t>A 15012-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7651,10 +7646,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46003</v>
+        <v>45399</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7667,7 +7662,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.1</v>
+        <v>6.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7710,7 +7705,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 30806-2023</t>
+          <t>A 2555-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7724,10 +7719,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45112</v>
+        <v>44579</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7739,13 +7734,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7788,7 +7778,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 4482-2026</t>
+          <t>A 4651-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7802,10 +7792,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46045</v>
+        <v>45328</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7817,13 +7807,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>6.5</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7866,7 +7851,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 17316-2024</t>
+          <t>A 30040-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7876,14 +7861,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45414</v>
+        <v>45488</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7893,11 +7878,6 @@
       <c r="G87" t="inlineStr">
         <is>
           <t>TOMELILLA</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I87" t="n">
@@ -7944,7 +7924,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 6852-2026</t>
+          <t>A 21291-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7958,10 +7938,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46057</v>
+        <v>46147</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7973,13 +7953,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8022,7 +7997,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 31993-2023</t>
+          <t>A 21293-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8036,10 +8011,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45119</v>
+        <v>46147</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8052,7 +8027,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>6.8</v>
+        <v>2.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8095,7 +8070,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 21291-2026</t>
+          <t>A 6357-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8109,10 +8084,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46147</v>
+        <v>45338</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8124,8 +8099,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8168,7 +8148,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 21293-2026</t>
+          <t>A 30673-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8182,10 +8162,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46147</v>
+        <v>45112</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8197,8 +8177,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8241,7 +8226,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 16568-2024</t>
+          <t>A 15288-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8255,10 +8240,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45408</v>
+        <v>46105</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8271,7 +8256,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8314,7 +8299,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 4677-2023</t>
+          <t>A 31993-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8328,10 +8313,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44952</v>
+        <v>45119</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8344,7 +8329,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.6</v>
+        <v>6.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8387,7 +8372,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 11802-2024</t>
+          <t>A 39796-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8401,10 +8386,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45375</v>
+        <v>45891</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8416,13 +8401,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8482,7 +8462,7 @@
         <v>45376</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8543,7 +8523,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 15288-2026</t>
+          <t>A 16483-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8557,10 +8537,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46105</v>
+        <v>45408</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8573,7 +8553,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8616,7 +8596,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 24248-2024</t>
+          <t>A 16611-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8630,10 +8610,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45457</v>
+        <v>46112</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8645,8 +8625,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8689,7 +8674,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 39796-2025</t>
+          <t>A 38562-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8703,10 +8688,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45891</v>
+        <v>45162</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8719,7 +8704,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8762,7 +8747,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 5027-2024</t>
+          <t>A 51031-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8776,10 +8761,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45329</v>
+        <v>45211</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8791,13 +8776,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8840,7 +8820,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 16611-2026</t>
+          <t>A 59528-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8854,10 +8834,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46112</v>
+        <v>44907</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8871,11 +8851,11 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8918,7 +8898,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 12181-2023</t>
+          <t>A 16027-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8932,10 +8912,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44998</v>
+        <v>44665</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8947,8 +8927,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8991,7 +8976,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 38562-2023</t>
+          <t>A 24002-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9001,14 +8986,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45162</v>
+        <v>46167</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9021,7 +9006,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.2</v>
+        <v>6.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9064,7 +9049,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 24002-2026</t>
+          <t>A 6259-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9074,14 +9059,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46167</v>
+        <v>45337</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9094,7 +9079,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9137,7 +9122,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 17778-2024</t>
+          <t>A 15296-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9151,10 +9136,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45418</v>
+        <v>46105</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9166,13 +9151,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9215,7 +9195,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 15296-2026</t>
+          <t>A 1199-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9229,10 +9209,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46105</v>
+        <v>45302</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9244,8 +9224,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>0.3</v>
+        <v>16.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9288,7 +9273,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 44675-2024</t>
+          <t>A 26473-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9298,14 +9283,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45574</v>
+        <v>45469</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9317,13 +9302,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>11.2</v>
+        <v>4.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9366,7 +9346,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 26473-2024</t>
+          <t>A 17778-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9380,10 +9360,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45469</v>
+        <v>45418</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9395,8 +9375,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9439,7 +9424,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 51031-2023</t>
+          <t>A 23621-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9453,10 +9438,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45211</v>
+        <v>46162</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9469,7 +9454,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9512,7 +9497,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 7745-2025</t>
+          <t>A 8190-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9522,14 +9507,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45706</v>
+        <v>45338</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9541,8 +9526,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>0.4</v>
+        <v>3.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9585,7 +9575,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 5565-2024</t>
+          <t>A 8192-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9599,10 +9589,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45334</v>
+        <v>45338</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9614,8 +9604,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9658,7 +9653,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 23310-2022</t>
+          <t>A 17151-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9672,10 +9667,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44720</v>
+        <v>45412</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9693,7 +9688,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9736,7 +9731,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 23621-2026</t>
+          <t>A 24987-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9750,10 +9745,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46162</v>
+        <v>46174</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9766,7 +9761,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9809,7 +9804,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 7955-2024</t>
+          <t>A 12181-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9823,10 +9818,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45350</v>
+        <v>44998</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9839,7 +9834,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9882,7 +9877,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 24987-2026</t>
+          <t>A 23310-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9896,10 +9891,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46174</v>
+        <v>44720</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9911,8 +9906,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>0.8</v>
+        <v>5.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9955,7 +9955,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 55676-2022</t>
+          <t>A 5027-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9969,10 +9969,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44888</v>
+        <v>45329</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9984,8 +9984,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10028,7 +10033,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 31134-2026</t>
+          <t>A 743-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10042,10 +10047,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46216</v>
+        <v>45300</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10063,7 +10068,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4.5</v>
+        <v>11.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10106,7 +10111,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 8455-2024</t>
+          <t>A 53977-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10120,10 +10125,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45354</v>
+        <v>44876</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10135,13 +10140,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10184,7 +10184,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 16027-2022</t>
+          <t>A 31134-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10198,10 +10198,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44665</v>
+        <v>46216</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10279,7 +10279,7 @@
         <v>46266</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 4651-2024</t>
+          <t>A 4188-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10349,10 +10349,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45328</v>
+        <v>45324</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10364,8 +10364,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>0.9</v>
+        <v>9.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10408,7 +10413,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 12988-2024</t>
+          <t>A 12663-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10422,10 +10427,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45385</v>
+        <v>44641</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10443,7 +10448,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>16.2</v>
+        <v>12.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10486,7 +10491,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 15305-2025</t>
+          <t>A 25597-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10496,14 +10501,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45746</v>
+        <v>46177</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10516,7 +10521,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10559,7 +10564,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 60817-2023</t>
+          <t>A 36180-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10573,10 +10578,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45260</v>
+        <v>45534</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10589,7 +10594,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4.3</v>
+        <v>1.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10632,7 +10637,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 4023-2024</t>
+          <t>A 12903-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10646,10 +10651,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45323</v>
+        <v>45385</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10661,13 +10666,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>15.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10710,7 +10710,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 25597-2026</t>
+          <t>A 15075-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10720,14 +10720,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46177</v>
+        <v>45399</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10783,7 +10783,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 25605-2026</t>
+          <t>A 11887-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10797,10 +10797,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46177</v>
+        <v>45376</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10812,8 +10812,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>1.6</v>
+        <v>6.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10856,7 +10861,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 12310-2023</t>
+          <t>A 37743-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10870,10 +10875,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44999</v>
+        <v>46279</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10885,13 +10890,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10934,7 +10934,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 15921-2025</t>
+          <t>A 38074-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10948,10 +10948,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45749</v>
+        <v>46280</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11007,7 +11007,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 38074-2026</t>
+          <t>A 5565-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11021,10 +11021,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46280</v>
+        <v>45334</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11080,7 +11080,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 35742-2024</t>
+          <t>A 32955-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11094,10 +11094,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45532</v>
+        <v>46244</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11153,7 +11153,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 35715-2024</t>
+          <t>A 32948-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11167,10 +11167,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45532</v>
+        <v>46244</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11226,7 +11226,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 37743-2026</t>
+          <t>A 35742-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11240,10 +11240,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46279</v>
+        <v>45532</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11299,7 +11299,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 11806-2025</t>
+          <t>A 10908-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11313,10 +11313,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45727</v>
+        <v>46079</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11372,7 +11372,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 11810-2025</t>
+          <t>A 35715-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11386,10 +11386,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45727</v>
+        <v>45532</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11445,7 +11445,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 32948-2026</t>
+          <t>A 11806-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11459,10 +11459,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46244</v>
+        <v>45727</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11518,7 +11518,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 32955-2026</t>
+          <t>A 11810-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11532,10 +11532,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46244</v>
+        <v>45727</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11591,7 +11591,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 10908-2026</t>
+          <t>A 40128-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11605,10 +11605,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46079</v>
+        <v>46293</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11664,7 +11664,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 40128-2026</t>
+          <t>A 40129-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11681,7 +11681,7 @@
         <v>46293</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11694,7 +11694,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11734,27 +11734,27 @@
       </c>
       <c r="V138" s="2" t="inlineStr"/>
     </row>
-    <row r="139" ht="15" customHeight="1">
+    <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 40129-2026</t>
+          <t>S 3422-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46293</v>
+        <v>45537</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11766,8 +11766,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11806,84 +11811,6 @@
         <v>0</v>
       </c>
       <c r="V139" s="2" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>S 3422-2024</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D140" s="1" t="n">
-        <v>45537</v>
-      </c>
-      <c r="E140" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>TOMELILLA</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I140" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" t="n">
-        <v>0</v>
-      </c>
-      <c r="L140" t="n">
-        <v>0</v>
-      </c>
-      <c r="M140" t="n">
-        <v>0</v>
-      </c>
-      <c r="N140" t="n">
-        <v>0</v>
-      </c>
-      <c r="O140" t="n">
-        <v>0</v>
-      </c>
-      <c r="P140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
-      <c r="R140" t="n">
-        <v>0</v>
-      </c>
-      <c r="S140" t="n">
-        <v>0</v>
-      </c>
-      <c r="T140" t="n">
-        <v>0</v>
-      </c>
-      <c r="U140" t="n">
-        <v>0</v>
-      </c>
-      <c r="V140" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TOMELILLA.xlsx
+++ b/Översikt TOMELILLA.xlsx
@@ -601,7 +601,7 @@
         <v>44756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45120</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45260</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 14152-2023</t>
+          <t>A 2018-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45009</v>
+        <v>45308</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.5</v>
+        <v>17.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1125,10 +1125,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1140,153 +1140,153 @@
         <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Västlig hakmossa
+Röd glada</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2018-2024 artfynd.xlsx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2018-2024 karta.png", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2018-2024 georefererad karta.tif", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2018-2024 FSC-klagomål.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2018-2024 FSC-klagomål mail.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2018-2024 tillsynsbegäran.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2018-2024 tillsynsbegäran mail.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 2018-2024 prioriterade fågelarter.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 14152-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45009</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TOMELILLA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Kråka
 Röd glada</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 14152-2023 artfynd.xlsx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 14152-2023 karta.png", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 14152-2023 georefererad karta.tif", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 14152-2023 FSC-klagomål.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 14152-2023 FSC-klagomål mail.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 14152-2023 tillsynsbegäran.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 14152-2023 tillsynsbegäran mail.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 14152-2023 prioriterade fågelarter.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 2018-2024</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45308</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>TOMELILLA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Västlig hakmossa
-Röd glada</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2018-2024 artfynd.xlsx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2018-2024 karta.png", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2018-2024 georefererad karta.tif", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2018-2024 FSC-klagomål.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2018-2024 FSC-klagomål mail.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2018-2024 tillsynsbegäran.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2018-2024 tillsynsbegäran mail.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 2018-2024 prioriterade fågelarter.docx", "A 2018-2024")</f>
         <v/>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
         <v>45299</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>45429</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45744</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>44613</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>44721</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 6261-2024</t>
+          <t>A 42387-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45337</v>
+        <v>44830</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1875,17 +1875,17 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>12.6</v>
+        <v>1.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1911,46 +1911,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 42387-2022 artfynd.xlsx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 42387-2022 karta.png", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 42387-2022 georefererad karta.tif", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 42387-2022 FSC-klagomål.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 42387-2022 FSC-klagomål mail.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 42387-2022 tillsynsbegäran.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 42387-2022 tillsynsbegäran mail.docx", "A 42387-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 6261-2024</t>
+          <t>A 60820-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45337</v>
+        <v>45260</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>12.6</v>
+        <v>4.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2016,46 +2016,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 60820-2023 artfynd.xlsx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 60820-2023 karta.png", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 60820-2023 georefererad karta.tif", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 60820-2023 FSC-klagomål.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 60820-2023 FSC-klagomål mail.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 60820-2023 tillsynsbegäran.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 60820-2023 tillsynsbegäran mail.docx", "A 60820-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2193-2022</t>
+          <t>A 28862-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44578</v>
+        <v>45104</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2086,20 +2086,20 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>6.6</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2126,46 +2126,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Skogslysing</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2193-2022 artfynd.xlsx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2193-2022 karta.png", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2193-2022 georefererad karta.tif", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 28862-2023 georefererad karta.tif", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2193-2022 FSC-klagomål.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 28862-2023 FSC-klagomål.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2193-2022 FSC-klagomål mail.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 28862-2023 FSC-klagomål mail.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2193-2022 tillsynsbegäran.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 28862-2023 tillsynsbegäran.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2193-2022 tillsynsbegäran mail.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 28862-2023 tillsynsbegäran mail.docx", "A 28862-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 26958-2025</t>
+          <t>A 2193-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45811</v>
+        <v>44578</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2194,18 +2194,23 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
@@ -2219,7 +2224,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2231,46 +2236,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Skogslysing</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26958-2025 artfynd.xlsx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2193-2022 artfynd.xlsx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26958-2025 karta.png", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2193-2022 karta.png", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26958-2025 georefererad karta.tif", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2193-2022 georefererad karta.tif", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26958-2025 FSC-klagomål.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2193-2022 FSC-klagomål.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26958-2025 FSC-klagomål mail.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2193-2022 FSC-klagomål mail.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26958-2025 tillsynsbegäran.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2193-2022 tillsynsbegäran.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26958-2025 tillsynsbegäran mail.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2193-2022 tillsynsbegäran mail.docx", "A 2193-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 49813-2025</t>
+          <t>A 17907-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2284,10 +2289,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45940</v>
+        <v>45419</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2300,10 +2305,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2336,46 +2341,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Gulplister</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 49813-2025 artfynd.xlsx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 17907-2024 artfynd.xlsx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 49813-2025 karta.png", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 17907-2024 karta.png", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 49813-2025 georefererad karta.tif", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 17907-2024 georefererad karta.tif", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 49813-2025 FSC-klagomål.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 17907-2024 FSC-klagomål.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 49813-2025 FSC-klagomål mail.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 17907-2024 FSC-klagomål mail.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 49813-2025 tillsynsbegäran.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 17907-2024 tillsynsbegäran.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 49813-2025 tillsynsbegäran mail.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 17907-2024 tillsynsbegäran mail.docx", "A 17907-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 61314-2025</t>
+          <t>A 756-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2389,10 +2394,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46000</v>
+        <v>45300</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2404,18 +2409,23 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>13.1</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -2429,7 +2439,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2445,42 +2455,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 756-2024 artfynd.xlsx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 756-2024 karta.png", "A 756-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 756-2024 georefererad karta.tif", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 756-2024 FSC-klagomål.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 756-2024 FSC-klagomål mail.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 756-2024 tillsynsbegäran.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 756-2024 tillsynsbegäran mail.docx", "A 756-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 6262-2024</t>
+          <t>A 6261-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2497,7 +2507,7 @@
         <v>45337</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2510,13 +2520,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.5</v>
+        <v>12.6</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2550,42 +2560,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6262-2024 artfynd.xlsx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6262-2024 karta.png", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6262-2024 georefererad karta.tif", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6262-2024 FSC-klagomål.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6262-2024 FSC-klagomål mail.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6262-2024 tillsynsbegäran.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6262-2024 tillsynsbegäran mail.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 28862-2023</t>
+          <t>A 6262-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2599,10 +2609,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45104</v>
+        <v>45337</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2614,13 +2624,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2656,46 +2661,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6262-2024 artfynd.xlsx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6262-2024 karta.png", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 28862-2023 georefererad karta.tif", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6262-2024 georefererad karta.tif", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 28862-2023 FSC-klagomål.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6262-2024 FSC-klagomål.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 28862-2023 FSC-klagomål mail.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6262-2024 FSC-klagomål mail.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 28862-2023 tillsynsbegäran.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6262-2024 tillsynsbegäran.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 28862-2023 tillsynsbegäran mail.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6262-2024 tillsynsbegäran mail.docx", "A 6262-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 60820-2023</t>
+          <t>A 26958-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2709,10 +2714,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45260</v>
+        <v>45811</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2725,7 +2730,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2765,42 +2770,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 60820-2023 artfynd.xlsx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26958-2025 artfynd.xlsx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 60820-2023 karta.png", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26958-2025 karta.png", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 60820-2023 georefererad karta.tif", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26958-2025 georefererad karta.tif", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 60820-2023 FSC-klagomål.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26958-2025 FSC-klagomål.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 60820-2023 FSC-klagomål mail.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26958-2025 FSC-klagomål mail.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 60820-2023 tillsynsbegäran.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26958-2025 tillsynsbegäran.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 60820-2023 tillsynsbegäran mail.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26958-2025 tillsynsbegäran mail.docx", "A 26958-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 42387-2022</t>
+          <t>A 6261-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2814,10 +2819,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44830</v>
+        <v>45337</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2830,16 +2835,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>12.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2854,7 +2859,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2866,46 +2871,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 42387-2022 artfynd.xlsx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 42387-2022 karta.png", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 42387-2022 georefererad karta.tif", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 42387-2022 FSC-klagomål.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 42387-2022 FSC-klagomål mail.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 42387-2022 tillsynsbegäran.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 42387-2022 tillsynsbegäran mail.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 756-2024</t>
+          <t>A 49813-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2919,10 +2924,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45300</v>
+        <v>45940</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2934,22 +2939,17 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>13.1</v>
+        <v>4.5</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2964,7 +2964,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2980,42 +2980,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 756-2024 artfynd.xlsx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 49813-2025 artfynd.xlsx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 756-2024 karta.png", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 49813-2025 karta.png", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 756-2024 georefererad karta.tif", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 49813-2025 georefererad karta.tif", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 756-2024 FSC-klagomål.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 49813-2025 FSC-klagomål.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 756-2024 FSC-klagomål mail.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 49813-2025 FSC-klagomål mail.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 756-2024 tillsynsbegäran.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 49813-2025 tillsynsbegäran.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 756-2024 tillsynsbegäran mail.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 49813-2025 tillsynsbegäran mail.docx", "A 49813-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 20397-2026</t>
+          <t>A 61314-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3029,10 +3029,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46139</v>
+        <v>46000</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3085,42 +3085,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 20397-2026 artfynd.xlsx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 20397-2026 karta.png", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 20397-2026 georefererad karta.tif", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 20397-2026 FSC-klagomål.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 20397-2026 FSC-klagomål mail.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 20397-2026 tillsynsbegäran.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 20397-2026 tillsynsbegäran mail.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 26823-2026</t>
+          <t>A 20397-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3134,10 +3134,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46183</v>
+        <v>46139</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3150,16 +3150,16 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>12.1</v>
+        <v>4.2</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3174,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3190,35 +3190,35 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26823-2026 artfynd.xlsx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 20397-2026 artfynd.xlsx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26823-2026 karta.png", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 20397-2026 karta.png", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26823-2026 georefererad karta.tif", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 20397-2026 georefererad karta.tif", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26823-2026 FSC-klagomål.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 20397-2026 FSC-klagomål.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26823-2026 FSC-klagomål mail.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 20397-2026 FSC-klagomål mail.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26823-2026 tillsynsbegäran.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 20397-2026 tillsynsbegäran.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26823-2026 tillsynsbegäran mail.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 20397-2026 tillsynsbegäran mail.docx", "A 20397-2026")</f>
         <v/>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
         <v>46244</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 17907-2024</t>
+          <t>A 26823-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45419</v>
+        <v>46183</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.1</v>
+        <v>12.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3373,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3400,39 +3400,39 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Gulplister</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 17907-2024 artfynd.xlsx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26823-2026 artfynd.xlsx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 17907-2024 karta.png", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26823-2026 karta.png", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 17907-2024 georefererad karta.tif", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26823-2026 georefererad karta.tif", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 17907-2024 FSC-klagomål.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26823-2026 FSC-klagomål.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 17907-2024 FSC-klagomål mail.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26823-2026 FSC-klagomål mail.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 17907-2024 tillsynsbegäran.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26823-2026 tillsynsbegäran.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 17907-2024 tillsynsbegäran mail.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26823-2026 tillsynsbegäran mail.docx", "A 26823-2026")</f>
         <v/>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
         <v>44684</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44560</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44490</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44642</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44721</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 47231-2023</t>
+          <t>A 36180-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45202</v>
+        <v>45534</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4038,7 +4038,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 11802-2024</t>
+          <t>A 23813-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45375</v>
+        <v>45455</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4067,13 +4067,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4116,7 +4111,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 4023-2024</t>
+          <t>A 8455-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4130,10 +4125,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45323</v>
+        <v>45354</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4151,7 +4146,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>15.2</v>
+        <v>5.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4194,7 +4189,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 19454-2024</t>
+          <t>A 16027-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4208,10 +4203,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45429</v>
+        <v>44665</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4223,8 +4218,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4267,7 +4267,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 23813-2024</t>
+          <t>A 31993-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45455</v>
+        <v>45119</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>6.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 24248-2024</t>
+          <t>A 19454-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4354,10 +4354,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45457</v>
+        <v>45429</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2548-2024</t>
+          <t>A 16568-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45313</v>
+        <v>45408</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4486,7 +4486,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 23185-2025</t>
+          <t>A 4677-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4496,14 +4496,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45791</v>
+        <v>44952</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 17760-2025</t>
+          <t>A 59528-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4573,10 +4573,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45758</v>
+        <v>44907</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4588,8 +4588,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4632,7 +4637,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38787-2024</t>
+          <t>A 30673-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4646,10 +4651,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45547</v>
+        <v>45112</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4661,8 +4666,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4705,7 +4715,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 44675-2024</t>
+          <t>A 11802-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4715,14 +4725,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45574</v>
+        <v>45375</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4736,11 +4746,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>11.2</v>
+        <v>4.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4783,7 +4793,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 45729-2024</t>
+          <t>A 11894-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4797,10 +4807,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45579</v>
+        <v>45376</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4812,8 +4822,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>10.1</v>
+        <v>4.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4856,7 +4871,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 17316-2024</t>
+          <t>A 4651-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4870,10 +4885,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45414</v>
+        <v>45328</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4885,13 +4900,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4934,7 +4944,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 15158-2025</t>
+          <t>A 24248-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4948,10 +4958,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45744</v>
+        <v>45457</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4964,7 +4974,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5007,7 +5017,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 43306-2025</t>
+          <t>A 12988-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5021,10 +5031,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45910</v>
+        <v>45385</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5036,8 +5046,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>16.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5080,7 +5095,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11811-2025</t>
+          <t>A 15305-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5090,14 +5105,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45727</v>
+        <v>45746</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5110,7 +5125,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>9.699999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5153,7 +5168,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 16568-2024</t>
+          <t>A 60817-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5167,10 +5182,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45408</v>
+        <v>45260</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5183,7 +5198,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5226,7 +5241,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 12310-2023</t>
+          <t>A 4023-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5240,10 +5255,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44999</v>
+        <v>45323</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5257,11 +5272,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.2</v>
+        <v>15.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5304,7 +5319,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 60817-2023</t>
+          <t>A 1199-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5318,10 +5333,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45260</v>
+        <v>45302</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5333,8 +5348,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>4.3</v>
+        <v>16.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5377,7 +5397,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 7955-2024</t>
+          <t>A 5027-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5391,10 +5411,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45350</v>
+        <v>45329</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5406,8 +5426,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5450,7 +5475,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 42794-2024</t>
+          <t>A 4018-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5464,10 +5489,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45566</v>
+        <v>45323</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5479,8 +5504,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5523,7 +5553,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 48171-2025</t>
+          <t>A 6259-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5537,10 +5567,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45933</v>
+        <v>45337</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5553,7 +5583,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5596,7 +5626,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 2190-2022</t>
+          <t>A 6316-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5610,10 +5640,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44578</v>
+        <v>45338</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5627,11 +5657,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.9</v>
+        <v>28.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5674,7 +5704,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 10272-2023</t>
+          <t>A 12181-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5688,10 +5718,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44986</v>
+        <v>44998</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5703,13 +5733,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>7.7</v>
+        <v>1.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5752,7 +5777,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 55676-2022</t>
+          <t>A 38562-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5766,10 +5791,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44888</v>
+        <v>45162</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5782,7 +5807,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5825,7 +5850,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 35792-2025</t>
+          <t>A 12310-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5839,10 +5864,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45861</v>
+        <v>44999</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5856,11 +5881,11 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5903,7 +5928,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 35971-2025</t>
+          <t>A 42794-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5917,10 +5942,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45863</v>
+        <v>45566</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5933,7 +5958,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5976,7 +6001,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 39791-2025</t>
+          <t>A 17778-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5990,10 +6015,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45891</v>
+        <v>45418</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6005,8 +6030,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6049,7 +6079,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30806-2023</t>
+          <t>A 15921-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6063,10 +6093,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45112</v>
+        <v>45749</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6078,13 +6108,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6127,7 +6152,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 49815-2025</t>
+          <t>A 44675-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6137,14 +6162,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45940</v>
+        <v>45574</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6156,8 +6181,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>11.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6200,7 +6230,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 4969-2026</t>
+          <t>A 35742-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6214,10 +6244,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46049</v>
+        <v>45532</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6229,13 +6259,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6278,7 +6303,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 6316-2024</t>
+          <t>A 35715-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6292,10 +6317,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45338</v>
+        <v>45532</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6307,13 +6332,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>28.6</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6356,7 +6376,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 8455-2024</t>
+          <t>A 26473-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6370,10 +6390,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45354</v>
+        <v>45469</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6385,13 +6405,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6434,7 +6449,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 13159-2024</t>
+          <t>A 11806-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6448,10 +6463,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45386</v>
+        <v>45727</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6464,7 +6479,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6507,7 +6522,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 49913-2025</t>
+          <t>A 11810-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6517,14 +6532,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45940</v>
+        <v>45727</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6537,7 +6552,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6580,7 +6595,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 61970-2025</t>
+          <t>A 4188-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6590,14 +6605,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46003</v>
+        <v>45324</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6609,8 +6624,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>9.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6653,7 +6673,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 7745-2025</t>
+          <t>A 2190-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6663,14 +6683,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45706</v>
+        <v>44578</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6682,8 +6702,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>4.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6726,7 +6751,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 15921-2025</t>
+          <t>A 51031-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6740,10 +6765,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45749</v>
+        <v>45211</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6756,7 +6781,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6799,7 +6824,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 15305-2025</t>
+          <t>A 53977-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6809,14 +6834,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45746</v>
+        <v>44876</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6829,7 +6854,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6872,7 +6897,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 6124-2026</t>
+          <t>A 7745-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6882,14 +6907,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46053</v>
+        <v>45706</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6902,7 +6927,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6945,7 +6970,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 16621-2026</t>
+          <t>A 12903-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6959,10 +6984,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46112</v>
+        <v>45385</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6974,13 +6999,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>0.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7023,7 +7043,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 28966-2022</t>
+          <t>A 23185-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7033,14 +7053,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44749</v>
+        <v>45791</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7053,7 +7073,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7096,7 +7116,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 578-2024</t>
+          <t>A 17151-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7110,10 +7130,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45299</v>
+        <v>45412</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7131,7 +7151,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>67.40000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7174,7 +7194,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12988-2024</t>
+          <t>A 17760-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7188,10 +7208,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45385</v>
+        <v>45758</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7203,13 +7223,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>16.2</v>
+        <v>3.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7252,7 +7267,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 61841-2025</t>
+          <t>A 2548-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7266,10 +7281,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46003</v>
+        <v>45313</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7282,7 +7297,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7325,7 +7340,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 4677-2023</t>
+          <t>A 13159-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7339,10 +7354,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44952</v>
+        <v>45386</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7355,7 +7370,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7398,7 +7413,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 4018-2024</t>
+          <t>A 2555-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7412,10 +7427,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45323</v>
+        <v>44579</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7427,13 +7442,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7476,7 +7486,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 4482-2026</t>
+          <t>A 743-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7490,10 +7500,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46045</v>
+        <v>45300</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7511,7 +7521,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>6.5</v>
+        <v>11.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7554,7 +7564,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 6852-2026</t>
+          <t>A 45729-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7568,10 +7578,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46057</v>
+        <v>45579</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7583,13 +7593,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>4.8</v>
+        <v>10.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7632,7 +7637,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 15012-2024</t>
+          <t>A 30040-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7642,14 +7647,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45399</v>
+        <v>45488</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7662,7 +7667,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7705,7 +7710,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 2555-2022</t>
+          <t>A 15075-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7715,14 +7720,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44579</v>
+        <v>45399</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7735,7 +7740,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7778,7 +7783,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 4651-2024</t>
+          <t>A 38787-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7792,10 +7797,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45328</v>
+        <v>45547</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7808,7 +7813,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7851,7 +7856,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 30040-2024</t>
+          <t>A 5565-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7861,14 +7866,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45488</v>
+        <v>45334</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7881,7 +7886,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7924,7 +7929,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 21291-2026</t>
+          <t>A 23310-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7938,10 +7943,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46147</v>
+        <v>44720</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7953,8 +7958,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7997,7 +8007,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 21293-2026</t>
+          <t>A 11887-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8011,10 +8021,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46147</v>
+        <v>45376</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8026,8 +8036,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>2.6</v>
+        <v>6.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8070,7 +8085,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 6357-2024</t>
+          <t>A 10272-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8084,10 +8099,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45338</v>
+        <v>44986</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8101,11 +8116,11 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>7.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8148,7 +8163,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 30673-2023</t>
+          <t>A 7955-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8162,10 +8177,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45112</v>
+        <v>45350</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8177,13 +8192,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8226,7 +8236,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 15288-2026</t>
+          <t>A 15012-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8240,10 +8250,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46105</v>
+        <v>45399</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8256,7 +8266,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.8</v>
+        <v>6.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8299,7 +8309,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 31993-2023</t>
+          <t>A 16483-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8313,10 +8323,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45119</v>
+        <v>45408</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8329,7 +8339,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>6.8</v>
+        <v>0.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8372,7 +8382,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 39796-2025</t>
+          <t>A 11811-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8386,10 +8396,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45891</v>
+        <v>45727</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8402,7 +8412,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8445,7 +8455,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 11894-2024</t>
+          <t>A 55676-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8459,10 +8469,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45376</v>
+        <v>44888</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8474,13 +8484,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8523,7 +8528,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 16483-2024</t>
+          <t>A 12663-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8537,10 +8542,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45408</v>
+        <v>44641</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8552,8 +8557,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>0.7</v>
+        <v>12.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8596,7 +8606,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 16611-2026</t>
+          <t>A 30806-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8610,10 +8620,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46112</v>
+        <v>45112</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8627,7 +8637,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I97" t="n">
@@ -8674,7 +8684,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 38562-2023</t>
+          <t>A 17316-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8688,10 +8698,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45162</v>
+        <v>45414</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8703,8 +8713,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8747,7 +8762,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 51031-2023</t>
+          <t>A 8190-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8761,10 +8776,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45211</v>
+        <v>45338</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8776,8 +8791,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8820,7 +8840,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 59528-2022</t>
+          <t>A 8192-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8834,10 +8854,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44907</v>
+        <v>45338</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8851,11 +8871,11 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8898,7 +8918,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 16027-2022</t>
+          <t>A 47231-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8912,10 +8932,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44665</v>
+        <v>45202</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8927,13 +8947,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8976,7 +8991,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 24002-2026</t>
+          <t>A 28966-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8990,10 +9005,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46167</v>
+        <v>44749</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9006,7 +9021,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>6.4</v>
+        <v>3.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9049,7 +9064,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 6259-2024</t>
+          <t>A 35792-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9063,10 +9078,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45337</v>
+        <v>45861</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9078,8 +9093,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9122,7 +9142,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 15296-2026</t>
+          <t>A 35971-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9136,10 +9156,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46105</v>
+        <v>45863</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9152,7 +9172,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9195,7 +9215,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 1199-2024</t>
+          <t>A 578-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9209,10 +9229,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45302</v>
+        <v>45299</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9230,7 +9250,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>16.1</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9273,7 +9293,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 26473-2024</t>
+          <t>A 6357-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9287,10 +9307,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45469</v>
+        <v>45338</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9302,8 +9322,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9346,7 +9371,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 17778-2024</t>
+          <t>A 48171-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9360,10 +9385,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45418</v>
+        <v>45933</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9375,13 +9400,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9424,7 +9444,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 23621-2026</t>
+          <t>A 39791-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9438,10 +9458,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46162</v>
+        <v>45891</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9497,7 +9517,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 8190-2024</t>
+          <t>A 15158-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9511,10 +9531,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45338</v>
+        <v>45744</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9526,13 +9546,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9575,7 +9590,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 8192-2024</t>
+          <t>A 43306-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9589,10 +9604,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45338</v>
+        <v>45910</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9604,13 +9619,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9653,7 +9663,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 17151-2024</t>
+          <t>A 49913-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9663,14 +9673,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45412</v>
+        <v>45940</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9682,13 +9692,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9731,7 +9736,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 24987-2026</t>
+          <t>A 49815-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9745,10 +9750,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46174</v>
+        <v>45940</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9761,7 +9766,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9804,7 +9809,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 12181-2023</t>
+          <t>A 4969-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9818,10 +9823,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44998</v>
+        <v>46049</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9833,8 +9838,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9877,7 +9887,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 23310-2022</t>
+          <t>A 61970-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9887,14 +9897,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44720</v>
+        <v>46003</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9906,13 +9916,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9955,7 +9960,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 5027-2024</t>
+          <t>A 6124-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9969,10 +9974,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45329</v>
+        <v>46053</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9984,13 +9989,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10033,7 +10033,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 743-2024</t>
+          <t>A 16621-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10047,10 +10047,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45300</v>
+        <v>46112</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10064,11 +10064,11 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>11.1</v>
+        <v>0.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10111,7 +10111,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 53977-2022</t>
+          <t>A 61841-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10125,10 +10125,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44876</v>
+        <v>46003</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10184,7 +10184,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 31134-2026</t>
+          <t>A 4482-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10198,10 +10198,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46216</v>
+        <v>46045</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 35897-2026</t>
+          <t>A 6852-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10276,10 +10276,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46266</v>
+        <v>46057</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10291,8 +10291,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10335,7 +10340,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 4188-2024</t>
+          <t>A 21291-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10349,10 +10354,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45324</v>
+        <v>46147</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10364,13 +10369,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>9.6</v>
+        <v>3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10413,7 +10413,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 12663-2022</t>
+          <t>A 21293-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10427,10 +10427,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44641</v>
+        <v>46147</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10442,13 +10442,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>12.4</v>
+        <v>2.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10491,7 +10486,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 25597-2026</t>
+          <t>A 15288-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10505,10 +10500,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46177</v>
+        <v>46105</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10521,7 +10516,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10564,7 +10559,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 36180-2024</t>
+          <t>A 39796-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10578,10 +10573,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45534</v>
+        <v>45891</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10594,7 +10589,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10637,7 +10632,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 12903-2024</t>
+          <t>A 16611-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10651,10 +10646,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45385</v>
+        <v>46112</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10666,8 +10661,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>9.199999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10710,7 +10710,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 15075-2024</t>
+          <t>A 24002-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10724,10 +10724,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45399</v>
+        <v>46167</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.7</v>
+        <v>6.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10783,7 +10783,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 11887-2024</t>
+          <t>A 15296-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10797,10 +10797,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45376</v>
+        <v>46105</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10812,13 +10812,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>6.3</v>
+        <v>0.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10861,7 +10856,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 37743-2026</t>
+          <t>A 23621-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10875,10 +10870,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46279</v>
+        <v>46162</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10891,7 +10886,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10934,7 +10929,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 38074-2026</t>
+          <t>A 24987-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10948,10 +10943,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46280</v>
+        <v>46174</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10964,7 +10959,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11007,7 +11002,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 5565-2024</t>
+          <t>A 31134-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11021,10 +11016,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45334</v>
+        <v>46216</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11036,8 +11031,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11080,7 +11080,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 32955-2026</t>
+          <t>A 35897-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11094,10 +11094,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46244</v>
+        <v>46266</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11153,7 +11153,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 32948-2026</t>
+          <t>A 38074-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11167,10 +11167,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46244</v>
+        <v>46280</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11226,7 +11226,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 35742-2024</t>
+          <t>A 32948-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11240,10 +11240,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45532</v>
+        <v>46244</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11299,7 +11299,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 10908-2026</t>
+          <t>A 32955-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11313,10 +11313,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46079</v>
+        <v>46244</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11372,7 +11372,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 35715-2024</t>
+          <t>A 10908-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11386,10 +11386,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45532</v>
+        <v>46079</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11445,7 +11445,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 11806-2025</t>
+          <t>A 40128-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11459,10 +11459,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45727</v>
+        <v>46293</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11518,7 +11518,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 11810-2025</t>
+          <t>A 40129-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11532,10 +11532,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45727</v>
+        <v>46293</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11591,7 +11591,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 40128-2026</t>
+          <t>A 25597-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11605,10 +11605,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46293</v>
+        <v>46177</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11664,7 +11664,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 40129-2026</t>
+          <t>A 37743-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11678,10 +11678,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46293</v>
+        <v>46279</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>45537</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>

--- a/Översikt TOMELILLA.xlsx
+++ b/Översikt TOMELILLA.xlsx
@@ -601,7 +601,7 @@
         <v>44756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45120</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45260</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2018-2024</t>
+          <t>A 14152-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45308</v>
+        <v>45009</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>17.2</v>
+        <v>3.5</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1125,10 +1125,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1140,153 +1140,153 @@
         <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Kråka
+Röd glada</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 14152-2023 artfynd.xlsx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 14152-2023 karta.png", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 14152-2023 georefererad karta.tif", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 14152-2023 FSC-klagomål.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 14152-2023 FSC-klagomål mail.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 14152-2023 tillsynsbegäran.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 14152-2023 tillsynsbegäran mail.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 14152-2023 prioriterade fågelarter.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 2018-2024</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45308</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TOMELILLA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Västlig hakmossa
 Röd glada</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2018-2024 artfynd.xlsx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2018-2024 karta.png", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2018-2024 georefererad karta.tif", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2018-2024 FSC-klagomål.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2018-2024 FSC-klagomål mail.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2018-2024 tillsynsbegäran.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2018-2024 tillsynsbegäran mail.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 2018-2024 prioriterade fågelarter.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 14152-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45009</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>TOMELILLA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Kråka
-Röd glada</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 14152-2023 artfynd.xlsx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 14152-2023 karta.png", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 14152-2023 georefererad karta.tif", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 14152-2023 FSC-klagomål.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 14152-2023 FSC-klagomål mail.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 14152-2023 tillsynsbegäran.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 14152-2023 tillsynsbegäran mail.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 14152-2023 prioriterade fågelarter.docx", "A 14152-2023")</f>
         <v/>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
         <v>45299</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>45429</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45744</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>44613</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>44721</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 42387-2022</t>
+          <t>A 6261-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44830</v>
+        <v>45337</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1875,16 +1875,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.1</v>
+        <v>12.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1911,46 +1911,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 42387-2022 artfynd.xlsx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 42387-2022 karta.png", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 42387-2022 georefererad karta.tif", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 42387-2022 FSC-klagomål.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 42387-2022 FSC-klagomål mail.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 42387-2022 tillsynsbegäran.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 42387-2022 tillsynsbegäran mail.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 60820-2023</t>
+          <t>A 49813-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45260</v>
+        <v>45940</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1980,13 +1980,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -2020,42 +2020,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 60820-2023 artfynd.xlsx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 49813-2025 artfynd.xlsx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 60820-2023 karta.png", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 49813-2025 karta.png", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 60820-2023 georefererad karta.tif", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 49813-2025 georefererad karta.tif", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 60820-2023 FSC-klagomål.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 49813-2025 FSC-klagomål.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 60820-2023 FSC-klagomål mail.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 49813-2025 FSC-klagomål mail.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 60820-2023 tillsynsbegäran.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 49813-2025 tillsynsbegäran.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 60820-2023 tillsynsbegäran mail.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 49813-2025 tillsynsbegäran mail.docx", "A 49813-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28862-2023</t>
+          <t>A 61314-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45104</v>
+        <v>46000</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2084,13 +2084,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>6.6</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2130,35 +2125,35 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 28862-2023 georefererad karta.tif", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 28862-2023 FSC-klagomål.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 28862-2023 FSC-klagomål mail.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 28862-2023 tillsynsbegäran.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 28862-2023 tillsynsbegäran mail.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
     </row>
@@ -2182,7 +2177,7 @@
         <v>44578</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2275,7 +2270,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 17907-2024</t>
+          <t>A 6261-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2289,10 +2284,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45419</v>
+        <v>45337</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2305,13 +2300,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.1</v>
+        <v>12.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2345,42 +2340,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Gulplister</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 17907-2024 artfynd.xlsx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 17907-2024 karta.png", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 17907-2024 georefererad karta.tif", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 17907-2024 FSC-klagomål.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 17907-2024 FSC-klagomål mail.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 17907-2024 tillsynsbegäran.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 17907-2024 tillsynsbegäran mail.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 756-2024</t>
+          <t>A 26958-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2394,10 +2389,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45300</v>
+        <v>45811</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2409,22 +2404,17 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>13.1</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2439,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2455,42 +2445,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 756-2024 artfynd.xlsx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26958-2025 artfynd.xlsx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 756-2024 karta.png", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26958-2025 karta.png", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 756-2024 georefererad karta.tif", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26958-2025 georefererad karta.tif", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 756-2024 FSC-klagomål.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26958-2025 FSC-klagomål.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 756-2024 FSC-klagomål mail.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26958-2025 FSC-klagomål mail.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 756-2024 tillsynsbegäran.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26958-2025 tillsynsbegäran.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 756-2024 tillsynsbegäran mail.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26958-2025 tillsynsbegäran mail.docx", "A 26958-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 6261-2024</t>
+          <t>A 6262-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2507,7 +2497,7 @@
         <v>45337</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2520,13 +2510,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>12.6</v>
+        <v>4.5</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2560,42 +2550,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6262-2024 artfynd.xlsx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6262-2024 karta.png", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6262-2024 georefererad karta.tif", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6262-2024 FSC-klagomål.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6262-2024 FSC-klagomål mail.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6262-2024 tillsynsbegäran.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6262-2024 tillsynsbegäran mail.docx", "A 6262-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 6262-2024</t>
+          <t>A 28862-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2609,10 +2599,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45337</v>
+        <v>45104</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2624,8 +2614,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2661,46 +2656,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6262-2024 artfynd.xlsx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6262-2024 karta.png", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6262-2024 georefererad karta.tif", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 28862-2023 georefererad karta.tif", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6262-2024 FSC-klagomål.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 28862-2023 FSC-klagomål.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6262-2024 FSC-klagomål mail.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 28862-2023 FSC-klagomål mail.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6262-2024 tillsynsbegäran.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 28862-2023 tillsynsbegäran.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6262-2024 tillsynsbegäran mail.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 28862-2023 tillsynsbegäran mail.docx", "A 28862-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 26958-2025</t>
+          <t>A 20397-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2714,10 +2709,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45811</v>
+        <v>46139</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2730,13 +2725,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2770,42 +2765,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26958-2025 artfynd.xlsx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 20397-2026 artfynd.xlsx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26958-2025 karta.png", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 20397-2026 karta.png", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26958-2025 georefererad karta.tif", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 20397-2026 georefererad karta.tif", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26958-2025 FSC-klagomål.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 20397-2026 FSC-klagomål.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26958-2025 FSC-klagomål mail.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 20397-2026 FSC-klagomål mail.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26958-2025 tillsynsbegäran.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 20397-2026 tillsynsbegäran.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26958-2025 tillsynsbegäran mail.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 20397-2026 tillsynsbegäran mail.docx", "A 20397-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 6261-2024</t>
+          <t>A 60820-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2819,10 +2814,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45337</v>
+        <v>45260</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2835,7 +2830,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>12.6</v>
+        <v>4.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2871,46 +2866,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 60820-2023 artfynd.xlsx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 60820-2023 karta.png", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 60820-2023 georefererad karta.tif", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 60820-2023 FSC-klagomål.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 60820-2023 FSC-klagomål mail.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 60820-2023 tillsynsbegäran.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 60820-2023 tillsynsbegäran mail.docx", "A 60820-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49813-2025</t>
+          <t>A 42387-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2924,10 +2919,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45940</v>
+        <v>44830</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2940,17 +2935,17 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
@@ -2964,7 +2959,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2980,42 +2975,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 49813-2025 artfynd.xlsx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 42387-2022 artfynd.xlsx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 49813-2025 karta.png", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 42387-2022 karta.png", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 49813-2025 georefererad karta.tif", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 42387-2022 georefererad karta.tif", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 49813-2025 FSC-klagomål.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 42387-2022 FSC-klagomål.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 49813-2025 FSC-klagomål mail.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 42387-2022 FSC-klagomål mail.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 49813-2025 tillsynsbegäran.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 42387-2022 tillsynsbegäran.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 49813-2025 tillsynsbegäran mail.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 42387-2022 tillsynsbegäran mail.docx", "A 42387-2022")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 61314-2025</t>
+          <t>A 756-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3029,10 +3024,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46000</v>
+        <v>45300</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3044,18 +3039,23 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>13.1</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3085,42 +3085,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 756-2024 artfynd.xlsx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 756-2024 karta.png", "A 756-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 756-2024 georefererad karta.tif", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 756-2024 FSC-klagomål.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 756-2024 FSC-klagomål mail.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 756-2024 tillsynsbegäran.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 756-2024 tillsynsbegäran mail.docx", "A 756-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 20397-2026</t>
+          <t>A 32949-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3134,10 +3134,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46139</v>
+        <v>46244</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3190,42 +3190,46 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 20397-2026 artfynd.xlsx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 32949-2026 artfynd.xlsx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 20397-2026 karta.png", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 32949-2026 karta.png", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 20397-2026 georefererad karta.tif", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 32949-2026 georefererad karta.tif", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 20397-2026 FSC-klagomål.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 32949-2026 FSC-klagomål.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 20397-2026 FSC-klagomål mail.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 32949-2026 FSC-klagomål mail.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 20397-2026 tillsynsbegäran.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 32949-2026 tillsynsbegäran.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 20397-2026 tillsynsbegäran mail.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 32949-2026 tillsynsbegäran mail.docx", "A 32949-2026")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 32949-2026 prioriterade fågelarter.docx", "A 32949-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32949-2026</t>
+          <t>A 26823-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3239,10 +3243,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46244</v>
+        <v>46183</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3255,17 +3259,17 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.8</v>
+        <v>12.1</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
@@ -3279,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3295,46 +3299,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 32949-2026 artfynd.xlsx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26823-2026 artfynd.xlsx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 32949-2026 karta.png", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26823-2026 karta.png", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 32949-2026 georefererad karta.tif", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26823-2026 georefererad karta.tif", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 32949-2026 FSC-klagomål.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26823-2026 FSC-klagomål.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 32949-2026 FSC-klagomål mail.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26823-2026 FSC-klagomål mail.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 32949-2026 tillsynsbegäran.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26823-2026 tillsynsbegäran.docx", "A 26823-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 32949-2026 tillsynsbegäran mail.docx", "A 32949-2026")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 32949-2026 prioriterade fågelarter.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26823-2026 tillsynsbegäran mail.docx", "A 26823-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 26823-2026</t>
+          <t>A 17907-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46183</v>
+        <v>45419</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>12.1</v>
+        <v>3.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3373,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3400,39 +3400,39 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Gulplister</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26823-2026 artfynd.xlsx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 17907-2024 artfynd.xlsx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26823-2026 karta.png", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 17907-2024 karta.png", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26823-2026 georefererad karta.tif", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 17907-2024 georefererad karta.tif", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26823-2026 FSC-klagomål.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 17907-2024 FSC-klagomål.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26823-2026 FSC-klagomål mail.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 17907-2024 FSC-klagomål mail.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26823-2026 tillsynsbegäran.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 17907-2024 tillsynsbegäran.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26823-2026 tillsynsbegäran mail.docx", "A 26823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 17907-2024 tillsynsbegäran mail.docx", "A 17907-2024")</f>
         <v/>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
         <v>44684</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44560</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44490</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44642</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44721</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 36180-2024</t>
+          <t>A 47231-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45534</v>
+        <v>45202</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4038,7 +4038,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 23813-2024</t>
+          <t>A 4023-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45455</v>
+        <v>45323</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4067,8 +4067,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>15.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4111,7 +4116,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8455-2024</t>
+          <t>A 11802-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4125,10 +4130,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45354</v>
+        <v>45375</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4146,7 +4151,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4189,7 +4194,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 16027-2022</t>
+          <t>A 19454-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4203,10 +4208,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44665</v>
+        <v>45429</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4218,13 +4223,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4267,7 +4267,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 31993-2023</t>
+          <t>A 23813-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45119</v>
+        <v>45455</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.8</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 19454-2024</t>
+          <t>A 24248-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4354,10 +4354,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45429</v>
+        <v>45457</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 16568-2024</t>
+          <t>A 2548-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45408</v>
+        <v>45313</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4486,7 +4486,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 4677-2023</t>
+          <t>A 23185-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4496,14 +4496,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44952</v>
+        <v>45791</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 59528-2022</t>
+          <t>A 17760-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4573,10 +4573,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44907</v>
+        <v>45758</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4588,13 +4588,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4637,7 +4632,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30673-2023</t>
+          <t>A 44675-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4647,14 +4642,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45112</v>
+        <v>45574</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4668,11 +4663,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.4</v>
+        <v>11.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4715,7 +4710,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 11802-2024</t>
+          <t>A 49815-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4729,10 +4724,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45375</v>
+        <v>45940</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4744,13 +4739,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4793,7 +4783,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11894-2024</t>
+          <t>A 15158-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4807,10 +4797,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45376</v>
+        <v>45744</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4822,13 +4812,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4871,7 +4856,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 4651-2024</t>
+          <t>A 17316-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4885,10 +4870,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45328</v>
+        <v>45414</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4900,8 +4885,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4944,7 +4934,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 24248-2024</t>
+          <t>A 4969-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4958,10 +4948,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45457</v>
+        <v>46049</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4973,8 +4963,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5017,7 +5012,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 12988-2024</t>
+          <t>A 38787-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5031,10 +5026,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45385</v>
+        <v>45547</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5046,13 +5041,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>16.2</v>
+        <v>1.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5095,7 +5085,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 15305-2025</t>
+          <t>A 43306-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5105,14 +5095,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45746</v>
+        <v>45910</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5125,7 +5115,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5168,7 +5158,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 60817-2023</t>
+          <t>A 45729-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5182,10 +5172,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45260</v>
+        <v>45579</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5198,7 +5188,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.3</v>
+        <v>10.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5241,7 +5231,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 4023-2024</t>
+          <t>A 16568-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5255,10 +5245,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45323</v>
+        <v>45408</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5270,13 +5260,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>15.2</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5319,7 +5304,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 1199-2024</t>
+          <t>A 12310-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5333,10 +5318,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45302</v>
+        <v>44999</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5350,11 +5335,11 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>16.1</v>
+        <v>2.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5397,7 +5382,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 5027-2024</t>
+          <t>A 60817-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5411,10 +5396,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45329</v>
+        <v>45260</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5426,13 +5411,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5475,7 +5455,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 4018-2024</t>
+          <t>A 7955-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5489,10 +5469,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45323</v>
+        <v>45350</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5504,13 +5484,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5553,7 +5528,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 6259-2024</t>
+          <t>A 48171-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5567,10 +5542,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45337</v>
+        <v>45933</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5583,7 +5558,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5626,7 +5601,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 6316-2024</t>
+          <t>A 42794-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5640,10 +5615,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45338</v>
+        <v>45566</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5655,13 +5630,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>28.6</v>
+        <v>1.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5704,7 +5674,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 12181-2023</t>
+          <t>A 61970-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5714,14 +5684,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44998</v>
+        <v>46003</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5734,7 +5704,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5777,7 +5747,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 38562-2023</t>
+          <t>A 39791-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5791,10 +5761,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45162</v>
+        <v>45891</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5807,7 +5777,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5850,7 +5820,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 12310-2023</t>
+          <t>A 2190-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5864,10 +5834,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44999</v>
+        <v>44578</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5885,7 +5855,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5928,7 +5898,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 42794-2024</t>
+          <t>A 10272-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5942,10 +5912,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45566</v>
+        <v>44986</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5957,8 +5927,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1.9</v>
+        <v>7.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6001,7 +5976,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 17778-2024</t>
+          <t>A 55676-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6015,10 +5990,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45418</v>
+        <v>44888</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6030,13 +6005,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6079,7 +6049,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 15921-2025</t>
+          <t>A 6124-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6093,10 +6063,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45749</v>
+        <v>46053</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6109,7 +6079,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6152,7 +6122,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 44675-2024</t>
+          <t>A 30806-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6162,14 +6132,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45574</v>
+        <v>45112</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6183,11 +6153,11 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>11.2</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6230,7 +6200,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 35742-2024</t>
+          <t>A 16621-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6244,10 +6214,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45532</v>
+        <v>46112</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6259,8 +6229,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6303,7 +6278,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 35715-2024</t>
+          <t>A 6316-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6317,10 +6292,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45532</v>
+        <v>45338</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6332,8 +6307,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>28.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6376,7 +6356,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 26473-2024</t>
+          <t>A 11811-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6390,10 +6370,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45469</v>
+        <v>45727</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6406,7 +6386,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6449,7 +6429,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 11806-2025</t>
+          <t>A 8455-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6463,10 +6443,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45727</v>
+        <v>45354</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6478,8 +6458,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6522,7 +6507,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 11810-2025</t>
+          <t>A 13159-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6536,10 +6521,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45727</v>
+        <v>45386</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6552,7 +6537,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6595,7 +6580,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 4188-2024</t>
+          <t>A 49913-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6605,14 +6590,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45324</v>
+        <v>45940</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6624,13 +6609,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>9.6</v>
+        <v>0.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6673,7 +6653,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 2190-2022</t>
+          <t>A 61841-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6687,10 +6667,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44578</v>
+        <v>46003</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6702,13 +6682,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>4.9</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6751,7 +6726,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 51031-2023</t>
+          <t>A 7745-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6761,14 +6736,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45211</v>
+        <v>45706</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6781,7 +6756,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6824,7 +6799,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 53977-2022</t>
+          <t>A 15921-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6838,10 +6813,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44876</v>
+        <v>45749</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6854,7 +6829,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6897,7 +6872,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 7745-2025</t>
+          <t>A 35792-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6907,14 +6882,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45706</v>
+        <v>45861</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6926,8 +6901,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6970,7 +6950,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 12903-2024</t>
+          <t>A 35971-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6984,10 +6964,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45385</v>
+        <v>45863</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7000,7 +6980,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>9.199999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7043,7 +7023,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23185-2025</t>
+          <t>A 4482-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7053,14 +7033,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45791</v>
+        <v>46045</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7072,8 +7052,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>6.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7116,7 +7101,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 17151-2024</t>
+          <t>A 15305-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7126,14 +7111,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45412</v>
+        <v>45746</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7145,13 +7130,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7194,7 +7174,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 17760-2025</t>
+          <t>A 6852-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7208,10 +7188,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45758</v>
+        <v>46057</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7223,8 +7203,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7267,7 +7252,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 2548-2024</t>
+          <t>A 28966-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7277,14 +7262,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45313</v>
+        <v>44749</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7297,7 +7282,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7340,7 +7325,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13159-2024</t>
+          <t>A 578-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7354,10 +7339,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45386</v>
+        <v>45299</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7369,8 +7354,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7413,7 +7403,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 2555-2022</t>
+          <t>A 21291-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7427,10 +7417,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44579</v>
+        <v>46147</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7443,7 +7433,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7486,7 +7476,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 743-2024</t>
+          <t>A 21293-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7500,10 +7490,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45300</v>
+        <v>46147</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7515,13 +7505,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>11.1</v>
+        <v>2.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7564,7 +7549,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 45729-2024</t>
+          <t>A 12988-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7578,10 +7563,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45579</v>
+        <v>45385</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7593,8 +7578,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>10.1</v>
+        <v>16.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7637,7 +7627,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 30040-2024</t>
+          <t>A 15288-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7647,14 +7637,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45488</v>
+        <v>46105</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7667,7 +7657,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7710,7 +7700,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 15075-2024</t>
+          <t>A 39796-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7720,14 +7710,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45399</v>
+        <v>45891</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7740,7 +7730,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7783,7 +7773,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 38787-2024</t>
+          <t>A 4677-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7797,10 +7787,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45547</v>
+        <v>44952</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7813,7 +7803,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7856,7 +7846,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 5565-2024</t>
+          <t>A 4018-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7870,10 +7860,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45334</v>
+        <v>45323</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7885,8 +7875,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7929,7 +7924,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 23310-2022</t>
+          <t>A 16611-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7943,10 +7938,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44720</v>
+        <v>46112</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7960,11 +7955,11 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8007,7 +8002,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 11887-2024</t>
+          <t>A 15012-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8021,10 +8016,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45376</v>
+        <v>45399</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8036,13 +8031,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8085,7 +8075,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 10272-2023</t>
+          <t>A 2555-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8099,10 +8089,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44986</v>
+        <v>44579</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8114,13 +8104,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>7.7</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8163,7 +8148,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 7955-2024</t>
+          <t>A 24002-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8173,14 +8158,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45350</v>
+        <v>46167</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8193,7 +8178,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.2</v>
+        <v>6.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8236,7 +8221,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 15012-2024</t>
+          <t>A 4651-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8250,10 +8235,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45399</v>
+        <v>45328</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8266,7 +8251,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>6.9</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8309,7 +8294,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 16483-2024</t>
+          <t>A 30040-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8319,14 +8304,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45408</v>
+        <v>45488</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8339,7 +8324,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8382,7 +8367,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 11811-2025</t>
+          <t>A 15296-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8396,10 +8381,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45727</v>
+        <v>46105</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8412,7 +8397,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>9.699999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8455,7 +8440,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 55676-2022</t>
+          <t>A 6357-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8469,10 +8454,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44888</v>
+        <v>45338</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8484,8 +8469,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8528,7 +8518,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 12663-2022</t>
+          <t>A 30673-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8542,10 +8532,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44641</v>
+        <v>45112</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8563,7 +8553,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8606,7 +8596,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 30806-2023</t>
+          <t>A 31993-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8620,10 +8610,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45112</v>
+        <v>45119</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8635,13 +8625,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>6.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8684,7 +8669,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 17316-2024</t>
+          <t>A 11894-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8698,10 +8683,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45414</v>
+        <v>45376</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8719,7 +8704,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8762,7 +8747,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 8190-2024</t>
+          <t>A 16483-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8776,10 +8761,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45338</v>
+        <v>45408</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8791,13 +8776,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8840,7 +8820,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 8192-2024</t>
+          <t>A 23621-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8854,10 +8834,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45338</v>
+        <v>46162</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8869,13 +8849,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8918,7 +8893,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 47231-2023</t>
+          <t>A 24987-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8932,10 +8907,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45202</v>
+        <v>46174</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8948,7 +8923,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8991,7 +8966,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 28966-2022</t>
+          <t>A 38562-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9001,14 +8976,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44749</v>
+        <v>45162</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9021,7 +8996,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9064,7 +9039,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 35792-2025</t>
+          <t>A 51031-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9078,10 +9053,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45861</v>
+        <v>45211</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9093,13 +9068,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9142,7 +9112,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 35971-2025</t>
+          <t>A 59528-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9156,10 +9126,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45863</v>
+        <v>44907</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9171,8 +9141,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9215,7 +9190,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 578-2024</t>
+          <t>A 16027-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9229,10 +9204,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45299</v>
+        <v>44665</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9250,7 +9225,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>67.40000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9293,7 +9268,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 6357-2024</t>
+          <t>A 6259-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9307,10 +9282,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45338</v>
+        <v>45337</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9322,13 +9297,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9371,7 +9341,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 48171-2025</t>
+          <t>A 31134-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9385,10 +9355,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45933</v>
+        <v>46216</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9400,8 +9370,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9444,7 +9419,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 39791-2025</t>
+          <t>A 35897-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9458,10 +9433,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45891</v>
+        <v>46266</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9474,7 +9449,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9517,7 +9492,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 15158-2025</t>
+          <t>A 1199-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9531,10 +9506,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45744</v>
+        <v>45302</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9546,8 +9521,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>1.8</v>
+        <v>16.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9590,7 +9570,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 43306-2025</t>
+          <t>A 26473-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9604,10 +9584,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45910</v>
+        <v>45469</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9620,7 +9600,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9663,7 +9643,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 49913-2025</t>
+          <t>A 17778-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9673,14 +9653,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45940</v>
+        <v>45418</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9692,8 +9672,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9736,7 +9721,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 49815-2025</t>
+          <t>A 8190-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9750,10 +9735,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45940</v>
+        <v>45338</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9765,8 +9750,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9809,7 +9799,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 4969-2026</t>
+          <t>A 8192-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9823,10 +9813,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46049</v>
+        <v>45338</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9840,11 +9830,11 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9887,7 +9877,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 61970-2025</t>
+          <t>A 17151-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9897,14 +9887,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46003</v>
+        <v>45412</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9916,8 +9906,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9960,7 +9955,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 6124-2026</t>
+          <t>A 12181-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9974,10 +9969,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46053</v>
+        <v>44998</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9990,7 +9985,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10033,7 +10028,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 16621-2026</t>
+          <t>A 23310-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10047,10 +10042,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46112</v>
+        <v>44720</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10064,11 +10059,11 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.4</v>
+        <v>5.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10111,7 +10106,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 61841-2025</t>
+          <t>A 38074-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10125,10 +10120,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46003</v>
+        <v>46280</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10141,7 +10136,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10184,7 +10179,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 4482-2026</t>
+          <t>A 5027-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10198,10 +10193,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46045</v>
+        <v>45329</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10219,7 +10214,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>6.5</v>
+        <v>4.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10262,7 +10257,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 6852-2026</t>
+          <t>A 743-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10276,10 +10271,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46057</v>
+        <v>45300</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10297,7 +10292,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>4.8</v>
+        <v>11.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10340,7 +10335,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 21291-2026</t>
+          <t>A 53977-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10354,10 +10349,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46147</v>
+        <v>44876</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10370,7 +10365,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10413,7 +10408,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 21293-2026</t>
+          <t>A 32955-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10427,10 +10422,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46147</v>
+        <v>46244</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10443,7 +10438,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10486,7 +10481,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 15288-2026</t>
+          <t>A 32948-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10500,10 +10495,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46105</v>
+        <v>46244</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10516,7 +10511,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4.8</v>
+        <v>1.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10559,7 +10554,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 39796-2025</t>
+          <t>A 10908-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10573,10 +10568,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45891</v>
+        <v>46079</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10589,7 +10584,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10632,7 +10627,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 16611-2026</t>
+          <t>A 4188-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10646,10 +10641,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46112</v>
+        <v>45324</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10663,11 +10658,11 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.7</v>
+        <v>9.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10710,7 +10705,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 24002-2026</t>
+          <t>A 12663-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10720,14 +10715,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46167</v>
+        <v>44641</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10739,8 +10734,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>6.4</v>
+        <v>12.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10783,7 +10783,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 15296-2026</t>
+          <t>A 40128-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10797,10 +10797,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46105</v>
+        <v>46293</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10856,7 +10856,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 23621-2026</t>
+          <t>A 40129-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10870,10 +10870,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46162</v>
+        <v>46293</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10929,7 +10929,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 24987-2026</t>
+          <t>A 36180-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10943,10 +10943,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46174</v>
+        <v>45534</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11002,7 +11002,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 31134-2026</t>
+          <t>A 25597-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11016,10 +11016,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46216</v>
+        <v>46177</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11031,13 +11031,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11080,7 +11075,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 35897-2026</t>
+          <t>A 37743-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11094,10 +11089,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46266</v>
+        <v>46279</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11110,7 +11105,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11153,7 +11148,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 38074-2026</t>
+          <t>A 12903-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11167,10 +11162,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46280</v>
+        <v>45385</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11183,7 +11178,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>4.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11226,7 +11221,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 32948-2026</t>
+          <t>A 15075-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11236,14 +11231,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46244</v>
+        <v>45399</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11256,7 +11251,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11299,7 +11294,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 32955-2026</t>
+          <t>A 11887-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11313,10 +11308,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46244</v>
+        <v>45376</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11328,8 +11323,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11372,7 +11372,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 10908-2026</t>
+          <t>A 5565-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11386,10 +11386,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46079</v>
+        <v>45334</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11445,7 +11445,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 40128-2026</t>
+          <t>A 35742-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11459,10 +11459,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46293</v>
+        <v>45532</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11518,7 +11518,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 40129-2026</t>
+          <t>A 35715-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11532,10 +11532,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46293</v>
+        <v>45532</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 25597-2026</t>
+          <t>A 11806-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11605,10 +11605,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46177</v>
+        <v>45727</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11664,7 +11664,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 37743-2026</t>
+          <t>A 11810-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11678,10 +11678,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46279</v>
+        <v>45727</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11694,7 +11694,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11754,7 +11754,7 @@
         <v>45537</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>

--- a/Översikt TOMELILLA.xlsx
+++ b/Översikt TOMELILLA.xlsx
@@ -601,7 +601,7 @@
         <v>44756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45120</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45260</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 14152-2023</t>
+          <t>A 2018-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45009</v>
+        <v>45308</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.5</v>
+        <v>17.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1125,10 +1125,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1140,153 +1140,153 @@
         <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Västlig hakmossa
+Röd glada</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2018-2024 artfynd.xlsx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2018-2024 karta.png", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2018-2024 georefererad karta.tif", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2018-2024 FSC-klagomål.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2018-2024 FSC-klagomål mail.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2018-2024 tillsynsbegäran.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2018-2024 tillsynsbegäran mail.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 2018-2024 prioriterade fågelarter.docx", "A 2018-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 14152-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45009</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TOMELILLA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Kråka
 Röd glada</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 14152-2023 artfynd.xlsx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 14152-2023 karta.png", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 14152-2023 georefererad karta.tif", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 14152-2023 FSC-klagomål.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 14152-2023 FSC-klagomål mail.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 14152-2023 tillsynsbegäran.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 14152-2023 tillsynsbegäran mail.docx", "A 14152-2023")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 14152-2023 prioriterade fågelarter.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 2018-2024</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45308</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>TOMELILLA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Västlig hakmossa
-Röd glada</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2018-2024 artfynd.xlsx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2018-2024 karta.png", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2018-2024 georefererad karta.tif", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2018-2024 FSC-klagomål.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2018-2024 FSC-klagomål mail.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2018-2024 tillsynsbegäran.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2018-2024 tillsynsbegäran mail.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 2018-2024 prioriterade fågelarter.docx", "A 2018-2024")</f>
         <v/>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
         <v>45299</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>45429</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45744</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>44613</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>44721</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 6261-2024</t>
+          <t>A 17907-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45337</v>
+        <v>45419</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1875,13 +1875,13 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>12.6</v>
+        <v>3.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1915,42 +1915,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Gulplister</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 17907-2024 artfynd.xlsx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 17907-2024 karta.png", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 17907-2024 georefererad karta.tif", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 17907-2024 FSC-klagomål.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 17907-2024 FSC-klagomål mail.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 17907-2024 tillsynsbegäran.docx", "A 17907-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 17907-2024 tillsynsbegäran mail.docx", "A 17907-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 49813-2025</t>
+          <t>A 6261-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45940</v>
+        <v>45337</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1980,13 +1980,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.5</v>
+        <v>12.6</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -2016,46 +2016,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 49813-2025 artfynd.xlsx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 49813-2025 karta.png", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 49813-2025 georefererad karta.tif", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 49813-2025 FSC-klagomål.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 49813-2025 FSC-klagomål mail.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 49813-2025 tillsynsbegäran.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 49813-2025 tillsynsbegäran mail.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 61314-2025</t>
+          <t>A 49813-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46000</v>
+        <v>45940</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2125,42 +2125,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 49813-2025 artfynd.xlsx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 49813-2025 karta.png", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 49813-2025 georefererad karta.tif", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 49813-2025 FSC-klagomål.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 49813-2025 FSC-klagomål mail.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 49813-2025 tillsynsbegäran.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 49813-2025 tillsynsbegäran mail.docx", "A 49813-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 2193-2022</t>
+          <t>A 61314-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44578</v>
+        <v>46000</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2189,22 +2189,17 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2219,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2231,39 +2226,39 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Skogslysing</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2193-2022 artfynd.xlsx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2193-2022 karta.png", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2193-2022 georefererad karta.tif", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2193-2022 FSC-klagomål.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2193-2022 FSC-klagomål mail.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2193-2022 tillsynsbegäran.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2193-2022 tillsynsbegäran mail.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
     </row>
@@ -2287,7 +2282,7 @@
         <v>45337</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2375,7 +2370,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 26958-2025</t>
+          <t>A 2193-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2389,10 +2384,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45811</v>
+        <v>44578</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2404,18 +2399,23 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2441,46 +2441,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Skogslysing</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26958-2025 artfynd.xlsx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2193-2022 artfynd.xlsx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26958-2025 karta.png", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2193-2022 karta.png", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26958-2025 georefererad karta.tif", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2193-2022 georefererad karta.tif", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26958-2025 FSC-klagomål.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2193-2022 FSC-klagomål.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26958-2025 FSC-klagomål mail.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2193-2022 FSC-klagomål mail.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26958-2025 tillsynsbegäran.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2193-2022 tillsynsbegäran.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26958-2025 tillsynsbegäran mail.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2193-2022 tillsynsbegäran mail.docx", "A 2193-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 6262-2024</t>
+          <t>A 26958-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45337</v>
+        <v>45811</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2546,46 +2546,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6262-2024 artfynd.xlsx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26958-2025 artfynd.xlsx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6262-2024 karta.png", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26958-2025 karta.png", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6262-2024 georefererad karta.tif", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26958-2025 georefererad karta.tif", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6262-2024 FSC-klagomål.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26958-2025 FSC-klagomål.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6262-2024 FSC-klagomål mail.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26958-2025 FSC-klagomål mail.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6262-2024 tillsynsbegäran.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26958-2025 tillsynsbegäran.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6262-2024 tillsynsbegäran mail.docx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26958-2025 tillsynsbegäran mail.docx", "A 26958-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 28862-2023</t>
+          <t>A 6262-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45104</v>
+        <v>45337</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2614,13 +2614,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2656,46 +2651,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6262-2024 artfynd.xlsx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6262-2024 karta.png", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 28862-2023 georefererad karta.tif", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6262-2024 georefererad karta.tif", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 28862-2023 FSC-klagomål.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6262-2024 FSC-klagomål.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 28862-2023 FSC-klagomål mail.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6262-2024 FSC-klagomål mail.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 28862-2023 tillsynsbegäran.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6262-2024 tillsynsbegäran.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 28862-2023 tillsynsbegäran mail.docx", "A 28862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6262-2024 tillsynsbegäran mail.docx", "A 6262-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 20397-2026</t>
+          <t>A 60820-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2709,10 +2704,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46139</v>
+        <v>45260</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2725,13 +2720,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2765,42 +2760,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 20397-2026 artfynd.xlsx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 60820-2023 artfynd.xlsx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 20397-2026 karta.png", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 60820-2023 karta.png", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 20397-2026 georefererad karta.tif", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 60820-2023 georefererad karta.tif", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 20397-2026 FSC-klagomål.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 60820-2023 FSC-klagomål.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 20397-2026 FSC-klagomål mail.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 60820-2023 FSC-klagomål mail.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 20397-2026 tillsynsbegäran.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 60820-2023 tillsynsbegäran.docx", "A 60820-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 20397-2026 tillsynsbegäran mail.docx", "A 20397-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 60820-2023 tillsynsbegäran mail.docx", "A 60820-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 60820-2023</t>
+          <t>A 20397-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2814,10 +2809,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45260</v>
+        <v>46139</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2830,13 +2825,13 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2870,42 +2865,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 60820-2023 artfynd.xlsx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 20397-2026 artfynd.xlsx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 60820-2023 karta.png", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 20397-2026 karta.png", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 60820-2023 georefererad karta.tif", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 20397-2026 georefererad karta.tif", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 60820-2023 FSC-klagomål.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 20397-2026 FSC-klagomål.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 60820-2023 FSC-klagomål mail.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 20397-2026 FSC-klagomål mail.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 60820-2023 tillsynsbegäran.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 20397-2026 tillsynsbegäran.docx", "A 20397-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 60820-2023 tillsynsbegäran mail.docx", "A 60820-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 20397-2026 tillsynsbegäran mail.docx", "A 20397-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 42387-2022</t>
+          <t>A 28862-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2919,10 +2914,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44830</v>
+        <v>45104</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2934,17 +2929,22 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>6.6</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2959,7 +2959,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2975,42 +2975,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 42387-2022 artfynd.xlsx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 42387-2022 karta.png", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 42387-2022 georefererad karta.tif", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 28862-2023 georefererad karta.tif", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 42387-2022 FSC-klagomål.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 28862-2023 FSC-klagomål.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 42387-2022 FSC-klagomål mail.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 28862-2023 FSC-klagomål mail.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 42387-2022 tillsynsbegäran.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 28862-2023 tillsynsbegäran.docx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 42387-2022 tillsynsbegäran mail.docx", "A 42387-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 28862-2023 tillsynsbegäran mail.docx", "A 28862-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 756-2024</t>
+          <t>A 32949-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45300</v>
+        <v>46244</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3039,22 +3039,17 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>13.1</v>
+        <v>4.8</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3069,7 +3064,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3085,42 +3080,46 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 756-2024 artfynd.xlsx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 32949-2026 artfynd.xlsx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 756-2024 karta.png", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 32949-2026 karta.png", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 756-2024 georefererad karta.tif", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 32949-2026 georefererad karta.tif", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 756-2024 FSC-klagomål.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 32949-2026 FSC-klagomål.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 756-2024 FSC-klagomål mail.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 32949-2026 FSC-klagomål mail.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 756-2024 tillsynsbegäran.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 32949-2026 tillsynsbegäran.docx", "A 32949-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 756-2024 tillsynsbegäran mail.docx", "A 756-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 32949-2026 tillsynsbegäran mail.docx", "A 32949-2026")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 32949-2026 prioriterade fågelarter.docx", "A 32949-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32949-2026</t>
+          <t>A 756-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3134,10 +3133,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46244</v>
+        <v>45300</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3149,18 +3148,23 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>4.8</v>
+        <v>13.1</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
@@ -3174,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3190,39 +3194,35 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 32949-2026 artfynd.xlsx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 756-2024 artfynd.xlsx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 32949-2026 karta.png", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 756-2024 karta.png", "A 756-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 32949-2026 georefererad karta.tif", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 756-2024 georefererad karta.tif", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 32949-2026 FSC-klagomål.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 756-2024 FSC-klagomål.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 32949-2026 FSC-klagomål mail.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 756-2024 FSC-klagomål mail.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 32949-2026 tillsynsbegäran.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 756-2024 tillsynsbegäran.docx", "A 756-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 32949-2026 tillsynsbegäran mail.docx", "A 32949-2026")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 32949-2026 prioriterade fågelarter.docx", "A 32949-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 756-2024 tillsynsbegäran mail.docx", "A 756-2024")</f>
         <v/>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
         <v>46183</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 17907-2024</t>
+          <t>A 42387-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45419</v>
+        <v>44830</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3373,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3400,39 +3400,39 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Gulplister</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 17907-2024 artfynd.xlsx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 42387-2022 artfynd.xlsx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 17907-2024 karta.png", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 42387-2022 karta.png", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 17907-2024 georefererad karta.tif", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 42387-2022 georefererad karta.tif", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 17907-2024 FSC-klagomål.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 42387-2022 FSC-klagomål.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 17907-2024 FSC-klagomål mail.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 42387-2022 FSC-klagomål mail.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 17907-2024 tillsynsbegäran.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 42387-2022 tillsynsbegäran.docx", "A 42387-2022")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 17907-2024 tillsynsbegäran mail.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 42387-2022 tillsynsbegäran mail.docx", "A 42387-2022")</f>
         <v/>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
         <v>44684</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44560</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44490</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44642</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44721</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 47231-2023</t>
+          <t>A 36180-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45202</v>
+        <v>45534</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4038,7 +4038,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 4023-2024</t>
+          <t>A 2548-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45323</v>
+        <v>45313</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4067,13 +4067,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>15.2</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4116,7 +4111,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 11802-2024</t>
+          <t>A 23185-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4126,14 +4121,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45375</v>
+        <v>45791</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4145,13 +4140,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4194,7 +4184,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 19454-2024</t>
+          <t>A 13159-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4208,10 +4198,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45429</v>
+        <v>45386</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4224,7 +4214,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4267,7 +4257,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 23813-2024</t>
+          <t>A 2555-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4281,10 +4271,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45455</v>
+        <v>44579</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4297,7 +4287,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4340,7 +4330,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 24248-2024</t>
+          <t>A 743-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4354,10 +4344,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45457</v>
+        <v>45300</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4369,8 +4359,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>11.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4413,7 +4408,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2548-2024</t>
+          <t>A 15075-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4423,14 +4418,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45313</v>
+        <v>45399</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4443,7 +4438,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4486,7 +4481,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 23185-2025</t>
+          <t>A 11887-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4496,14 +4491,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45791</v>
+        <v>45376</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4515,8 +4510,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>6.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 17760-2025</t>
+          <t>A 10272-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4573,10 +4573,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45758</v>
+        <v>44986</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4588,8 +4588,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>3.7</v>
+        <v>7.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4632,7 +4637,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 44675-2024</t>
+          <t>A 15158-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4642,14 +4647,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45574</v>
+        <v>45744</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4661,13 +4666,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>11.2</v>
+        <v>1.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4710,7 +4710,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 49815-2025</t>
+          <t>A 43306-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45940</v>
+        <v>45910</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4783,7 +4783,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 15158-2025</t>
+          <t>A 17760-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45744</v>
+        <v>45758</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4856,7 +4856,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 17316-2024</t>
+          <t>A 15012-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4870,10 +4870,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45414</v>
+        <v>45399</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4885,13 +4885,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>4.3</v>
+        <v>6.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4934,7 +4929,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 4969-2026</t>
+          <t>A 45729-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4948,10 +4943,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46049</v>
+        <v>45579</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4963,13 +4958,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>2.6</v>
+        <v>10.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5029,7 +5019,7 @@
         <v>45547</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5085,7 +5075,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 43306-2025</t>
+          <t>A 49815-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5099,10 +5089,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45910</v>
+        <v>45940</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5115,7 +5105,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5158,7 +5148,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 45729-2024</t>
+          <t>A 4969-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5172,10 +5162,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45579</v>
+        <v>46049</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5187,8 +5177,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>10.1</v>
+        <v>2.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5231,7 +5226,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 16568-2024</t>
+          <t>A 8190-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5245,10 +5240,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45408</v>
+        <v>45338</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5260,8 +5255,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5304,7 +5304,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 12310-2023</t>
+          <t>A 8192-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5318,10 +5318,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44999</v>
+        <v>45338</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5335,11 +5335,11 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 60817-2023</t>
+          <t>A 47231-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45260</v>
+        <v>45202</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5455,7 +5455,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 7955-2024</t>
+          <t>A 48171-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45350</v>
+        <v>45933</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5528,7 +5528,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 48171-2025</t>
+          <t>A 28966-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5538,14 +5538,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45933</v>
+        <v>44749</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5601,7 +5601,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 42794-2024</t>
+          <t>A 578-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5615,10 +5615,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45566</v>
+        <v>45299</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5630,8 +5630,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1.9</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5674,7 +5679,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 61970-2025</t>
+          <t>A 6357-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5684,14 +5689,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46003</v>
+        <v>45338</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5703,8 +5708,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5764,7 +5774,7 @@
         <v>45891</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5820,7 +5830,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 2190-2022</t>
+          <t>A 23813-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5834,10 +5844,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44578</v>
+        <v>45455</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5849,13 +5859,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5898,7 +5903,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 10272-2023</t>
+          <t>A 61970-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5908,14 +5913,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44986</v>
+        <v>46003</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5927,13 +5932,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>7.7</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 55676-2022</t>
+          <t>A 19454-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44888</v>
+        <v>45429</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6049,7 +6049,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 6124-2026</t>
+          <t>A 59528-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46053</v>
+        <v>44907</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6078,8 +6078,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6122,7 +6127,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 30806-2023</t>
+          <t>A 30673-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6139,7 +6144,7 @@
         <v>45112</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6157,7 +6162,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6200,7 +6205,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 16621-2026</t>
+          <t>A 11811-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6214,10 +6219,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46112</v>
+        <v>45727</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6229,13 +6234,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>0.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6278,7 +6278,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 6316-2024</t>
+          <t>A 6124-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6292,10 +6292,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45338</v>
+        <v>46053</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6307,13 +6307,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>28.6</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6356,7 +6351,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 11811-2025</t>
+          <t>A 16621-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6370,10 +6365,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45727</v>
+        <v>46112</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6385,8 +6380,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>9.699999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6429,7 +6429,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 8455-2024</t>
+          <t>A 1199-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6443,10 +6443,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45354</v>
+        <v>45302</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5.1</v>
+        <v>16.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6507,7 +6507,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 13159-2024</t>
+          <t>A 49913-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6517,14 +6517,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45386</v>
+        <v>45940</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6580,7 +6580,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 49913-2025</t>
+          <t>A 4018-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6590,14 +6590,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45940</v>
+        <v>45323</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6609,8 +6609,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6653,7 +6658,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 61841-2025</t>
+          <t>A 6259-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6667,10 +6672,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46003</v>
+        <v>45337</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6683,7 +6688,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6726,7 +6731,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 7745-2025</t>
+          <t>A 6316-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6736,14 +6741,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45706</v>
+        <v>45338</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6755,8 +6760,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.4</v>
+        <v>28.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6799,7 +6809,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 15921-2025</t>
+          <t>A 42794-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6813,10 +6823,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45749</v>
+        <v>45566</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6829,7 +6839,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6872,7 +6882,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 35792-2025</t>
+          <t>A 61841-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6886,10 +6896,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45861</v>
+        <v>46003</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6901,13 +6911,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6950,7 +6955,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 35971-2025</t>
+          <t>A 4482-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6964,10 +6969,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45863</v>
+        <v>46045</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6979,8 +6984,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>1.2</v>
+        <v>6.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7023,7 +7033,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 4482-2026</t>
+          <t>A 4188-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7037,10 +7047,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46045</v>
+        <v>45324</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7058,7 +7068,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6.5</v>
+        <v>9.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7101,7 +7111,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 15305-2025</t>
+          <t>A 2190-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7111,14 +7121,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45746</v>
+        <v>44578</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7130,8 +7140,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7174,7 +7189,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 6852-2026</t>
+          <t>A 53977-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7188,10 +7203,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46057</v>
+        <v>44876</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7203,13 +7218,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7252,7 +7262,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 28966-2022</t>
+          <t>A 12903-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7262,14 +7272,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44749</v>
+        <v>45385</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7282,7 +7292,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7325,7 +7335,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 578-2024</t>
+          <t>A 35792-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7339,10 +7349,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45299</v>
+        <v>45861</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7360,7 +7370,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>67.40000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7403,7 +7413,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 21291-2026</t>
+          <t>A 17151-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7417,10 +7427,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46147</v>
+        <v>45412</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7432,8 +7442,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7476,7 +7491,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 21293-2026</t>
+          <t>A 35971-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7490,10 +7505,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46147</v>
+        <v>45863</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7506,7 +7521,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7549,7 +7564,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 12988-2024</t>
+          <t>A 6852-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7563,10 +7578,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45385</v>
+        <v>46057</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7584,7 +7599,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>16.2</v>
+        <v>4.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7627,7 +7642,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 15288-2026</t>
+          <t>A 30040-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7637,14 +7652,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46105</v>
+        <v>45488</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7657,7 +7672,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7700,7 +7715,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 39796-2025</t>
+          <t>A 21291-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7714,10 +7729,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45891</v>
+        <v>46147</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7730,7 +7745,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7773,7 +7788,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 4677-2023</t>
+          <t>A 21293-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7787,10 +7802,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44952</v>
+        <v>46147</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7803,7 +7818,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7846,7 +7861,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 4018-2024</t>
+          <t>A 16483-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7860,10 +7875,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45323</v>
+        <v>45408</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7875,13 +7890,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7924,7 +7934,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 16611-2026</t>
+          <t>A 12663-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7938,10 +7948,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46112</v>
+        <v>44641</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7955,11 +7965,11 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>12.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8002,7 +8012,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 15012-2024</t>
+          <t>A 15288-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8016,10 +8026,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45399</v>
+        <v>46105</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8032,7 +8042,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>6.9</v>
+        <v>4.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8075,7 +8085,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 2555-2022</t>
+          <t>A 30806-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8089,10 +8099,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44579</v>
+        <v>45112</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8104,8 +8114,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8148,7 +8163,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 24002-2026</t>
+          <t>A 39796-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8158,14 +8173,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46167</v>
+        <v>45891</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8178,7 +8193,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>6.4</v>
+        <v>3.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8221,7 +8236,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 4651-2024</t>
+          <t>A 17316-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8235,10 +8250,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45328</v>
+        <v>45414</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8250,8 +8265,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8294,7 +8314,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 30040-2024</t>
+          <t>A 16611-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8304,14 +8324,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45488</v>
+        <v>46112</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8323,8 +8343,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8367,7 +8392,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 15296-2026</t>
+          <t>A 24002-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8377,14 +8402,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46105</v>
+        <v>46167</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8397,7 +8422,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.3</v>
+        <v>6.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8440,7 +8465,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 6357-2024</t>
+          <t>A 15296-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8454,10 +8479,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45338</v>
+        <v>46105</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8469,13 +8494,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8518,7 +8538,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 30673-2023</t>
+          <t>A 31993-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8532,10 +8552,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45112</v>
+        <v>45119</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8547,13 +8567,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>2.4</v>
+        <v>6.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8596,7 +8611,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 31993-2023</t>
+          <t>A 16568-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8610,10 +8625,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45119</v>
+        <v>45408</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8626,7 +8641,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>6.8</v>
+        <v>0.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8669,7 +8684,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 11894-2024</t>
+          <t>A 4677-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8683,10 +8698,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45376</v>
+        <v>44952</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8698,13 +8713,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8747,7 +8757,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 16483-2024</t>
+          <t>A 11802-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8761,10 +8771,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45408</v>
+        <v>45375</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8776,8 +8786,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>4.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8820,7 +8835,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 23621-2026</t>
+          <t>A 11894-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8834,10 +8849,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46162</v>
+        <v>45376</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8849,8 +8864,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8893,7 +8913,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 24987-2026</t>
+          <t>A 24248-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8907,10 +8927,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46174</v>
+        <v>45457</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8923,7 +8943,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8966,7 +8986,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 38562-2023</t>
+          <t>A 23621-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8980,10 +9000,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45162</v>
+        <v>46162</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8996,7 +9016,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9039,7 +9059,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 51031-2023</t>
+          <t>A 5027-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9053,10 +9073,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45211</v>
+        <v>45329</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9068,8 +9088,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9112,7 +9137,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 59528-2022</t>
+          <t>A 24987-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9126,10 +9151,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44907</v>
+        <v>46174</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9141,13 +9166,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9190,7 +9210,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 16027-2022</t>
+          <t>A 31134-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9204,10 +9224,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44665</v>
+        <v>46216</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9225,7 +9245,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9268,7 +9288,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 6259-2024</t>
+          <t>A 12181-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9282,10 +9302,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45337</v>
+        <v>44998</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9298,7 +9318,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9341,7 +9361,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 31134-2026</t>
+          <t>A 38562-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9355,10 +9375,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46216</v>
+        <v>45162</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9370,13 +9390,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9419,7 +9434,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 35897-2026</t>
+          <t>A 17778-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9433,10 +9448,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46266</v>
+        <v>45418</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9448,8 +9463,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9492,7 +9512,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 1199-2024</t>
+          <t>A 35897-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9506,10 +9526,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45302</v>
+        <v>46266</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9521,13 +9541,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>16.1</v>
+        <v>3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9570,7 +9585,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 26473-2024</t>
+          <t>A 44675-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9580,14 +9595,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45469</v>
+        <v>45574</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9599,8 +9614,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>4.4</v>
+        <v>11.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9643,7 +9663,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 17778-2024</t>
+          <t>A 26473-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9657,10 +9677,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45418</v>
+        <v>45469</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9672,13 +9692,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9721,7 +9736,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 8190-2024</t>
+          <t>A 51031-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9735,10 +9750,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45338</v>
+        <v>45211</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9750,13 +9765,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9799,7 +9809,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 8192-2024</t>
+          <t>A 7745-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9809,14 +9819,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45338</v>
+        <v>45706</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9828,13 +9838,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9877,7 +9882,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 17151-2024</t>
+          <t>A 38074-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9891,10 +9896,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45412</v>
+        <v>46280</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9906,13 +9911,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9955,7 +9955,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 12181-2023</t>
+          <t>A 5565-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9969,10 +9969,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44998</v>
+        <v>45334</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10045,7 +10045,7 @@
         <v>44720</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 38074-2026</t>
+          <t>A 32948-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10120,10 +10120,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46280</v>
+        <v>46244</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 5027-2024</t>
+          <t>A 32955-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10193,10 +10193,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45329</v>
+        <v>46244</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10208,13 +10208,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10257,7 +10252,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 743-2024</t>
+          <t>A 7955-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10271,10 +10266,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45300</v>
+        <v>45350</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10286,13 +10281,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>11.1</v>
+        <v>2.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10335,7 +10325,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 53977-2022</t>
+          <t>A 10908-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10349,10 +10339,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44876</v>
+        <v>46079</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10365,7 +10355,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10408,7 +10398,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 32955-2026</t>
+          <t>A 40128-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10422,10 +10412,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46244</v>
+        <v>46293</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10438,7 +10428,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>6</v>
+        <v>0.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10481,7 +10471,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 32948-2026</t>
+          <t>A 55676-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10495,10 +10485,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46244</v>
+        <v>44888</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10511,7 +10501,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10554,7 +10544,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 10908-2026</t>
+          <t>A 40129-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10568,10 +10558,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46079</v>
+        <v>46293</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10584,7 +10574,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10627,7 +10617,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 4188-2024</t>
+          <t>A 25597-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10641,10 +10631,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45324</v>
+        <v>46177</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10656,13 +10646,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>9.6</v>
+        <v>2.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10705,7 +10690,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 12663-2022</t>
+          <t>A 37743-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10719,10 +10704,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44641</v>
+        <v>46279</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10734,13 +10719,8 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>12.4</v>
+        <v>1.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10783,7 +10763,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 40128-2026</t>
+          <t>A 8455-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10797,10 +10777,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46293</v>
+        <v>45354</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10812,8 +10792,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>0.9</v>
+        <v>5.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10856,7 +10841,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 40129-2026</t>
+          <t>A 16027-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10870,10 +10855,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46293</v>
+        <v>44665</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10885,8 +10870,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10929,7 +10919,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 36180-2024</t>
+          <t>A 4651-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10943,10 +10933,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45534</v>
+        <v>45328</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10959,7 +10949,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11002,7 +10992,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 25597-2026</t>
+          <t>A 12988-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11016,10 +11006,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46177</v>
+        <v>45385</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11031,8 +11021,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>2.5</v>
+        <v>16.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11075,7 +11070,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 37743-2026</t>
+          <t>A 15305-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11085,14 +11080,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46279</v>
+        <v>45746</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11105,7 +11100,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11148,7 +11143,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 12903-2024</t>
+          <t>A 60817-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11162,10 +11157,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45385</v>
+        <v>45260</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11178,7 +11173,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>9.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11221,7 +11216,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 15075-2024</t>
+          <t>A 4023-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11231,14 +11226,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45399</v>
+        <v>45323</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11250,8 +11245,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>1.7</v>
+        <v>15.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11294,7 +11294,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 11887-2024</t>
+          <t>A 12310-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11308,10 +11308,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45376</v>
+        <v>44999</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11325,11 +11325,11 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>6.3</v>
+        <v>2.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11372,7 +11372,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 5565-2024</t>
+          <t>A 15921-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11386,10 +11386,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45334</v>
+        <v>45749</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11462,7 +11462,7 @@
         <v>45532</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>45532</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>45727</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>45727</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>45537</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>

--- a/Översikt TOMELILLA.xlsx
+++ b/Översikt TOMELILLA.xlsx
@@ -601,7 +601,7 @@
         <v>44756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45120</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45260</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>45308</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>45009</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45299</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>45429</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45744</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>44613</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>44721</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>45419</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>45337</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>45940</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>46000</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>45337</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>44578</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45811</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>45337</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>45260</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>46139</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>45104</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>46244</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>45300</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>46183</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>44830</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>44684</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44560</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44490</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44642</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44721</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>45534</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>45313</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>45791</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>45386</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>44579</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>45300</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>45399</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>45376</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>44986</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>45744</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>45910</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>45758</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>45399</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>45579</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>45547</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>45940</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>46049</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>45338</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>45338</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>45202</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>45933</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>44749</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>45299</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>45338</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>45891</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>45455</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>46003</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45429</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>44907</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>45112</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>45727</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>46053</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>46112</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>45302</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>45940</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>45323</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45337</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>45338</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6826,7 +6826,7 @@
         <v>45566</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>46003</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>46045</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>45324</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>44578</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>44876</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>45385</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>45861</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>45412</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>45863</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>46057</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>45488</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>46147</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>46147</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>45408</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>44641</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8029,7 +8029,7 @@
         <v>46105</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>45112</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>45891</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>45414</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>46112</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>46167</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>46105</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>45119</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>45408</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         <v>44952</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>45375</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>45376</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>45457</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         <v>46162</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>45329</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>46174</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>46216</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>44998</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>45162</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>45418</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>46266</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>45574</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>45469</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>45211</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>45706</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>46280</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>45334</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>44720</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>46244</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>46244</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>45350</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>46079</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>46293</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>44888</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>46293</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>46177</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>46279</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>45354</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>44665</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>45328</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>45385</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>45746</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>45260</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>45323</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>44999</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>45749</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>45532</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>45532</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>45727</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>45727</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>45537</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>

--- a/Översikt TOMELILLA.xlsx
+++ b/Översikt TOMELILLA.xlsx
@@ -601,7 +601,7 @@
         <v>44756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45120</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45260</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>45308</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>45009</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45299</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>45429</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45744</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>44613</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>44721</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>45419</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>45337</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>45940</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>46000</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>45337</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>44578</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45811</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>45337</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>45260</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>46139</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>45104</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>46244</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>45300</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>46183</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>44830</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>44684</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44560</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44490</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44642</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44721</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>45534</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>45313</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>45791</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>45386</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>44579</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>45300</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>45399</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>45376</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>44986</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>45744</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>45910</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>45758</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>45399</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>45579</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>45547</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>45940</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>46049</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>45338</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>45338</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>45202</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>45933</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>44749</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>45299</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>45338</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>45891</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>45455</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>46003</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45429</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>44907</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>45112</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>45727</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>46053</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>46112</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>45302</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>45940</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>45323</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45337</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>45338</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6826,7 +6826,7 @@
         <v>45566</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>46003</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>46045</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>45324</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>44578</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>44876</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>45385</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>45861</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>45412</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>45863</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>46057</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>45488</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>46147</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>46147</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>45408</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>44641</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8029,7 +8029,7 @@
         <v>46105</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>45112</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>45891</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>45414</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>46112</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>46167</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>46105</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>45119</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>45408</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         <v>44952</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>45375</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>45376</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>45457</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         <v>46162</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>45329</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>46174</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>46216</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>44998</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>45162</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>45418</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>46266</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>45574</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>45469</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>45211</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>45706</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>46280</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>45334</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>44720</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>46244</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>46244</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>45350</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>46079</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>46293</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>44888</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>46293</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>46177</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>46279</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>45354</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>44665</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>45328</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>45385</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>45746</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>45260</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>45323</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>44999</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>45749</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>45532</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>45532</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>45727</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>45727</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>45537</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>

--- a/Översikt TOMELILLA.xlsx
+++ b/Översikt TOMELILLA.xlsx
@@ -601,7 +601,7 @@
         <v>44756</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45952</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45120</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45260</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2018-2024</t>
+          <t>A 14152-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45308</v>
+        <v>45009</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>17.2</v>
+        <v>3.5</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1125,10 +1125,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1140,153 +1140,153 @@
         <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Kråka
+Röd glada</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 14152-2023 artfynd.xlsx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 14152-2023 karta.png", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 14152-2023 georefererad karta.tif", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 14152-2023 FSC-klagomål.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 14152-2023 FSC-klagomål mail.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 14152-2023 tillsynsbegäran.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 14152-2023 tillsynsbegäran mail.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 14152-2023 prioriterade fågelarter.docx", "A 14152-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 2018-2024</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45308</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TOMELILLA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Västlig hakmossa
 Röd glada</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2018-2024 artfynd.xlsx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2018-2024 karta.png", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2018-2024 georefererad karta.tif", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2018-2024 FSC-klagomål.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2018-2024 FSC-klagomål mail.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2018-2024 tillsynsbegäran.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2018-2024 tillsynsbegäran mail.docx", "A 2018-2024")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 2018-2024 prioriterade fågelarter.docx", "A 2018-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 14152-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45009</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>TOMELILLA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Kråka
-Röd glada</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 14152-2023 artfynd.xlsx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 14152-2023 karta.png", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 14152-2023 georefererad karta.tif", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 14152-2023 FSC-klagomål.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 14152-2023 FSC-klagomål mail.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 14152-2023 tillsynsbegäran.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 14152-2023 tillsynsbegäran mail.docx", "A 14152-2023")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/fåglar/A 14152-2023 prioriterade fågelarter.docx", "A 14152-2023")</f>
         <v/>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
         <v>45299</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>45429</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45744</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>44613</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>44721</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17907-2024</t>
+          <t>A 6261-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45419</v>
+        <v>45337</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1875,13 +1875,13 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.1</v>
+        <v>12.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1915,42 +1915,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Gulplister</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 17907-2024 artfynd.xlsx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 17907-2024 karta.png", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 17907-2024 georefererad karta.tif", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 17907-2024 FSC-klagomål.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 17907-2024 FSC-klagomål mail.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 17907-2024 tillsynsbegäran.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 17907-2024 tillsynsbegäran mail.docx", "A 17907-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 6261-2024</t>
+          <t>A 49813-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45337</v>
+        <v>45940</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1980,13 +1980,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>12.6</v>
+        <v>4.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -2016,46 +2016,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 49813-2025 artfynd.xlsx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 49813-2025 karta.png", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 49813-2025 georefererad karta.tif", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 49813-2025 FSC-klagomål.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 49813-2025 FSC-klagomål mail.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 49813-2025 tillsynsbegäran.docx", "A 49813-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 49813-2025 tillsynsbegäran mail.docx", "A 49813-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 49813-2025</t>
+          <t>A 6261-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45940</v>
+        <v>45337</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2085,13 +2085,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.5</v>
+        <v>12.6</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2121,46 +2121,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 49813-2025 artfynd.xlsx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 49813-2025 karta.png", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 49813-2025 georefererad karta.tif", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 49813-2025 FSC-klagomål.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 49813-2025 FSC-klagomål mail.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 49813-2025 tillsynsbegäran.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 49813-2025 tillsynsbegäran mail.docx", "A 49813-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 61314-2025</t>
+          <t>A 2193-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46000</v>
+        <v>44578</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2189,18 +2189,23 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
@@ -2214,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2226,46 +2231,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Skogslysing</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2193-2022 artfynd.xlsx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2193-2022 karta.png", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2193-2022 georefererad karta.tif", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2193-2022 FSC-klagomål.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2193-2022 FSC-klagomål mail.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2193-2022 tillsynsbegäran.docx", "A 2193-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2193-2022 tillsynsbegäran mail.docx", "A 2193-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6261-2024</t>
+          <t>A 26958-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2279,10 +2284,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45337</v>
+        <v>45811</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2295,7 +2300,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>12.6</v>
+        <v>2.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2331,46 +2336,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6261-2024 artfynd.xlsx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26958-2025 artfynd.xlsx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6261-2024 karta.png", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26958-2025 karta.png", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6261-2024 georefererad karta.tif", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26958-2025 georefererad karta.tif", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6261-2024 FSC-klagomål.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26958-2025 FSC-klagomål.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6261-2024 FSC-klagomål mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26958-2025 FSC-klagomål mail.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6261-2024 tillsynsbegäran.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26958-2025 tillsynsbegäran.docx", "A 26958-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6261-2024 tillsynsbegäran mail.docx", "A 6261-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26958-2025 tillsynsbegäran mail.docx", "A 26958-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 2193-2022</t>
+          <t>A 61314-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2384,10 +2389,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44578</v>
+        <v>46000</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2399,22 +2404,17 @@
           <t>TOMELILLA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2441,46 +2441,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Skogslysing</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 2193-2022 artfynd.xlsx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 61314-2025 artfynd.xlsx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 2193-2022 karta.png", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 61314-2025 karta.png", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 2193-2022 georefererad karta.tif", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 61314-2025 georefererad karta.tif", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 2193-2022 FSC-klagomål.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 61314-2025 FSC-klagomål.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 2193-2022 FSC-klagomål mail.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 61314-2025 FSC-klagomål mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 2193-2022 tillsynsbegäran.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 61314-2025 tillsynsbegäran.docx", "A 61314-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 2193-2022 tillsynsbegäran mail.docx", "A 2193-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 61314-2025 tillsynsbegäran mail.docx", "A 61314-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 26958-2025</t>
+          <t>A 6262-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45811</v>
+        <v>45337</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2546,46 +2546,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 26958-2025 artfynd.xlsx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6262-2024 artfynd.xlsx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 26958-2025 karta.png", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6262-2024 karta.png", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 26958-2025 georefererad karta.tif", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6262-2024 georefererad karta.tif", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 26958-2025 FSC-klagomål.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomål/A 6262-2024 FSC-klagomål.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 26958-2025 FSC-klagomål mail.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/klagomålsmail/A 6262-2024 FSC-klagomål mail.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 26958-2025 tillsynsbegäran.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsyn/A 6262-2024 tillsynsbegäran.docx", "A 6262-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 26958-2025 tillsynsbegäran mail.docx", "A 26958-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/tillsynsmail/A 6262-2024 tillsynsbegäran mail.docx", "A 6262-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 6262-2024</t>
+          <t>A 28862-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45337</v>
+        <v>45104</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2614,8 +2614,13 @@
           <t>TOMELILLA</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2651,39 +2656,39 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 6262-2024 artfynd.xlsx", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/artfynd/A 28862-2023 artfynd.xlsx", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 6262-2024 karta.png", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor/A 28862-2023 karta.png", "A 28862-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff/A 6262-2024 georefererad karta.tif", "A 6262-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1270/kartor_geotiff